--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -642,7 +642,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-14T21:08:35+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-09-15T03:05:08+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -2136,22 +2136,22 @@
       </c>
       <c r="G15" s="23" t="n"/>
       <c r="H15" s="13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>0.3394779337547694</v>
+        <v>0.3415706915444789</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0.08755760368663595</v>
+        <v>0.09174311926605505</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="L15" s="14" t="n">
         <v>0.095</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>2.734257271302464</v>
+        <v>2.586492261217029</v>
       </c>
       <c r="N15" s="15" t="n">
         <v>0</v>
@@ -3088,12 +3088,12 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>FSU @ ALA</t>
+          <t>ARST @ TCU</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D30" s="25" t="n">
@@ -3106,27 +3106,27 @@
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>FSU ML</t>
+          <t>ARST ML</t>
         </is>
       </c>
       <c r="G30" s="26" t="n"/>
       <c r="H30" s="18" t="n">
-        <v>950</v>
+        <v>800</v>
       </c>
       <c r="I30" s="20" t="n">
-        <v>0.2055337410056303</v>
+        <v>0.2383301549565342</v>
       </c>
       <c r="J30" s="20" t="n">
-        <v>0.09174311926605505</v>
+        <v>0.1066176470588235</v>
       </c>
       <c r="K30" s="20" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>0.09499999999913208</v>
+        <v>0.09499999999903685</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>1.158104280559118</v>
+        <v>1.144971394608808</v>
       </c>
       <c r="N30" s="20" t="n">
         <v>0</v>
@@ -3153,12 +3153,12 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>ARST @ TCU</t>
+          <t>GAST @ UCF</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D31" s="22" t="n">
@@ -3171,27 +3171,27 @@
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>ARST ML</t>
+          <t>GAST ML</t>
         </is>
       </c>
       <c r="G31" s="23" t="n"/>
       <c r="H31" s="13" t="n">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>0.2383301549565342</v>
+        <v>0.2459347859855046</v>
       </c>
       <c r="J31" s="15" t="n">
-        <v>0.1066176470588235</v>
+        <v>0.1130434782608696</v>
       </c>
       <c r="K31" s="15" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="L31" s="14" t="n">
-        <v>0.09499999999903685</v>
+        <v>0.09499999999660841</v>
       </c>
       <c r="M31" s="14" t="n">
-        <v>1.144971394608808</v>
+        <v>1.090445680876789</v>
       </c>
       <c r="N31" s="15" t="n">
         <v>0</v>
@@ -3218,12 +3218,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>GAST @ UCF</t>
+          <t>LT @ BAY</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D32" s="25" t="n">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>GAST ML</t>
+          <t>LT ML</t>
         </is>
       </c>
       <c r="G32" s="26" t="n"/>
@@ -3244,7 +3244,7 @@
         <v>750</v>
       </c>
       <c r="I32" s="20" t="n">
-        <v>0.2459347859855046</v>
+        <v>0.2352858536522798</v>
       </c>
       <c r="J32" s="20" t="n">
         <v>0.1130434782608696</v>
@@ -3253,10 +3253,10 @@
         <v>0.1176470588235294</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>0.09499999999660841</v>
+        <v>0.09499999997535674</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>1.090445680876789</v>
+        <v>0.9999297560443785</v>
       </c>
       <c r="N32" s="20" t="n">
         <v>0</v>
@@ -3283,12 +3283,12 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>LT @ BAY</t>
+          <t>FSU @ ALA</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D33" s="22" t="n">
@@ -3301,27 +3301,27 @@
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>LT ML</t>
+          <t>FSU ML</t>
         </is>
       </c>
       <c r="G33" s="23" t="n"/>
       <c r="H33" s="13" t="n">
-        <v>750</v>
+        <v>850</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>0.2352858536522798</v>
+        <v>0.2102331438522113</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>0.1130434782608696</v>
+        <v>0.101141924959217</v>
       </c>
       <c r="K33" s="15" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>0.09499999997535674</v>
+        <v>0.09499999997387173</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>0.9999297560443785</v>
+        <v>0.997214866596007</v>
       </c>
       <c r="N33" s="15" t="n">
         <v>0</v>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>KENT @ OSU</t>
+          <t>BUFF @ PSU</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
@@ -3628,29 +3628,29 @@
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>KENT +52.5</t>
+          <t>BUFF +39.5</t>
         </is>
       </c>
       <c r="G38" s="26" t="n">
-        <v>-52.5</v>
+        <v>-39.5</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I38" s="20" t="n">
-        <v>0.7477418884696789</v>
+        <v>0.7416304528252272</v>
       </c>
       <c r="J38" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K38" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>0.09499574326169095</v>
+        <v>0.0949963700146782</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>0.440095488904567</v>
+        <v>0.4479451698016341</v>
       </c>
       <c r="N38" s="20" t="n">
         <v>0</v>
@@ -3677,12 +3677,12 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>WKU @ IU</t>
+          <t>KENT @ OSU</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D39" s="22" t="n">
@@ -3695,17 +3695,17 @@
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>WKU +44.5</t>
+          <t>KENT +52.5</t>
         </is>
       </c>
       <c r="G39" s="23" t="n">
-        <v>-44.5</v>
+        <v>-52.5</v>
       </c>
       <c r="H39" s="13" t="n">
         <v>-108</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>0.746930631659275</v>
+        <v>0.7477418884696789</v>
       </c>
       <c r="J39" s="15" t="n">
         <v>0.4956702459300312</v>
@@ -3714,10 +3714,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L39" s="14" t="n">
-        <v>0.09499559403640924</v>
+        <v>0.09499574326169095</v>
       </c>
       <c r="M39" s="14" t="n">
-        <v>0.438533068380826</v>
+        <v>0.440095488904567</v>
       </c>
       <c r="N39" s="15" t="n">
         <v>0</v>
@@ -3744,12 +3744,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>BUFF @ PSU</t>
+          <t>WKU @ IU</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D40" s="25" t="n">
@@ -3762,17 +3762,17 @@
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>BUFF +39.5</t>
+          <t>WKU +44.5</t>
         </is>
       </c>
       <c r="G40" s="26" t="n">
-        <v>-39.5</v>
+        <v>-44.5</v>
       </c>
       <c r="H40" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I40" s="20" t="n">
-        <v>0.7448826938834172</v>
+        <v>0.746930631659275</v>
       </c>
       <c r="J40" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -3781,10 +3781,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>0.09499519364471777</v>
+        <v>0.09499559403640924</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>0.4345888919236185</v>
+        <v>0.438533068380826</v>
       </c>
       <c r="N40" s="20" t="n">
         <v>0</v>
@@ -3945,12 +3945,12 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>BYU @ CSU</t>
+          <t>MIA @ WAKE</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-18 23:30</t>
         </is>
       </c>
       <c r="D43" s="22" t="n">
@@ -3963,17 +3963,17 @@
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>CSU +17.5</t>
+          <t>WAKE +20.5</t>
         </is>
       </c>
       <c r="G43" s="23" t="n">
-        <v>17.5</v>
+        <v>20.5</v>
       </c>
       <c r="H43" s="13" t="n">
         <v>-105</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>0.7277532660511183</v>
+        <v>0.729764022242086</v>
       </c>
       <c r="J43" s="15" t="n">
         <v>0.4891657638136511</v>
@@ -3982,10 +3982,10 @@
         <v>0.5121951219512195</v>
       </c>
       <c r="L43" s="14" t="n">
-        <v>0.09499340404251394</v>
+        <v>0.09499395082886701</v>
       </c>
       <c r="M43" s="14" t="n">
-        <v>0.4208516146712311</v>
+        <v>0.4247773767583585</v>
       </c>
       <c r="N43" s="15" t="n">
         <v>0</v>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>UGA @ ARK</t>
+          <t>BYU @ CSU</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D44" s="25" t="n">
@@ -4030,29 +4030,29 @@
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>ARK +25.5</t>
+          <t>CSU +17.5</t>
         </is>
       </c>
       <c r="G44" s="26" t="n">
-        <v>25.5</v>
+        <v>17.5</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I44" s="20" t="n">
-        <v>0.7460920421295146</v>
+        <v>0.7277532660511183</v>
       </c>
       <c r="J44" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K44" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L44" s="19" t="n">
-        <v>0.09499213308832515</v>
+        <v>0.09499340404251394</v>
       </c>
       <c r="M44" s="19" t="n">
-        <v>0.412245651173724</v>
+        <v>0.4208516146712311</v>
       </c>
       <c r="N44" s="20" t="n">
         <v>0</v>
@@ -4079,12 +4079,12 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>NIU @ ARIZ</t>
+          <t>UGA @ ARK</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 02:30</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D45" s="22" t="n">
@@ -4097,17 +4097,17 @@
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>NIU +34.5</t>
+          <t>ARK +25.5</t>
         </is>
       </c>
       <c r="G45" s="23" t="n">
-        <v>-34.5</v>
+        <v>25.5</v>
       </c>
       <c r="H45" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>0.744256934025459</v>
+        <v>0.7460920421295146</v>
       </c>
       <c r="J45" s="15" t="n">
         <v>0.5043297540699688</v>
@@ -4116,10 +4116,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L45" s="14" t="n">
-        <v>0.09499150679335959</v>
+        <v>0.09499213308832515</v>
       </c>
       <c r="M45" s="14" t="n">
-        <v>0.4087720536910473</v>
+        <v>0.412245651173724</v>
       </c>
       <c r="N45" s="15" t="n">
         <v>0</v>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>UTSA @ TEX</t>
+          <t>NIU @ ARIZ</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-20 02:30</t>
         </is>
       </c>
       <c r="D46" s="25" t="n">
@@ -4164,17 +4164,17 @@
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>UTSA +30.5</t>
+          <t>NIU +34.5</t>
         </is>
       </c>
       <c r="G46" s="26" t="n">
-        <v>-30.5</v>
+        <v>-34.5</v>
       </c>
       <c r="H46" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I46" s="20" t="n">
-        <v>0.744245043012444</v>
+        <v>0.744256934025459</v>
       </c>
       <c r="J46" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -4183,10 +4183,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L46" s="19" t="n">
-        <v>0.09499150257667892</v>
+        <v>0.09499150679335959</v>
       </c>
       <c r="M46" s="19" t="n">
-        <v>0.408749545702126</v>
+        <v>0.4087720536910473</v>
       </c>
       <c r="N46" s="20" t="n">
         <v>0</v>
@@ -4213,12 +4213,12 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>MIA @ WAKE</t>
+          <t>UTSA @ TEX</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>2026-09-18 23:30</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D47" s="22" t="n">
@@ -4231,32 +4231,32 @@
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>WAKE +21</t>
+          <t>UTSA +30.5</t>
         </is>
       </c>
       <c r="G47" s="23" t="n">
-        <v>21</v>
+        <v>-30.5</v>
       </c>
       <c r="H47" s="13" t="n">
         <v>-112</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>0.7392782043459014</v>
+        <v>0.744245043012444</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>0.502134927412468</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K47" s="15" t="n">
         <v>0.5283018867924528</v>
       </c>
       <c r="L47" s="14" t="n">
-        <v>0.09499086416737967</v>
+        <v>0.09499150257667892</v>
       </c>
       <c r="M47" s="14" t="n">
-        <v>0.3968720718708824</v>
+        <v>0.408749545702126</v>
       </c>
       <c r="N47" s="15" t="n">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="O47" s="24" t="n">
         <v>0.839</v>
@@ -5033,29 +5033,29 @@
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>FSU +20.5</t>
+          <t>FSU +19.5</t>
         </is>
       </c>
       <c r="G59" s="23" t="n">
-        <v>-20.5</v>
+        <v>-19.5</v>
       </c>
       <c r="H59" s="13" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>0.6887753710023599</v>
+        <v>0.6793442663113145</v>
       </c>
       <c r="J59" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K59" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v>0.09493291305090019</v>
+        <v>0.0949222753312902</v>
       </c>
       <c r="M59" s="14" t="n">
-        <v>0.3149347991863234</v>
+        <v>0.3083667351180872</v>
       </c>
       <c r="N59" s="15" t="n">
         <v>0</v>
@@ -5569,32 +5569,32 @@
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>MTSU +4</t>
+          <t>MTSU +3.5</t>
         </is>
       </c>
       <c r="G67" s="23" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="H67" s="13" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>0.6621583907731265</v>
+        <v>0.6456780878627362</v>
       </c>
       <c r="J67" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K67" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L67" s="14" t="n">
-        <v>0.09462892117027975</v>
+        <v>0.09467566434614678</v>
       </c>
       <c r="M67" s="14" t="n">
-        <v>0.2327372281153645</v>
+        <v>0.2435281692171216</v>
       </c>
       <c r="N67" s="15" t="n">
-        <v>0.0219</v>
+        <v>0</v>
       </c>
       <c r="O67" s="24" t="n">
         <v>0.839</v>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>M-OH @ CIN</t>
+          <t>WVU @ UVA</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D68" s="25" t="n">
@@ -5636,32 +5636,32 @@
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>M-OH +14.5</t>
+          <t>WVU +10</t>
         </is>
       </c>
       <c r="G68" s="26" t="n">
-        <v>-14.5</v>
+        <v>-10</v>
       </c>
       <c r="H68" s="18" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="I68" s="20" t="n">
-        <v>0.6451811605078074</v>
+        <v>0.6355658088456844</v>
       </c>
       <c r="J68" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K68" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L68" s="19" t="n">
-        <v>0.09458024269901827</v>
+        <v>0.09465199868567865</v>
       </c>
       <c r="M68" s="19" t="n">
-        <v>0.2317094882421777</v>
+        <v>0.2331106753254756</v>
       </c>
       <c r="N68" s="20" t="n">
-        <v>0</v>
+        <v>0.0322</v>
       </c>
       <c r="O68" s="27" t="n">
         <v>0.839</v>
@@ -5685,12 +5685,12 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>WVU @ UVA</t>
+          <t>M-OH @ CIN</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D69" s="22" t="n">
@@ -5703,32 +5703,32 @@
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>WVU +10</t>
+          <t>M-OH +14.5</t>
         </is>
       </c>
       <c r="G69" s="23" t="n">
-        <v>-10</v>
+        <v>-14.5</v>
       </c>
       <c r="H69" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>0.6388180499038745</v>
+        <v>0.6451811605078074</v>
       </c>
       <c r="J69" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K69" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L69" s="14" t="n">
-        <v>0.09456620654981601</v>
+        <v>0.09458024269901827</v>
       </c>
       <c r="M69" s="14" t="n">
-        <v>0.2229000611941639</v>
+        <v>0.2317094882421777</v>
       </c>
       <c r="N69" s="15" t="n">
-        <v>0.0322</v>
+        <v>0</v>
       </c>
       <c r="O69" s="24" t="n">
         <v>0.839</v>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>SYR @ PITT</t>
+          <t>CONN @ USM</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>2026-09-17 23:30</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D72" s="25" t="n">
@@ -5897,35 +5897,37 @@
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F72" s="17" t="inlineStr">
         <is>
-          <t>SYR ML</t>
-        </is>
-      </c>
-      <c r="G72" s="26" t="n"/>
+          <t>USM +3</t>
+        </is>
+      </c>
+      <c r="G72" s="26" t="n">
+        <v>3</v>
+      </c>
       <c r="H72" s="18" t="n">
-        <v>340</v>
+        <v>-105</v>
       </c>
       <c r="I72" s="20" t="n">
-        <v>0.2793579096730459</v>
+        <v>0.622927671553746</v>
       </c>
       <c r="J72" s="20" t="n">
-        <v>0.2180936995153474</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K72" s="20" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L72" s="19" t="n">
-        <v>0.09448804645983883</v>
+        <v>0.09440127563507143</v>
       </c>
       <c r="M72" s="19" t="n">
-        <v>0.2291748025614018</v>
+        <v>0.2056419451647072</v>
       </c>
       <c r="N72" s="20" t="n">
-        <v>0</v>
+        <v>0.0488</v>
       </c>
       <c r="O72" s="27" t="n">
         <v>0.839</v>
@@ -5937,7 +5939,7 @@
       </c>
       <c r="Q72" s="17" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -5949,12 +5951,12 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>CONN @ USM</t>
+          <t>LSU @ MISS</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D73" s="22" t="n">
@@ -5962,37 +5964,35 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>USM +3</t>
-        </is>
-      </c>
-      <c r="G73" s="23" t="n">
-        <v>3</v>
-      </c>
+          <t>MISS ML</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="n"/>
       <c r="H73" s="13" t="n">
-        <v>-105</v>
+        <v>130</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>0.622927671553746</v>
+        <v>0.5256664799798741</v>
       </c>
       <c r="J73" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4170073589533933</v>
       </c>
       <c r="K73" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="L73" s="14" t="n">
-        <v>0.09440127563507143</v>
+        <v>0.09421555028487143</v>
       </c>
       <c r="M73" s="14" t="n">
-        <v>0.2056419451647072</v>
+        <v>0.2090329039537104</v>
       </c>
       <c r="N73" s="15" t="n">
-        <v>0.0488</v>
+        <v>0</v>
       </c>
       <c r="O73" s="24" t="n">
         <v>0.839</v>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="Q73" s="12" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -6016,12 +6016,12 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>LSU @ MISS</t>
+          <t>MRSH @ MOST</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 22:30</t>
         </is>
       </c>
       <c r="D74" s="25" t="n">
@@ -6029,32 +6029,34 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>MISS ML</t>
-        </is>
-      </c>
-      <c r="G74" s="26" t="n"/>
+          <t>MOST +3.5</t>
+        </is>
+      </c>
+      <c r="G74" s="26" t="n">
+        <v>3.5</v>
+      </c>
       <c r="H74" s="18" t="n">
-        <v>130</v>
+        <v>-115</v>
       </c>
       <c r="I74" s="20" t="n">
-        <v>0.5256664799798741</v>
+        <v>0.6419872296137685</v>
       </c>
       <c r="J74" s="20" t="n">
-        <v>0.4170073589533933</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K74" s="20" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L74" s="19" t="n">
-        <v>0.09421555028487143</v>
+        <v>0.09415004360125051</v>
       </c>
       <c r="M74" s="19" t="n">
-        <v>0.2090329039537104</v>
+        <v>0.2002369944953062</v>
       </c>
       <c r="N74" s="20" t="n">
         <v>0</v>
@@ -6069,7 +6071,7 @@
       </c>
       <c r="Q74" s="17" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -6081,12 +6083,12 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>MRSH @ MOST</t>
+          <t>VT @ MD</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 22:30</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D75" s="22" t="n">
@@ -6099,17 +6101,17 @@
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>MOST +3.5</t>
+          <t>MD +3</t>
         </is>
       </c>
       <c r="G75" s="23" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="H75" s="13" t="n">
         <v>-115</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>0.6419872296137685</v>
+        <v>0.6417725157444896</v>
       </c>
       <c r="J75" s="15" t="n">
         <v>0.5108342361863488</v>
@@ -6118,13 +6120,13 @@
         <v>0.5348837209302325</v>
       </c>
       <c r="L75" s="14" t="n">
-        <v>0.09415004360125051</v>
+        <v>0.09414252318920331</v>
       </c>
       <c r="M75" s="14" t="n">
-        <v>0.2002369944953062</v>
+        <v>0.1904233174293797</v>
       </c>
       <c r="N75" s="15" t="n">
-        <v>0</v>
+        <v>0.0471</v>
       </c>
       <c r="O75" s="24" t="n">
         <v>0.839</v>
@@ -6148,12 +6150,12 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>VT @ MD</t>
+          <t>PUR @ UCLA</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-20 03:00</t>
         </is>
       </c>
       <c r="D76" s="25" t="n">
@@ -6166,32 +6168,32 @@
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>MD +3</t>
+          <t>PUR +14.5</t>
         </is>
       </c>
       <c r="G76" s="26" t="n">
-        <v>3</v>
+        <v>-14.5</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I76" s="20" t="n">
-        <v>0.6417725157444896</v>
+        <v>0.626725570000096</v>
       </c>
       <c r="J76" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5</v>
       </c>
       <c r="K76" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L76" s="19" t="n">
-        <v>0.09414252318920331</v>
+        <v>0.0940893474354626</v>
       </c>
       <c r="M76" s="19" t="n">
-        <v>0.1904233174293797</v>
+        <v>0.1964760881820016</v>
       </c>
       <c r="N76" s="20" t="n">
-        <v>0.0471</v>
+        <v>0</v>
       </c>
       <c r="O76" s="27" t="n">
         <v>0.839</v>
@@ -6215,12 +6217,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>PUR @ UCLA</t>
+          <t>LSU @ MISS</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 03:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D77" s="22" t="n">
@@ -6228,34 +6230,34 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>PUR +14.5</t>
+          <t>Under 58.5</t>
         </is>
       </c>
       <c r="G77" s="23" t="n">
-        <v>-14.5</v>
+        <v>58.5</v>
       </c>
       <c r="H77" s="13" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>0.626725570000096</v>
+        <v>0.6008800497599214</v>
       </c>
       <c r="J77" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K77" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L77" s="14" t="n">
-        <v>0.0940893474354626</v>
+        <v>0.09391295607894259</v>
       </c>
       <c r="M77" s="14" t="n">
-        <v>0.1964760881820016</v>
+        <v>0.1899781377598444</v>
       </c>
       <c r="N77" s="15" t="n">
         <v>0</v>
@@ -6282,12 +6284,12 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>KENN @ TENN</t>
+          <t>MSST @ SC</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:45</t>
+          <t>2026-09-19 20:15</t>
         </is>
       </c>
       <c r="D78" s="25" t="n">
@@ -6307,22 +6309,22 @@
         <v>59.5</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I78" s="20" t="n">
-        <v>0.6173353421732071</v>
+        <v>0.6264949469239921</v>
       </c>
       <c r="J78" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K78" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L78" s="19" t="n">
-        <v>0.09392335192393866</v>
+        <v>0.09384822250916708</v>
       </c>
       <c r="M78" s="19" t="n">
-        <v>0.1889421404817322</v>
+        <v>0.185865435248985</v>
       </c>
       <c r="N78" s="20" t="n">
         <v>0</v>
@@ -6349,12 +6351,12 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>MSST @ SC</t>
+          <t>WKU @ IU</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 20:15</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D79" s="22" t="n">
@@ -6367,29 +6369,29 @@
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>Under 59.5</t>
+          <t>Under 60.5</t>
         </is>
       </c>
       <c r="G79" s="23" t="n">
-        <v>59.5</v>
+        <v>60.5</v>
       </c>
       <c r="H79" s="13" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I79" s="15" t="n">
-        <v>0.6264949469239921</v>
+        <v>0.6195002215045176</v>
       </c>
       <c r="J79" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K79" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L79" s="14" t="n">
-        <v>0.09384822250916708</v>
+        <v>0.09376764301607408</v>
       </c>
       <c r="M79" s="14" t="n">
-        <v>0.185865435248985</v>
+        <v>0.1826822410540789</v>
       </c>
       <c r="N79" s="15" t="n">
         <v>0</v>
@@ -6416,12 +6418,12 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>WKU @ IU</t>
+          <t>KENN @ TENN</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-19 23:45</t>
         </is>
       </c>
       <c r="D80" s="25" t="n">
@@ -6434,17 +6436,17 @@
       </c>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>Under 60.5</t>
+          <t>Under 59.5</t>
         </is>
       </c>
       <c r="G80" s="26" t="n">
-        <v>60.5</v>
+        <v>59.5</v>
       </c>
       <c r="H80" s="18" t="n">
         <v>-110</v>
       </c>
       <c r="I80" s="20" t="n">
-        <v>0.6195002215045176</v>
+        <v>0.6195002192081915</v>
       </c>
       <c r="J80" s="20" t="n">
         <v>0.5</v>
@@ -6453,10 +6455,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L80" s="19" t="n">
-        <v>0.09376764301607408</v>
+        <v>0.0937676428976935</v>
       </c>
       <c r="M80" s="19" t="n">
-        <v>0.1826822410540789</v>
+        <v>0.1826822366701839</v>
       </c>
       <c r="N80" s="20" t="n">
         <v>0</v>
@@ -6617,12 +6619,12 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>LSU @ MISS</t>
+          <t>FLA @ AUB</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D83" s="22" t="n">
@@ -6630,34 +6632,32 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>Under 59.5</t>
-        </is>
-      </c>
-      <c r="G83" s="23" t="n">
-        <v>59.5</v>
-      </c>
+          <t>AUB ML</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="n"/>
       <c r="H83" s="13" t="n">
-        <v>-118</v>
+        <v>120</v>
       </c>
       <c r="I83" s="15" t="n">
-        <v>0.6346008251653976</v>
+        <v>0.529941702877028</v>
       </c>
       <c r="J83" s="15" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.4365079365079365</v>
       </c>
       <c r="K83" s="15" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="L83" s="14" t="n">
-        <v>0.09340323881448255</v>
+        <v>0.09292540522593648</v>
       </c>
       <c r="M83" s="14" t="n">
-        <v>0.1723981346275989</v>
+        <v>0.1658717463294617</v>
       </c>
       <c r="N83" s="15" t="n">
         <v>0</v>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="Q83" s="12" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>FLA @ AUB</t>
+          <t>JMU @ SDSU</t>
         </is>
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-20 02:00</t>
         </is>
       </c>
       <c r="D84" s="25" t="n">
@@ -6697,32 +6697,34 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>AUB ML</t>
-        </is>
-      </c>
-      <c r="G84" s="26" t="n"/>
+          <t>Over 46.5</t>
+        </is>
+      </c>
+      <c r="G84" s="26" t="n">
+        <v>46.5</v>
+      </c>
       <c r="H84" s="18" t="n">
-        <v>120</v>
+        <v>-110</v>
       </c>
       <c r="I84" s="20" t="n">
-        <v>0.529941702877028</v>
+        <v>0.6061699858137528</v>
       </c>
       <c r="J84" s="20" t="n">
-        <v>0.4365079365079365</v>
+        <v>0.5</v>
       </c>
       <c r="K84" s="20" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L84" s="19" t="n">
-        <v>0.09292540522593648</v>
+        <v>0.09285029600564701</v>
       </c>
       <c r="M84" s="19" t="n">
-        <v>0.1658717463294617</v>
+        <v>0.1572336092808009</v>
       </c>
       <c r="N84" s="20" t="n">
         <v>0</v>
@@ -6749,12 +6751,12 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>JMU @ SDSU</t>
+          <t>SYR @ PITT</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 02:00</t>
+          <t>2026-09-17 23:30</t>
         </is>
       </c>
       <c r="D85" s="22" t="n">
@@ -6762,34 +6764,32 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
-        </is>
-      </c>
-      <c r="G85" s="23" t="n">
-        <v>46.5</v>
-      </c>
+          <t>SYR ML</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="n"/>
       <c r="H85" s="13" t="n">
-        <v>-110</v>
+        <v>300</v>
       </c>
       <c r="I85" s="15" t="n">
-        <v>0.6061699858137528</v>
+        <v>0.2903110599153722</v>
       </c>
       <c r="J85" s="15" t="n">
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
       <c r="K85" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.25</v>
       </c>
       <c r="L85" s="14" t="n">
-        <v>0.09285029600564701</v>
+        <v>0.09272556815502582</v>
       </c>
       <c r="M85" s="14" t="n">
-        <v>0.1572336092808009</v>
+        <v>0.1612442396614888</v>
       </c>
       <c r="N85" s="15" t="n">
         <v>0</v>
@@ -6948,12 +6948,12 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>FLA @ AUB</t>
+          <t>ASU @ KU</t>
         </is>
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D88" s="25" t="n">
@@ -6961,34 +6961,32 @@
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
-          <t>AUB +2.5</t>
-        </is>
-      </c>
-      <c r="G88" s="26" t="n">
-        <v>2.5</v>
-      </c>
+          <t>KU ML</t>
+        </is>
+      </c>
+      <c r="G88" s="26" t="n"/>
       <c r="H88" s="18" t="n">
-        <v>-105</v>
+        <v>185</v>
       </c>
       <c r="I88" s="20" t="n">
-        <v>0.5855778598029548</v>
+        <v>0.4036437946288706</v>
       </c>
       <c r="J88" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.3363518758085381</v>
       </c>
       <c r="K88" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.3508771929824561</v>
       </c>
       <c r="L88" s="19" t="n">
-        <v>0.09204940844258044</v>
+        <v>0.09222558621489992</v>
       </c>
       <c r="M88" s="19" t="n">
-        <v>0.1432710596152929</v>
+        <v>0.1503848146922813</v>
       </c>
       <c r="N88" s="20" t="n">
         <v>0</v>
@@ -7003,7 +7001,7 @@
       </c>
       <c r="Q88" s="17" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -7015,12 +7013,12 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>CCU @ DEL</t>
+          <t>FLA @ AUB</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 15:30</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D89" s="22" t="n">
@@ -7028,34 +7026,34 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>Under 57.5</t>
+          <t>AUB +2.5</t>
         </is>
       </c>
       <c r="G89" s="23" t="n">
-        <v>57.5</v>
+        <v>2.5</v>
       </c>
       <c r="H89" s="13" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="I89" s="15" t="n">
-        <v>0.5975243736282159</v>
+        <v>0.5855778598029548</v>
       </c>
       <c r="J89" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K89" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L89" s="14" t="n">
-        <v>0.09192163064792221</v>
+        <v>0.09204940844258044</v>
       </c>
       <c r="M89" s="14" t="n">
-        <v>0.1407283496538667</v>
+        <v>0.1432710596152929</v>
       </c>
       <c r="N89" s="15" t="n">
         <v>0</v>
@@ -7070,7 +7068,7 @@
       </c>
       <c r="Q89" s="12" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -7082,12 +7080,12 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>UTSA @ TEX</t>
+          <t>CCU @ DEL</t>
         </is>
       </c>
       <c r="C90" s="17" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-19 15:30</t>
         </is>
       </c>
       <c r="D90" s="25" t="n">
@@ -7100,29 +7098,29 @@
       </c>
       <c r="F90" s="17" t="inlineStr">
         <is>
-          <t>Under 58.5</t>
+          <t>Under 57.5</t>
         </is>
       </c>
       <c r="G90" s="26" t="n">
-        <v>58.5</v>
+        <v>57.5</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I90" s="20" t="n">
-        <v>0.6098765949800449</v>
+        <v>0.5975243736282159</v>
       </c>
       <c r="J90" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5</v>
       </c>
       <c r="K90" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L90" s="19" t="n">
-        <v>0.09184645230237359</v>
+        <v>0.09192163064792221</v>
       </c>
       <c r="M90" s="19" t="n">
-        <v>0.140204068875736</v>
+        <v>0.1407283496538667</v>
       </c>
       <c r="N90" s="20" t="n">
         <v>0</v>
@@ -7149,12 +7147,12 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>SYR @ PITT</t>
+          <t>UTSA @ TEX</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>2026-09-17 23:30</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D91" s="22" t="n">
@@ -7162,34 +7160,34 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>SYR +10.5</t>
+          <t>Under 58.5</t>
         </is>
       </c>
       <c r="G91" s="23" t="n">
-        <v>-10.5</v>
+        <v>58.5</v>
       </c>
       <c r="H91" s="13" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I91" s="15" t="n">
-        <v>0.5907172898003605</v>
+        <v>0.6098765949800449</v>
       </c>
       <c r="J91" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K91" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L91" s="14" t="n">
-        <v>0.09170440105581325</v>
+        <v>0.09184645230237359</v>
       </c>
       <c r="M91" s="14" t="n">
-        <v>0.1376777433192129</v>
+        <v>0.140204068875736</v>
       </c>
       <c r="N91" s="15" t="n">
         <v>0</v>
@@ -7204,7 +7202,7 @@
       </c>
       <c r="Q91" s="12" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7348,12 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>UNC @ CLEM</t>
+          <t>SYR @ PITT</t>
         </is>
       </c>
       <c r="C94" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-17 23:30</t>
         </is>
       </c>
       <c r="D94" s="25" t="n">
@@ -7363,34 +7361,34 @@
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F94" s="17" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>SYR +10.5</t>
         </is>
       </c>
       <c r="G94" s="26" t="n">
-        <v>44.5</v>
+        <v>-10.5</v>
       </c>
       <c r="H94" s="18" t="n">
-        <v>-102</v>
+        <v>-115</v>
       </c>
       <c r="I94" s="20" t="n">
-        <v>0.5635012337599586</v>
+        <v>0.5982992849285195</v>
       </c>
       <c r="J94" s="20" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K94" s="20" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L94" s="19" t="n">
-        <v>0.08957667652072997</v>
+        <v>0.08996930636203408</v>
       </c>
       <c r="M94" s="19" t="n">
-        <v>0.1159534237207025</v>
+        <v>0.1185595326924493</v>
       </c>
       <c r="N94" s="20" t="n">
         <v>0</v>
@@ -7405,7 +7403,7 @@
       </c>
       <c r="Q94" s="17" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -7417,7 +7415,7 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>ASU @ KU</t>
+          <t>UNC @ CLEM</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
@@ -7430,32 +7428,34 @@
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>KU ML</t>
-        </is>
-      </c>
-      <c r="G95" s="23" t="n"/>
+          <t>Over 44.5</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="n">
+        <v>44.5</v>
+      </c>
       <c r="H95" s="13" t="n">
-        <v>170</v>
+        <v>-102</v>
       </c>
       <c r="I95" s="15" t="n">
-        <v>0.4131032673244851</v>
+        <v>0.5635012337599586</v>
       </c>
       <c r="J95" s="15" t="n">
-        <v>0.3552708211997671</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K95" s="15" t="n">
-        <v>0.3703703703703703</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L95" s="14" t="n">
-        <v>0.08902237484424491</v>
+        <v>0.08957667652072997</v>
       </c>
       <c r="M95" s="14" t="n">
-        <v>0.1153788217761098</v>
+        <v>0.1159534237207025</v>
       </c>
       <c r="N95" s="15" t="n">
         <v>0</v>
@@ -7482,12 +7482,12 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>STAN @ DUKE</t>
+          <t>ASU @ KU</t>
         </is>
       </c>
       <c r="C96" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D96" s="25" t="n">
@@ -7500,32 +7500,32 @@
       </c>
       <c r="F96" s="17" t="inlineStr">
         <is>
-          <t>STAN +9.5</t>
+          <t>KU +6</t>
         </is>
       </c>
       <c r="G96" s="26" t="n">
-        <v>-9.5</v>
+        <v>6</v>
       </c>
       <c r="H96" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>0.5715225930695444</v>
+        <v>0.5854883267574933</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L96" s="19" t="n">
-        <v>0.08771199459942559</v>
+        <v>0.08879139890596684</v>
       </c>
       <c r="M96" s="19" t="n">
-        <v>0.1007101792450487</v>
+        <v>0.1053772486862944</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>0</v>
+        <v>0.0265</v>
       </c>
       <c r="O96" s="27" t="n">
         <v>0.839</v>
@@ -7549,12 +7549,12 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>ARST @ TCU</t>
+          <t>STAN @ DUKE</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D97" s="22" t="n">
@@ -7562,34 +7562,34 @@
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>Under 55.5</t>
+          <t>STAN +9.5</t>
         </is>
       </c>
       <c r="G97" s="23" t="n">
-        <v>55.5</v>
+        <v>-9.5</v>
       </c>
       <c r="H97" s="13" t="n">
-        <v>-102</v>
+        <v>-108</v>
       </c>
       <c r="I97" s="15" t="n">
-        <v>0.5559939298474784</v>
+        <v>0.5715225930695444</v>
       </c>
       <c r="J97" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K97" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L97" s="14" t="n">
-        <v>0.08755770255786806</v>
+        <v>0.08771199459942559</v>
       </c>
       <c r="M97" s="14" t="n">
-        <v>0.1010860179332416</v>
+        <v>0.1007101792450487</v>
       </c>
       <c r="N97" s="15" t="n">
         <v>0</v>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="Q97" s="12" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -7683,12 +7683,12 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>ASU @ KU</t>
+          <t>UAB @ UL</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D99" s="22" t="n">
@@ -7696,34 +7696,34 @@
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>KU +5.5</t>
+          <t>Under 56.5</t>
         </is>
       </c>
       <c r="G99" s="23" t="n">
-        <v>5.5</v>
+        <v>56.5</v>
       </c>
       <c r="H99" s="13" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I99" s="15" t="n">
-        <v>0.5799110759069217</v>
+        <v>0.5606183235247334</v>
       </c>
       <c r="J99" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K99" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L99" s="14" t="n">
-        <v>0.08457919911805903</v>
+        <v>0.08367486886758746</v>
       </c>
       <c r="M99" s="14" t="n">
-        <v>0.08418157669554915</v>
+        <v>0.07970936382541249</v>
       </c>
       <c r="N99" s="15" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="Q99" s="12" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -7750,12 +7750,12 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>WVU @ UVA</t>
+          <t>ARST @ TCU</t>
         </is>
       </c>
       <c r="C100" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D100" s="25" t="n">
@@ -7768,29 +7768,29 @@
       </c>
       <c r="F100" s="17" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>Under 55.5</t>
         </is>
       </c>
       <c r="G100" s="26" t="n">
-        <v>53.5</v>
+        <v>55.5</v>
       </c>
       <c r="H100" s="18" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>0.5625110917058415</v>
+        <v>0.5646759927056134</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L100" s="19" t="n">
-        <v>0.08450134139163748</v>
+        <v>0.08329254278965623</v>
       </c>
       <c r="M100" s="19" t="n">
-        <v>0.08335469513717619</v>
+        <v>0.07801780425617122</v>
       </c>
       <c r="N100" s="20" t="n">
         <v>0</v>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="Q100" s="17" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -7817,12 +7817,12 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>UAB @ UL</t>
+          <t>EMU @ WIS</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-19 16:30</t>
         </is>
       </c>
       <c r="D101" s="22" t="n">
@@ -7835,29 +7835,29 @@
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>Under 56.5</t>
+          <t>Over 45.5</t>
         </is>
       </c>
       <c r="G101" s="23" t="n">
-        <v>56.5</v>
+        <v>45.5</v>
       </c>
       <c r="H101" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I101" s="15" t="n">
-        <v>0.5606183235247334</v>
+        <v>0.568727561258213</v>
       </c>
       <c r="J101" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K101" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L101" s="14" t="n">
-        <v>0.08367486886758746</v>
+        <v>0.08290217412435039</v>
       </c>
       <c r="M101" s="14" t="n">
-        <v>0.07970936382541249</v>
+        <v>0.07652002666733182</v>
       </c>
       <c r="N101" s="15" t="n">
         <v>0</v>
@@ -7884,12 +7884,12 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>EMU @ WIS</t>
+          <t>UNM @ OU</t>
         </is>
       </c>
       <c r="C102" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:30</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D102" s="25" t="n">
@@ -7902,29 +7902,29 @@
       </c>
       <c r="F102" s="17" t="inlineStr">
         <is>
-          <t>Over 45.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="G102" s="26" t="n">
-        <v>45.5</v>
+        <v>46.5</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I102" s="20" t="n">
-        <v>0.568727561258213</v>
+        <v>0.5757334679148104</v>
       </c>
       <c r="J102" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K102" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L102" s="19" t="n">
-        <v>0.08290217412435039</v>
+        <v>0.08274761209707551</v>
       </c>
       <c r="M102" s="19" t="n">
-        <v>0.07652002666733182</v>
+        <v>0.07637126610160205</v>
       </c>
       <c r="N102" s="20" t="n">
         <v>0</v>
@@ -7951,12 +7951,12 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>UNM @ OU</t>
+          <t>UAB @ UL</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D103" s="22" t="n">
@@ -7964,34 +7964,32 @@
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
-        </is>
-      </c>
-      <c r="G103" s="23" t="n">
-        <v>46.5</v>
-      </c>
+          <t>UAB ML</t>
+        </is>
+      </c>
+      <c r="G103" s="23" t="n"/>
       <c r="H103" s="13" t="n">
-        <v>-115</v>
+        <v>250</v>
       </c>
       <c r="I103" s="15" t="n">
-        <v>0.5757334679148104</v>
+        <v>0.3059736485675911</v>
       </c>
       <c r="J103" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.274247491638796</v>
       </c>
       <c r="K103" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="L103" s="14" t="n">
-        <v>0.08274761209707551</v>
+        <v>0.07970342793993671</v>
       </c>
       <c r="M103" s="14" t="n">
-        <v>0.07637126610160205</v>
+        <v>0.070907769986569</v>
       </c>
       <c r="N103" s="15" t="n">
         <v>0</v>
@@ -8006,7 +8004,7 @@
       </c>
       <c r="Q103" s="12" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -8018,12 +8016,12 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>UAB @ UL</t>
+          <t>FIU @ FAU</t>
         </is>
       </c>
       <c r="C104" s="17" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D104" s="25" t="n">
@@ -8036,27 +8034,27 @@
       </c>
       <c r="F104" s="17" t="inlineStr">
         <is>
-          <t>UAB ML</t>
+          <t>FIU ML</t>
         </is>
       </c>
       <c r="G104" s="26" t="n"/>
       <c r="H104" s="18" t="n">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="I104" s="20" t="n">
-        <v>0.3059736485675911</v>
+        <v>0.3508605516708063</v>
       </c>
       <c r="J104" s="20" t="n">
-        <v>0.274247491638796</v>
+        <v>0.3146067415730336</v>
       </c>
       <c r="K104" s="20" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3278688524590164</v>
       </c>
       <c r="L104" s="19" t="n">
-        <v>0.07970342793993671</v>
+        <v>0.07956992486452395</v>
       </c>
       <c r="M104" s="19" t="n">
-        <v>0.070907769986569</v>
+        <v>0.07012468259595916</v>
       </c>
       <c r="N104" s="20" t="n">
         <v>0</v>
@@ -8071,7 +8069,7 @@
       </c>
       <c r="Q104" s="17" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -8083,12 +8081,12 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>FIU @ FAU</t>
+          <t>UK @ TA&amp;M</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D105" s="22" t="n">
@@ -8096,32 +8094,34 @@
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>FIU ML</t>
-        </is>
-      </c>
-      <c r="G105" s="23" t="n"/>
+          <t>Over 49.5</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="n">
+        <v>49.5</v>
+      </c>
       <c r="H105" s="13" t="n">
-        <v>205</v>
+        <v>-110</v>
       </c>
       <c r="I105" s="15" t="n">
-        <v>0.3508605516708063</v>
+        <v>0.5570690890896691</v>
       </c>
       <c r="J105" s="15" t="n">
-        <v>0.3146067415730336</v>
+        <v>0.5</v>
       </c>
       <c r="K105" s="15" t="n">
-        <v>0.3278688524590164</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L105" s="14" t="n">
-        <v>0.07956992486452395</v>
+        <v>0.07923928370038286</v>
       </c>
       <c r="M105" s="14" t="n">
-        <v>0.07012468259595916</v>
+        <v>0.06349553371664118</v>
       </c>
       <c r="N105" s="15" t="n">
         <v>0</v>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="Q105" s="12" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>UK @ TA&amp;M</t>
+          <t>SMU @ LOU</t>
         </is>
       </c>
       <c r="C106" s="17" t="inlineStr">
@@ -8161,34 +8161,32 @@
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F106" s="17" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
-        </is>
-      </c>
-      <c r="G106" s="26" t="n">
-        <v>49.5</v>
-      </c>
+          <t>LOU ML</t>
+        </is>
+      </c>
+      <c r="G106" s="26" t="n"/>
       <c r="H106" s="18" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I106" s="20" t="n">
-        <v>0.5570690890896691</v>
+        <v>0.5669673572258898</v>
       </c>
       <c r="J106" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K106" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L106" s="19" t="n">
-        <v>0.07923928370038286</v>
+        <v>0.07789591719715193</v>
       </c>
       <c r="M106" s="19" t="n">
-        <v>0.06349553371664118</v>
+        <v>0.05998245046579376</v>
       </c>
       <c r="N106" s="20" t="n">
         <v>0</v>
@@ -8203,7 +8201,7 @@
       </c>
       <c r="Q106" s="17" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -8215,12 +8213,12 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>SMU @ LOU</t>
+          <t>FIU @ FAU</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D107" s="22" t="n">
@@ -8228,35 +8226,37 @@
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>LOU ML</t>
-        </is>
-      </c>
-      <c r="G107" s="23" t="n"/>
+          <t>FIU +7</t>
+        </is>
+      </c>
+      <c r="G107" s="23" t="n">
+        <v>-7</v>
+      </c>
       <c r="H107" s="13" t="n">
-        <v>-115</v>
+        <v>-118</v>
       </c>
       <c r="I107" s="15" t="n">
-        <v>0.5669673572258898</v>
+        <v>0.5718590602560836</v>
       </c>
       <c r="J107" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K107" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L107" s="14" t="n">
-        <v>0.07789591719715193</v>
+        <v>0.07634413092525391</v>
       </c>
       <c r="M107" s="14" t="n">
-        <v>0.05998245046579376</v>
+        <v>0.05369500461115586</v>
       </c>
       <c r="N107" s="15" t="n">
-        <v>0</v>
+        <v>0.0494</v>
       </c>
       <c r="O107" s="24" t="n">
         <v>0.839</v>
@@ -8268,7 +8268,7 @@
       </c>
       <c r="Q107" s="12" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -8280,12 +8280,12 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>MIA @ WAKE</t>
+          <t>WYO @ CMU</t>
         </is>
       </c>
       <c r="C108" s="17" t="inlineStr">
         <is>
-          <t>2026-09-18 23:30</t>
+          <t>2026-09-19 17:00</t>
         </is>
       </c>
       <c r="D108" s="25" t="n">
@@ -8293,34 +8293,32 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F108" s="17" t="inlineStr">
         <is>
-          <t>Under 55.5</t>
-        </is>
-      </c>
-      <c r="G108" s="26" t="n">
-        <v>55.5</v>
-      </c>
+          <t>CMU ML</t>
+        </is>
+      </c>
+      <c r="G108" s="26" t="n"/>
       <c r="H108" s="18" t="n">
-        <v>-110</v>
+        <v>-120</v>
       </c>
       <c r="I108" s="20" t="n">
-        <v>0.5532315828247676</v>
+        <v>0.5759849761160167</v>
       </c>
       <c r="J108" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="K108" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="L108" s="19" t="n">
-        <v>0.07674100634293532</v>
+        <v>0.07585661476708026</v>
       </c>
       <c r="M108" s="19" t="n">
-        <v>0.05616938539273808</v>
+        <v>0.05597245621269753</v>
       </c>
       <c r="N108" s="20" t="n">
         <v>0</v>
@@ -8335,7 +8333,7 @@
       </c>
       <c r="Q108" s="17" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -8347,12 +8345,12 @@
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>FIU @ FAU</t>
+          <t>MIA @ WAKE</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-18 23:30</t>
         </is>
       </c>
       <c r="D109" s="22" t="n">
@@ -8360,37 +8358,37 @@
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>FIU +7</t>
+          <t>Under 55.5</t>
         </is>
       </c>
       <c r="G109" s="23" t="n">
-        <v>-7</v>
+        <v>55.5</v>
       </c>
       <c r="H109" s="13" t="n">
-        <v>-118</v>
+        <v>-112</v>
       </c>
       <c r="I109" s="15" t="n">
-        <v>0.5718590602560836</v>
+        <v>0.5553964598597521</v>
       </c>
       <c r="J109" s="15" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K109" s="15" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L109" s="14" t="n">
-        <v>0.07634413092525391</v>
+        <v>0.07485010906805592</v>
       </c>
       <c r="M109" s="14" t="n">
-        <v>0.05369500461115586</v>
+        <v>0.05128615616310217</v>
       </c>
       <c r="N109" s="15" t="n">
-        <v>0.0494</v>
+        <v>0</v>
       </c>
       <c r="O109" s="24" t="n">
         <v>0.839</v>
@@ -8402,7 +8400,7 @@
       </c>
       <c r="Q109" s="12" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -8414,12 +8412,12 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>WYO @ CMU</t>
+          <t>WVU @ UVA</t>
         </is>
       </c>
       <c r="C110" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 17:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D110" s="25" t="n">
@@ -8427,32 +8425,34 @@
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F110" s="17" t="inlineStr">
         <is>
-          <t>CMU ML</t>
-        </is>
-      </c>
-      <c r="G110" s="26" t="n"/>
+          <t>Under 52.5</t>
+        </is>
+      </c>
+      <c r="G110" s="26" t="n">
+        <v>52.5</v>
+      </c>
       <c r="H110" s="18" t="n">
-        <v>-120</v>
+        <v>-108</v>
       </c>
       <c r="I110" s="20" t="n">
-        <v>0.5759849761160167</v>
+        <v>0.5433307733251187</v>
       </c>
       <c r="J110" s="20" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K110" s="20" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L110" s="19" t="n">
-        <v>0.07585661476708026</v>
+        <v>0.07283150494346662</v>
       </c>
       <c r="M110" s="19" t="n">
-        <v>0.05597245621269753</v>
+        <v>0.04641482270022856</v>
       </c>
       <c r="N110" s="20" t="n">
         <v>0</v>
@@ -8479,12 +8479,12 @@
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>JMU @ SDSU</t>
+          <t>UAB @ UL</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 02:00</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D111" s="22" t="n">
@@ -8492,32 +8492,34 @@
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>SDSU ML</t>
-        </is>
-      </c>
-      <c r="G111" s="23" t="n"/>
+          <t>UAB +7.5</t>
+        </is>
+      </c>
+      <c r="G111" s="23" t="n">
+        <v>-7.5</v>
+      </c>
       <c r="H111" s="13" t="n">
-        <v>-130</v>
+        <v>-110</v>
       </c>
       <c r="I111" s="15" t="n">
-        <v>0.5962475947747694</v>
+        <v>0.5472095939894825</v>
       </c>
       <c r="J111" s="15" t="n">
-        <v>0.5427435387673957</v>
+        <v>0.5</v>
       </c>
       <c r="K111" s="15" t="n">
-        <v>0.5652173913043478</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L111" s="14" t="n">
-        <v>0.07381262445157261</v>
+        <v>0.07210638064482937</v>
       </c>
       <c r="M111" s="14" t="n">
-        <v>0.05489959075536133</v>
+        <v>0.04467286125264858</v>
       </c>
       <c r="N111" s="15" t="n">
         <v>0</v>
@@ -8530,11 +8532,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q111" s="12" t="inlineStr">
-        <is>
-          <t>correlated with a stronger play on the same game</t>
-        </is>
-      </c>
+      <c r="Q111" s="12" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="17" t="inlineStr">
@@ -8544,12 +8542,12 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>UAB @ UL</t>
+          <t>SMU @ LOU</t>
         </is>
       </c>
       <c r="C112" s="17" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D112" s="25" t="n">
@@ -8562,29 +8560,29 @@
       </c>
       <c r="F112" s="17" t="inlineStr">
         <is>
-          <t>UAB +7.5</t>
+          <t>LOU -1.5</t>
         </is>
       </c>
       <c r="G112" s="26" t="n">
-        <v>-7.5</v>
+        <v>-1.5</v>
       </c>
       <c r="H112" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I112" s="20" t="n">
-        <v>0.5472095939894825</v>
+        <v>0.541493713325953</v>
       </c>
       <c r="J112" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K112" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L112" s="19" t="n">
-        <v>0.07210638064482937</v>
+        <v>0.07125732823047302</v>
       </c>
       <c r="M112" s="19" t="n">
-        <v>0.04467286125264858</v>
+        <v>0.04287678122035388</v>
       </c>
       <c r="N112" s="20" t="n">
         <v>0</v>
@@ -8607,12 +8605,12 @@
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>SMU @ LOU</t>
+          <t>AKR @ MINN</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D113" s="22" t="n">
@@ -8620,34 +8618,34 @@
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>LOU -1.5</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="G113" s="23" t="n">
-        <v>-1.5</v>
+        <v>49.5</v>
       </c>
       <c r="H113" s="13" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I113" s="15" t="n">
-        <v>0.541493713325953</v>
+        <v>0.5342290726844449</v>
       </c>
       <c r="J113" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K113" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L113" s="14" t="n">
-        <v>0.07125732823047302</v>
+        <v>0.07111494203374541</v>
       </c>
       <c r="M113" s="14" t="n">
-        <v>0.04287678122035388</v>
+        <v>0.04301866571724955</v>
       </c>
       <c r="N113" s="15" t="n">
         <v>0</v>
@@ -8670,12 +8668,12 @@
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>AKR @ MINN</t>
+          <t>ECU @ ODU</t>
         </is>
       </c>
       <c r="C114" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D114" s="25" t="n">
@@ -8683,37 +8681,37 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F114" s="17" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>ODU -3</t>
         </is>
       </c>
       <c r="G114" s="26" t="n">
-        <v>49.5</v>
+        <v>-3</v>
       </c>
       <c r="H114" s="18" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I114" s="20" t="n">
-        <v>0.5342290726844449</v>
+        <v>0.5412771879339008</v>
       </c>
       <c r="J114" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K114" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L114" s="19" t="n">
-        <v>0.07111494203374541</v>
+        <v>0.07106560418871048</v>
       </c>
       <c r="M114" s="19" t="n">
-        <v>0.04301866571724955</v>
+        <v>0.03992067514679936</v>
       </c>
       <c r="N114" s="20" t="n">
-        <v>0</v>
+        <v>0.0598</v>
       </c>
       <c r="O114" s="27" t="n">
         <v>0.839</v>
@@ -8733,12 +8731,12 @@
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>ECU @ ODU</t>
+          <t>WYO @ CMU</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 17:00</t>
         </is>
       </c>
       <c r="D115" s="22" t="n">
@@ -8751,32 +8749,32 @@
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>ODU -3</t>
+          <t>CMU -1.5</t>
         </is>
       </c>
       <c r="G115" s="23" t="n">
-        <v>-3</v>
+        <v>-1.5</v>
       </c>
       <c r="H115" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I115" s="15" t="n">
-        <v>0.5412771879339008</v>
+        <v>0.5494763879953697</v>
       </c>
       <c r="J115" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K115" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L115" s="14" t="n">
-        <v>0.07106560418871048</v>
+        <v>0.06994614391061148</v>
       </c>
       <c r="M115" s="14" t="n">
-        <v>0.03992067514679936</v>
+        <v>0.04008030584837829</v>
       </c>
       <c r="N115" s="15" t="n">
-        <v>0.0598</v>
+        <v>0</v>
       </c>
       <c r="O115" s="24" t="n">
         <v>0.839</v>
@@ -8796,12 +8794,12 @@
       </c>
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>WYO @ CMU</t>
+          <t>JMU @ SDSU</t>
         </is>
       </c>
       <c r="C116" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 17:00</t>
+          <t>2026-09-20 02:00</t>
         </is>
       </c>
       <c r="D116" s="25" t="n">
@@ -8809,34 +8807,32 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F116" s="17" t="inlineStr">
         <is>
-          <t>CMU -1.5</t>
-        </is>
-      </c>
-      <c r="G116" s="26" t="n">
-        <v>-1.5</v>
-      </c>
+          <t>SDSU ML</t>
+        </is>
+      </c>
+      <c r="G116" s="26" t="n"/>
       <c r="H116" s="18" t="n">
-        <v>-112</v>
+        <v>-135</v>
       </c>
       <c r="I116" s="20" t="n">
-        <v>0.5494763879953697</v>
+        <v>0.6005963827493461</v>
       </c>
       <c r="J116" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.551441114716549</v>
       </c>
       <c r="K116" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.574468085106383</v>
       </c>
       <c r="L116" s="19" t="n">
-        <v>0.06994614391061148</v>
+        <v>0.06977235009208492</v>
       </c>
       <c r="M116" s="19" t="n">
-        <v>0.04008030584837829</v>
+        <v>0.04548259219330619</v>
       </c>
       <c r="N116" s="20" t="n">
         <v>0</v>
@@ -8859,12 +8855,12 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>ECU @ ODU</t>
+          <t>FSU @ ALA</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D117" s="22" t="n">
@@ -8872,32 +8868,34 @@
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>ODU ML</t>
-        </is>
-      </c>
-      <c r="G117" s="23" t="n"/>
+          <t>Over 49.5</t>
+        </is>
+      </c>
+      <c r="G117" s="23" t="n">
+        <v>49.5</v>
+      </c>
       <c r="H117" s="13" t="n">
-        <v>-148</v>
+        <v>-108</v>
       </c>
       <c r="I117" s="15" t="n">
-        <v>0.6220606248236609</v>
+        <v>0.5394353197399611</v>
       </c>
       <c r="J117" s="15" t="n">
-        <v>0.5720596355604638</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K117" s="15" t="n">
-        <v>0.5967741935483871</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L117" s="14" t="n">
-        <v>0.06896271628100531</v>
+        <v>0.06938064358534374</v>
       </c>
       <c r="M117" s="14" t="n">
-        <v>0.04237185781262087</v>
+        <v>0.03891246764733247</v>
       </c>
       <c r="N117" s="15" t="n">
         <v>0</v>
@@ -8920,12 +8918,12 @@
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>COLO @ NU</t>
+          <t>ECU @ ODU</t>
         </is>
       </c>
       <c r="C118" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D118" s="25" t="n">
@@ -8933,40 +8931,38 @@
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F118" s="17" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
-        </is>
-      </c>
-      <c r="G118" s="26" t="n">
-        <v>48.5</v>
-      </c>
+          <t>ODU ML</t>
+        </is>
+      </c>
+      <c r="G118" s="26" t="n"/>
       <c r="H118" s="18" t="n">
-        <v>-115</v>
+        <v>-148</v>
       </c>
       <c r="I118" s="20" t="n">
-        <v>0.554790475724132</v>
+        <v>0.6220606248236609</v>
       </c>
       <c r="J118" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5720596355604638</v>
       </c>
       <c r="K118" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5967741935483871</v>
       </c>
       <c r="L118" s="19" t="n">
-        <v>0.06831400400388417</v>
+        <v>0.06896271628100531</v>
       </c>
       <c r="M118" s="19" t="n">
-        <v>0.03721697635381194</v>
+        <v>0.04237185781262087</v>
       </c>
       <c r="N118" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O118" s="27" t="n">
-        <v>0.725</v>
+        <v>0.839</v>
       </c>
       <c r="P118" s="17" t="inlineStr">
         <is>
@@ -8983,12 +8979,12 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>CONN @ USM</t>
+          <t>COLO @ NU</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D119" s="22" t="n">
@@ -9001,35 +8997,35 @@
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>Under 54.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="G119" s="23" t="n">
-        <v>54.5</v>
+        <v>48.5</v>
       </c>
       <c r="H119" s="13" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I119" s="15" t="n">
-        <v>0.5374812731816272</v>
+        <v>0.554790475724132</v>
       </c>
       <c r="J119" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K119" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L119" s="14" t="n">
-        <v>0.06748471401583311</v>
+        <v>0.06831400400388417</v>
       </c>
       <c r="M119" s="14" t="n">
-        <v>0.0351491187201709</v>
+        <v>0.03721697635381194</v>
       </c>
       <c r="N119" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O119" s="24" t="n">
-        <v>0.839</v>
+        <v>0.725</v>
       </c>
       <c r="P119" s="12" t="inlineStr">
         <is>
@@ -9046,7 +9042,7 @@
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>FLA @ AUB</t>
+          <t>CONN @ USM</t>
         </is>
       </c>
       <c r="C120" s="17" t="inlineStr">
@@ -9064,17 +9060,17 @@
       </c>
       <c r="F120" s="17" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>Under 54.5</t>
         </is>
       </c>
       <c r="G120" s="26" t="n">
-        <v>53.5</v>
+        <v>54.5</v>
       </c>
       <c r="H120" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I120" s="20" t="n">
-        <v>0.5374812644972277</v>
+        <v>0.5374812731816272</v>
       </c>
       <c r="J120" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -9083,10 +9079,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L120" s="19" t="n">
-        <v>0.06748470533650047</v>
+        <v>0.06748471401583311</v>
       </c>
       <c r="M120" s="19" t="n">
-        <v>0.03514910199466081</v>
+        <v>0.0351491187201709</v>
       </c>
       <c r="N120" s="20" t="n">
         <v>0</v>
@@ -9235,12 +9231,12 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>FSU @ ALA</t>
+          <t>FLA @ AUB</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D123" s="22" t="n">
@@ -9253,29 +9249,29 @@
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="G123" s="23" t="n">
-        <v>49.5</v>
+        <v>53.5</v>
       </c>
       <c r="H123" s="13" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I123" s="15" t="n">
-        <v>0.5437650738099299</v>
+        <v>0.5385486876252762</v>
       </c>
       <c r="J123" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4978050921861282</v>
       </c>
       <c r="K123" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L123" s="14" t="n">
-        <v>0.06429106344870614</v>
+        <v>0.06621986905376226</v>
       </c>
       <c r="M123" s="14" t="n">
-        <v>0.02926960399736722</v>
+        <v>0.03720487987090237</v>
       </c>
       <c r="N123" s="15" t="n">
         <v>0</v>
@@ -9487,12 +9483,12 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>GASO @ JVST</t>
+          <t>NDSU @ SAC</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-20 02:30</t>
         </is>
       </c>
       <c r="D127" s="22" t="n">
@@ -9500,40 +9496,40 @@
       </c>
       <c r="E127" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>JVST -3</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="G127" s="23" t="n">
-        <v>-3</v>
+        <v>52.5</v>
       </c>
       <c r="H127" s="13" t="n">
-        <v>-115</v>
+        <v>-118</v>
       </c>
       <c r="I127" s="15" t="n">
-        <v>0.5409038393189131</v>
+        <v>0.5463702688202144</v>
       </c>
       <c r="J127" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K127" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L127" s="14" t="n">
-        <v>0.05233189673175039</v>
+        <v>0.05035104148096504</v>
       </c>
       <c r="M127" s="14" t="n">
-        <v>0.01057632720622837</v>
+        <v>0.009395920362768928</v>
       </c>
       <c r="N127" s="15" t="n">
-        <v>0.0603</v>
+        <v>0</v>
       </c>
       <c r="O127" s="24" t="n">
-        <v>0.839</v>
+        <v>0.926</v>
       </c>
       <c r="P127" s="12" t="inlineStr">
         <is>
@@ -9550,12 +9546,12 @@
       </c>
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>NDSU @ SAC</t>
+          <t>UTEP @ MICH</t>
         </is>
       </c>
       <c r="C128" s="17" t="inlineStr">
         <is>
-          <t>2026-09-20 02:30</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D128" s="25" t="n">
@@ -9568,35 +9564,35 @@
       </c>
       <c r="F128" s="17" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="G128" s="26" t="n">
-        <v>52.5</v>
+        <v>48.5</v>
       </c>
       <c r="H128" s="18" t="n">
-        <v>-118</v>
+        <v>-105</v>
       </c>
       <c r="I128" s="20" t="n">
-        <v>0.5463702688202144</v>
+        <v>0.5164897065922213</v>
       </c>
       <c r="J128" s="20" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K128" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L128" s="19" t="n">
-        <v>0.05035104148096504</v>
+        <v>0.0502020255010589</v>
       </c>
       <c r="M128" s="19" t="n">
-        <v>0.009395920362768928</v>
+        <v>0.008384665251479628</v>
       </c>
       <c r="N128" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O128" s="27" t="n">
-        <v>0.926</v>
+        <v>0.839</v>
       </c>
       <c r="P128" s="17" t="inlineStr">
         <is>
@@ -9613,12 +9609,12 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>UTEP @ MICH</t>
+          <t>OHIO @ USA</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D129" s="22" t="n">
@@ -9626,22 +9622,22 @@
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F129" s="12" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>USA -4.5</t>
         </is>
       </c>
       <c r="G129" s="23" t="n">
-        <v>48.5</v>
+        <v>-4.5</v>
       </c>
       <c r="H129" s="13" t="n">
         <v>-105</v>
       </c>
       <c r="I129" s="15" t="n">
-        <v>0.5164897065922213</v>
+        <v>0.5155053290436606</v>
       </c>
       <c r="J129" s="15" t="n">
         <v>0.4891657638136511</v>
@@ -9650,10 +9646,10 @@
         <v>0.5121951219512195</v>
       </c>
       <c r="L129" s="14" t="n">
-        <v>0.0502020255010589</v>
+        <v>0.04873542224059591</v>
       </c>
       <c r="M129" s="14" t="n">
-        <v>0.008384665251479628</v>
+        <v>0.006462785275718419</v>
       </c>
       <c r="N129" s="15" t="n">
         <v>0</v>
@@ -9676,7 +9672,7 @@
       </c>
       <c r="B130" s="17" t="inlineStr">
         <is>
-          <t>OHIO @ USA</t>
+          <t>GASO @ JVST</t>
         </is>
       </c>
       <c r="C130" s="17" t="inlineStr">
@@ -9694,32 +9690,32 @@
       </c>
       <c r="F130" s="17" t="inlineStr">
         <is>
-          <t>USA -4.5</t>
+          <t>JVST -3</t>
         </is>
       </c>
       <c r="G130" s="26" t="n">
-        <v>-4.5</v>
+        <v>-3</v>
       </c>
       <c r="H130" s="18" t="n">
-        <v>-105</v>
+        <v>-118</v>
       </c>
       <c r="I130" s="20" t="n">
-        <v>0.5155053290436606</v>
+        <v>0.5441687840838737</v>
       </c>
       <c r="J130" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K130" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L130" s="19" t="n">
-        <v>0.04873542224059591</v>
+        <v>0.04721891868696465</v>
       </c>
       <c r="M130" s="19" t="n">
-        <v>0.006462785275718419</v>
+        <v>0.005007445728714528</v>
       </c>
       <c r="N130" s="20" t="n">
-        <v>0</v>
+        <v>0.0603</v>
       </c>
       <c r="O130" s="27" t="n">
         <v>0.839</v>
@@ -10050,12 +10046,12 @@
       </c>
       <c r="B136" s="17" t="inlineStr">
         <is>
-          <t>BUFF @ PSU</t>
+          <t>COLO @ NU</t>
         </is>
       </c>
       <c r="C136" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D136" s="25" t="n">
@@ -10063,40 +10059,38 @@
       </c>
       <c r="E136" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F136" s="17" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
-        </is>
-      </c>
-      <c r="G136" s="26" t="n">
-        <v>48.5</v>
-      </c>
+          <t>NU ML</t>
+        </is>
+      </c>
+      <c r="G136" s="26" t="n"/>
       <c r="H136" s="18" t="n">
-        <v>-108</v>
+        <v>-180</v>
       </c>
       <c r="I136" s="20" t="n">
-        <v>0.5177573952126979</v>
+        <v>0.6428045510260727</v>
       </c>
       <c r="J136" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.6164383561643836</v>
       </c>
       <c r="K136" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="L136" s="19" t="n">
-        <v>0.04155632201891916</v>
+        <v>0.04009834576111896</v>
       </c>
       <c r="M136" s="19" t="n">
-        <v>-0.002837609219989101</v>
+        <v>-8.180951499803246e-05</v>
       </c>
       <c r="N136" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O136" s="27" t="n">
-        <v>0.839</v>
+        <v>0.725</v>
       </c>
       <c r="P136" s="17" t="inlineStr">
         <is>
@@ -10113,12 +10107,12 @@
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>COLO @ NU</t>
+          <t>BUFF @ PSU</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D137" s="22" t="n">
@@ -10126,38 +10120,40 @@
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>NU ML</t>
-        </is>
-      </c>
-      <c r="G137" s="23" t="n"/>
+          <t>Over 48.5</t>
+        </is>
+      </c>
+      <c r="G137" s="23" t="n">
+        <v>48.5</v>
+      </c>
       <c r="H137" s="13" t="n">
-        <v>-180</v>
+        <v>-110</v>
       </c>
       <c r="I137" s="15" t="n">
-        <v>0.6428045510260727</v>
+        <v>0.5199222722476823</v>
       </c>
       <c r="J137" s="15" t="n">
-        <v>0.6164383561643836</v>
+        <v>0.5</v>
       </c>
       <c r="K137" s="15" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L137" s="14" t="n">
-        <v>0.04009834576111896</v>
+        <v>0.03766166193749009</v>
       </c>
       <c r="M137" s="14" t="n">
-        <v>-8.180951499803246e-05</v>
+        <v>-0.007421116618061108</v>
       </c>
       <c r="N137" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O137" s="24" t="n">
-        <v>0.725</v>
+        <v>0.839</v>
       </c>
       <c r="P137" s="12" t="inlineStr">
         <is>
@@ -11052,12 +11048,12 @@
       </c>
       <c r="B152" s="17" t="inlineStr">
         <is>
-          <t>MSU @ ND</t>
+          <t>NCSU @ VAN</t>
         </is>
       </c>
       <c r="C152" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 16:45</t>
         </is>
       </c>
       <c r="D152" s="25" t="n">
@@ -11065,34 +11061,34 @@
       </c>
       <c r="E152" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F152" s="17" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>VAN -3.5</t>
         </is>
       </c>
       <c r="G152" s="26" t="n">
-        <v>52.5</v>
+        <v>-3.5</v>
       </c>
       <c r="H152" s="18" t="n">
-        <v>-118</v>
+        <v>-102</v>
       </c>
       <c r="I152" s="20" t="n">
-        <v>0.5266176939377067</v>
+        <v>0.4919086194809554</v>
       </c>
       <c r="J152" s="20" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K152" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L152" s="19" t="n">
-        <v>0.01767760700769214</v>
+        <v>0.01895499242707</v>
       </c>
       <c r="M152" s="19" t="n">
-        <v>-0.02709612475915202</v>
+        <v>-0.02582802808673523</v>
       </c>
       <c r="N152" s="20" t="n">
         <v>0</v>
@@ -11115,12 +11111,12 @@
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>STAN @ DUKE</t>
+          <t>MSU @ ND</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D153" s="22" t="n">
@@ -11133,29 +11129,29 @@
       </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="G153" s="23" t="n">
-        <v>51.5</v>
+        <v>52.5</v>
       </c>
       <c r="H153" s="13" t="n">
-        <v>-102</v>
+        <v>-118</v>
       </c>
       <c r="I153" s="15" t="n">
-        <v>0.4893224529444102</v>
+        <v>0.5266176939377067</v>
       </c>
       <c r="J153" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K153" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L153" s="14" t="n">
-        <v>0.0137569045525029</v>
+        <v>0.01767760700769214</v>
       </c>
       <c r="M153" s="14" t="n">
-        <v>-0.03094965201205024</v>
+        <v>-0.02709612475915202</v>
       </c>
       <c r="N153" s="15" t="n">
         <v>0</v>
@@ -11201,22 +11197,22 @@
       </c>
       <c r="G154" s="26" t="n"/>
       <c r="H154" s="18" t="n">
-        <v>-175</v>
+        <v>-170</v>
       </c>
       <c r="I154" s="20" t="n">
-        <v>0.6169928872884611</v>
+        <v>0.6142532555304204</v>
       </c>
       <c r="J154" s="20" t="n">
-        <v>0.6092362344582594</v>
+        <v>0.6037569709421778</v>
       </c>
       <c r="K154" s="20" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="L154" s="19" t="n">
-        <v>0.01265608411264996</v>
+        <v>0.01719344752098952</v>
       </c>
       <c r="M154" s="19" t="n">
-        <v>-0.03043974854670395</v>
+        <v>-0.02442130003992038</v>
       </c>
       <c r="N154" s="20" t="n">
         <v>0</v>
@@ -11239,12 +11235,12 @@
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ VAN</t>
+          <t>SYR @ PITT</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 16:45</t>
+          <t>2026-09-17 23:30</t>
         </is>
       </c>
       <c r="D155" s="22" t="n">
@@ -11252,34 +11248,34 @@
       </c>
       <c r="E155" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>VAN -3.5</t>
+          <t>Over 50.5</t>
         </is>
       </c>
       <c r="G155" s="23" t="n">
-        <v>-3.5</v>
+        <v>50.5</v>
       </c>
       <c r="H155" s="13" t="n">
-        <v>-105</v>
+        <v>-118</v>
       </c>
       <c r="I155" s="15" t="n">
-        <v>0.4951735642459161</v>
+        <v>0.5246294116207542</v>
       </c>
       <c r="J155" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K155" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L155" s="14" t="n">
-        <v>0.01221375728161167</v>
+        <v>0.0139414906840648</v>
       </c>
       <c r="M155" s="14" t="n">
-        <v>-0.03323256504368766</v>
+        <v>-0.03076939209047114</v>
       </c>
       <c r="N155" s="15" t="n">
         <v>0</v>
@@ -11302,12 +11298,12 @@
       </c>
       <c r="B156" s="17" t="inlineStr">
         <is>
-          <t>UNT @ TXST</t>
+          <t>STAN @ DUKE</t>
         </is>
       </c>
       <c r="C156" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D156" s="25" t="n">
@@ -11315,32 +11311,34 @@
       </c>
       <c r="E156" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F156" s="17" t="inlineStr">
         <is>
-          <t>TXST ML</t>
-        </is>
-      </c>
-      <c r="G156" s="26" t="n"/>
+          <t>Over 51.5</t>
+        </is>
+      </c>
+      <c r="G156" s="26" t="n">
+        <v>51.5</v>
+      </c>
       <c r="H156" s="18" t="n">
-        <v>-155</v>
+        <v>-102</v>
       </c>
       <c r="I156" s="20" t="n">
-        <v>0.5901397490546068</v>
+        <v>0.4893224529444102</v>
       </c>
       <c r="J156" s="20" t="n">
-        <v>0.5829926410466066</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K156" s="20" t="n">
-        <v>0.6078431372549019</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L156" s="19" t="n">
-        <v>0.01219174459406908</v>
+        <v>0.0137569045525029</v>
       </c>
       <c r="M156" s="19" t="n">
-        <v>-0.02912492897467933</v>
+        <v>-0.03094965201205024</v>
       </c>
       <c r="N156" s="20" t="n">
         <v>0</v>
@@ -11363,7 +11361,7 @@
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>UNC @ CLEM</t>
+          <t>UNT @ TXST</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
@@ -11376,34 +11374,32 @@
       </c>
       <c r="E157" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>UNC +3.5</t>
-        </is>
-      </c>
-      <c r="G157" s="23" t="n">
-        <v>-3.5</v>
-      </c>
+          <t>TXST ML</t>
+        </is>
+      </c>
+      <c r="G157" s="23" t="n"/>
       <c r="H157" s="13" t="n">
-        <v>-115</v>
+        <v>-155</v>
       </c>
       <c r="I157" s="15" t="n">
-        <v>0.5168979298761311</v>
+        <v>0.5901397490546068</v>
       </c>
       <c r="J157" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5829926410466066</v>
       </c>
       <c r="K157" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.6078431372549019</v>
       </c>
       <c r="L157" s="14" t="n">
-        <v>0.01180878843221538</v>
+        <v>0.01219174459406908</v>
       </c>
       <c r="M157" s="14" t="n">
-        <v>-0.03362560936201575</v>
+        <v>-0.02912492897467933</v>
       </c>
       <c r="N157" s="15" t="n">
         <v>0</v>
@@ -11426,12 +11422,12 @@
       </c>
       <c r="B158" s="17" t="inlineStr">
         <is>
-          <t>PUR @ UCLA</t>
+          <t>UNC @ CLEM</t>
         </is>
       </c>
       <c r="C158" s="17" t="inlineStr">
         <is>
-          <t>2026-09-20 03:00</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D158" s="25" t="n">
@@ -11439,34 +11435,34 @@
       </c>
       <c r="E158" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F158" s="17" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>UNC +3.5</t>
         </is>
       </c>
       <c r="G158" s="26" t="n">
-        <v>52.5</v>
+        <v>-3.5</v>
       </c>
       <c r="H158" s="18" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I158" s="20" t="n">
-        <v>0.510144932073888</v>
+        <v>0.5168979298761311</v>
       </c>
       <c r="J158" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K158" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L158" s="19" t="n">
-        <v>0.01147421824891267</v>
+        <v>0.01180878843221538</v>
       </c>
       <c r="M158" s="19" t="n">
-        <v>-0.03436852143156921</v>
+        <v>-0.03362560936201575</v>
       </c>
       <c r="N158" s="20" t="n">
         <v>0</v>
@@ -11489,12 +11485,12 @@
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>SYR @ PITT</t>
+          <t>PUR @ UCLA</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>2026-09-17 23:30</t>
+          <t>2026-09-20 03:00</t>
         </is>
       </c>
       <c r="D159" s="22" t="n">
@@ -11507,29 +11503,29 @@
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="G159" s="23" t="n">
-        <v>51.5</v>
+        <v>52.5</v>
       </c>
       <c r="H159" s="13" t="n">
-        <v>-102</v>
+        <v>-112</v>
       </c>
       <c r="I159" s="15" t="n">
-        <v>0.4873271438797994</v>
+        <v>0.510144932073888</v>
       </c>
       <c r="J159" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K159" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L159" s="14" t="n">
-        <v>0.009686323683237564</v>
+        <v>0.01147421824891267</v>
       </c>
       <c r="M159" s="14" t="n">
-        <v>-0.03490114643412279</v>
+        <v>-0.03436852143156921</v>
       </c>
       <c r="N159" s="15" t="n">
         <v>0</v>
@@ -12552,12 +12548,12 @@
       </c>
       <c r="B176" s="17" t="inlineStr">
         <is>
-          <t>SYR @ PITT</t>
+          <t>PUR @ UCLA</t>
         </is>
       </c>
       <c r="C176" s="17" t="inlineStr">
         <is>
-          <t>2026-09-17 23:30</t>
+          <t>2026-09-20 03:00</t>
         </is>
       </c>
       <c r="D176" s="25" t="n">
@@ -12570,29 +12566,29 @@
       </c>
       <c r="F176" s="17" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="G176" s="26" t="n">
-        <v>51.5</v>
+        <v>52.5</v>
       </c>
       <c r="H176" s="18" t="n">
-        <v>-118</v>
+        <v>-108</v>
       </c>
       <c r="I176" s="20" t="n">
-        <v>0.5126728561202006</v>
+        <v>0.489855067926112</v>
       </c>
       <c r="J176" s="20" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K176" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L176" s="19" t="n">
-        <v>-0.009040199208922843</v>
+        <v>-0.01167266990722887</v>
       </c>
       <c r="M176" s="19" t="n">
-        <v>-0.05285862174403611</v>
+        <v>-0.05657542473489541</v>
       </c>
       <c r="N176" s="20" t="n">
         <v>0</v>
@@ -12615,12 +12611,12 @@
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t>PUR @ UCLA</t>
+          <t>UNC @ CLEM</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 03:00</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D177" s="22" t="n">
@@ -12628,34 +12624,34 @@
       </c>
       <c r="E177" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F177" s="12" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>CLEM -3.5</t>
         </is>
       </c>
       <c r="G177" s="23" t="n">
-        <v>52.5</v>
+        <v>-3.5</v>
       </c>
       <c r="H177" s="13" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I177" s="15" t="n">
-        <v>0.489855067926112</v>
+        <v>0.4831020701238688</v>
       </c>
       <c r="J177" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K177" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L177" s="14" t="n">
-        <v>-0.01167266990722887</v>
+        <v>-0.01232611359603768</v>
       </c>
       <c r="M177" s="14" t="n">
-        <v>-0.05657542473489541</v>
+        <v>-0.05680072023435145</v>
       </c>
       <c r="N177" s="15" t="n">
         <v>0</v>
@@ -12678,12 +12674,12 @@
       </c>
       <c r="B178" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ VAN</t>
+          <t>STAN @ DUKE</t>
         </is>
       </c>
       <c r="C178" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:45</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D178" s="25" t="n">
@@ -12691,34 +12687,34 @@
       </c>
       <c r="E178" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F178" s="17" t="inlineStr">
         <is>
-          <t>NCSU +3.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G178" s="26" t="n">
-        <v>-3.5</v>
+        <v>51.5</v>
       </c>
       <c r="H178" s="18" t="n">
-        <v>-115</v>
+        <v>-118</v>
       </c>
       <c r="I178" s="20" t="n">
-        <v>0.5048264357540839</v>
+        <v>0.5106775470555898</v>
       </c>
       <c r="J178" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K178" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L178" s="19" t="n">
-        <v>-0.01170104801794024</v>
+        <v>-0.01284516826271762</v>
       </c>
       <c r="M178" s="19" t="n">
-        <v>-0.05619405489453877</v>
+        <v>-0.05654487069391045</v>
       </c>
       <c r="N178" s="20" t="n">
         <v>0</v>
@@ -12741,12 +12737,12 @@
       </c>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t>UNC @ CLEM</t>
+          <t>CCU @ DEL</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 15:30</t>
         </is>
       </c>
       <c r="D179" s="22" t="n">
@@ -12754,34 +12750,32 @@
       </c>
       <c r="E179" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F179" s="12" t="inlineStr">
         <is>
-          <t>CLEM -3.5</t>
-        </is>
-      </c>
-      <c r="G179" s="23" t="n">
-        <v>-3.5</v>
-      </c>
+          <t>DEL ML</t>
+        </is>
+      </c>
+      <c r="G179" s="23" t="n"/>
       <c r="H179" s="13" t="n">
-        <v>-105</v>
+        <v>-218</v>
       </c>
       <c r="I179" s="15" t="n">
-        <v>0.4831020701238688</v>
+        <v>0.6488902362061244</v>
       </c>
       <c r="J179" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.6574752261956054</v>
       </c>
       <c r="K179" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.6855345911949685</v>
       </c>
       <c r="L179" s="14" t="n">
-        <v>-0.01232611359603768</v>
+        <v>-0.0129759009596392</v>
       </c>
       <c r="M179" s="14" t="n">
-        <v>-0.05680072023435145</v>
+        <v>-0.05345369213969009</v>
       </c>
       <c r="N179" s="15" t="n">
         <v>0</v>
@@ -12804,12 +12798,12 @@
       </c>
       <c r="B180" s="17" t="inlineStr">
         <is>
-          <t>STAN @ DUKE</t>
+          <t>SYR @ PITT</t>
         </is>
       </c>
       <c r="C180" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-17 23:30</t>
         </is>
       </c>
       <c r="D180" s="25" t="n">
@@ -12822,29 +12816,29 @@
       </c>
       <c r="F180" s="17" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Under 50.5</t>
         </is>
       </c>
       <c r="G180" s="26" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="H180" s="18" t="n">
-        <v>-118</v>
+        <v>-102</v>
       </c>
       <c r="I180" s="20" t="n">
-        <v>0.5106775470555898</v>
+        <v>0.4753705883792458</v>
       </c>
       <c r="J180" s="20" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K180" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L180" s="19" t="n">
-        <v>-0.01284516826271762</v>
+        <v>-0.01492861240241163</v>
       </c>
       <c r="M180" s="19" t="n">
-        <v>-0.05654487069391045</v>
+        <v>-0.05857981517051314</v>
       </c>
       <c r="N180" s="20" t="n">
         <v>0</v>
@@ -12867,12 +12861,12 @@
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t>CCU @ DEL</t>
+          <t>UNT @ TXST</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 15:30</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D181" s="22" t="n">
@@ -12885,27 +12879,27 @@
       </c>
       <c r="F181" s="12" t="inlineStr">
         <is>
-          <t>DEL ML</t>
+          <t>UNT ML</t>
         </is>
       </c>
       <c r="G181" s="23" t="n"/>
       <c r="H181" s="13" t="n">
-        <v>-218</v>
+        <v>130</v>
       </c>
       <c r="I181" s="15" t="n">
-        <v>0.6488902362061244</v>
+        <v>0.4098602509453932</v>
       </c>
       <c r="J181" s="15" t="n">
-        <v>0.6574752261956054</v>
+        <v>0.4170073589533933</v>
       </c>
       <c r="K181" s="15" t="n">
-        <v>0.6855345911949685</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="L181" s="14" t="n">
-        <v>-0.0129759009596392</v>
+        <v>-0.01695548674894086</v>
       </c>
       <c r="M181" s="14" t="n">
-        <v>-0.05345369213969009</v>
+        <v>-0.0573214228255956</v>
       </c>
       <c r="N181" s="15" t="n">
         <v>0</v>
@@ -12928,12 +12922,12 @@
       </c>
       <c r="B182" s="17" t="inlineStr">
         <is>
-          <t>UNT @ TXST</t>
+          <t>NCSU @ VAN</t>
         </is>
       </c>
       <c r="C182" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 16:45</t>
         </is>
       </c>
       <c r="D182" s="25" t="n">
@@ -12941,32 +12935,34 @@
       </c>
       <c r="E182" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F182" s="17" t="inlineStr">
         <is>
-          <t>UNT ML</t>
-        </is>
-      </c>
-      <c r="G182" s="26" t="n"/>
+          <t>NCSU +3.5</t>
+        </is>
+      </c>
+      <c r="G182" s="26" t="n">
+        <v>-3.5</v>
+      </c>
       <c r="H182" s="18" t="n">
-        <v>130</v>
+        <v>-118</v>
       </c>
       <c r="I182" s="20" t="n">
-        <v>0.4098602509453932</v>
+        <v>0.5080913805190446</v>
       </c>
       <c r="J182" s="20" t="n">
-        <v>0.4170073589533933</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K182" s="20" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L182" s="19" t="n">
-        <v>-0.01695548674894086</v>
+        <v>-0.01771338763472689</v>
       </c>
       <c r="M182" s="19" t="n">
-        <v>-0.0573214228255956</v>
+        <v>-0.0613227037868499</v>
       </c>
       <c r="N182" s="20" t="n">
         <v>0</v>
@@ -13241,12 +13237,12 @@
       </c>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ VAN</t>
+          <t>TEM @ TOL</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 16:45</t>
+          <t>2026-09-19 19:00</t>
         </is>
       </c>
       <c r="D187" s="22" t="n">
@@ -13254,32 +13250,34 @@
       </c>
       <c r="E187" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F187" s="12" t="inlineStr">
         <is>
-          <t>NCSU ML</t>
-        </is>
-      </c>
-      <c r="G187" s="23" t="n"/>
+          <t>TEM +5.5</t>
+        </is>
+      </c>
+      <c r="G187" s="23" t="n">
+        <v>-5.5</v>
+      </c>
       <c r="H187" s="13" t="n">
-        <v>145</v>
+        <v>-110</v>
       </c>
       <c r="I187" s="15" t="n">
-        <v>0.3830071127115389</v>
+        <v>0.4869345497538249</v>
       </c>
       <c r="J187" s="15" t="n">
-        <v>0.3907637655417407</v>
+        <v>0.5</v>
       </c>
       <c r="K187" s="15" t="n">
-        <v>0.4081632653061225</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L187" s="14" t="n">
-        <v>-0.01956606076761507</v>
+        <v>-0.02549123803810194</v>
       </c>
       <c r="M187" s="14" t="n">
-        <v>-0.06163257385672971</v>
+        <v>-0.0703976777426979</v>
       </c>
       <c r="N187" s="15" t="n">
         <v>0</v>
@@ -13302,12 +13300,12 @@
       </c>
       <c r="B188" s="17" t="inlineStr">
         <is>
-          <t>TEM @ TOL</t>
+          <t>MSST @ SC</t>
         </is>
       </c>
       <c r="C188" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 19:00</t>
+          <t>2026-09-19 20:15</t>
         </is>
       </c>
       <c r="D188" s="25" t="n">
@@ -13320,32 +13318,32 @@
       </c>
       <c r="F188" s="17" t="inlineStr">
         <is>
-          <t>TEM +5.5</t>
+          <t>SC -4</t>
         </is>
       </c>
       <c r="G188" s="26" t="n">
-        <v>-5.5</v>
+        <v>-4</v>
       </c>
       <c r="H188" s="18" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="I188" s="20" t="n">
-        <v>0.4869345497538249</v>
+        <v>0.4763052717883661</v>
       </c>
       <c r="J188" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K188" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L188" s="19" t="n">
-        <v>-0.02549123803810194</v>
+        <v>-0.02563943015515805</v>
       </c>
       <c r="M188" s="19" t="n">
-        <v>-0.0703976777426979</v>
+        <v>-0.06788445525469856</v>
       </c>
       <c r="N188" s="20" t="n">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
       <c r="O188" s="27" t="n">
         <v>0.839</v>
@@ -13365,12 +13363,12 @@
       </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t>MSST @ SC</t>
+          <t>NCSU @ VAN</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 20:15</t>
+          <t>2026-09-19 16:45</t>
         </is>
       </c>
       <c r="D189" s="22" t="n">
@@ -13378,37 +13376,35 @@
       </c>
       <c r="E189" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F189" s="12" t="inlineStr">
         <is>
-          <t>SC -4</t>
-        </is>
-      </c>
-      <c r="G189" s="23" t="n">
-        <v>-4</v>
-      </c>
+          <t>NCSU ML</t>
+        </is>
+      </c>
+      <c r="G189" s="23" t="n"/>
       <c r="H189" s="13" t="n">
-        <v>-105</v>
+        <v>142</v>
       </c>
       <c r="I189" s="15" t="n">
-        <v>0.4763052717883661</v>
+        <v>0.3857467444695796</v>
       </c>
       <c r="J189" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.3962430290578221</v>
       </c>
       <c r="K189" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.4132231404958678</v>
       </c>
       <c r="L189" s="14" t="n">
-        <v>-0.02563943015515805</v>
+        <v>-0.02582369133656057</v>
       </c>
       <c r="M189" s="14" t="n">
-        <v>-0.06788445525469856</v>
+        <v>-0.0664928783836175</v>
       </c>
       <c r="N189" s="15" t="n">
-        <v>0.0312</v>
+        <v>0</v>
       </c>
       <c r="O189" s="24" t="n">
         <v>0.839</v>
@@ -13869,12 +13865,12 @@
       </c>
       <c r="B197" s="12" t="inlineStr">
         <is>
-          <t>UAB @ UL</t>
+          <t>BUFF @ PSU</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D197" s="22" t="n">
@@ -13882,32 +13878,34 @@
       </c>
       <c r="E197" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F197" s="12" t="inlineStr">
         <is>
-          <t>UL ML</t>
-        </is>
-      </c>
-      <c r="G197" s="23" t="n"/>
+          <t>Under 48.5</t>
+        </is>
+      </c>
+      <c r="G197" s="23" t="n">
+        <v>48.5</v>
+      </c>
       <c r="H197" s="13" t="n">
-        <v>-310</v>
+        <v>-110</v>
       </c>
       <c r="I197" s="15" t="n">
-        <v>0.6940263514324089</v>
+        <v>0.4800777277523177</v>
       </c>
       <c r="J197" s="15" t="n">
-        <v>0.725752508361204</v>
+        <v>0.5</v>
       </c>
       <c r="K197" s="15" t="n">
-        <v>0.7560975609756098</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L197" s="14" t="n">
-        <v>-0.04087009668957784</v>
+        <v>-0.03766166193749009</v>
       </c>
       <c r="M197" s="14" t="n">
-        <v>-0.08209418036358829</v>
+        <v>-0.08348797429102972</v>
       </c>
       <c r="N197" s="15" t="n">
         <v>0</v>
@@ -13930,12 +13928,12 @@
       </c>
       <c r="B198" s="17" t="inlineStr">
         <is>
-          <t>BUFF @ PSU</t>
+          <t>UAB @ UL</t>
         </is>
       </c>
       <c r="C198" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D198" s="25" t="n">
@@ -13943,34 +13941,32 @@
       </c>
       <c r="E198" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F198" s="17" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
-        </is>
-      </c>
-      <c r="G198" s="26" t="n">
-        <v>48.5</v>
-      </c>
+          <t>UL ML</t>
+        </is>
+      </c>
+      <c r="G198" s="26" t="n"/>
       <c r="H198" s="18" t="n">
-        <v>-112</v>
+        <v>-310</v>
       </c>
       <c r="I198" s="20" t="n">
-        <v>0.4822426047873021</v>
+        <v>0.6940263514324089</v>
       </c>
       <c r="J198" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.725752508361204</v>
       </c>
       <c r="K198" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.7560975609756098</v>
       </c>
       <c r="L198" s="19" t="n">
-        <v>-0.04093543912204675</v>
+        <v>-0.04087009668957784</v>
       </c>
       <c r="M198" s="19" t="n">
-        <v>-0.08718364093832109</v>
+        <v>-0.08209418036358829</v>
       </c>
       <c r="N198" s="20" t="n">
         <v>0</v>
@@ -14369,12 +14365,12 @@
       </c>
       <c r="B205" s="12" t="inlineStr">
         <is>
-          <t>CLT @ APP</t>
+          <t>GASO @ JVST</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D205" s="22" t="n">
@@ -14382,37 +14378,37 @@
       </c>
       <c r="E205" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F205" s="12" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>GASO +3</t>
         </is>
       </c>
       <c r="G205" s="23" t="n">
-        <v>51.5</v>
+        <v>-3</v>
       </c>
       <c r="H205" s="13" t="n">
-        <v>-115</v>
+        <v>-102</v>
       </c>
       <c r="I205" s="15" t="n">
-        <v>0.4815279804051003</v>
+        <v>0.4558312159161263</v>
       </c>
       <c r="J205" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K205" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L205" s="14" t="n">
-        <v>-0.05128201958250349</v>
+        <v>-0.04997083654564062</v>
       </c>
       <c r="M205" s="14" t="n">
-        <v>-0.09975203663394305</v>
+        <v>-0.0914097264071613</v>
       </c>
       <c r="N205" s="15" t="n">
-        <v>0</v>
+        <v>0.0603</v>
       </c>
       <c r="O205" s="24" t="n">
         <v>0.839</v>
@@ -14432,12 +14428,12 @@
       </c>
       <c r="B206" s="17" t="inlineStr">
         <is>
-          <t>NDSU @ SAC</t>
+          <t>CLT @ APP</t>
         </is>
       </c>
       <c r="C206" s="17" t="inlineStr">
         <is>
-          <t>2026-09-20 02:30</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D206" s="25" t="n">
@@ -14450,35 +14446,35 @@
       </c>
       <c r="F206" s="17" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G206" s="26" t="n">
-        <v>52.5</v>
+        <v>51.5</v>
       </c>
       <c r="H206" s="18" t="n">
-        <v>-102</v>
+        <v>-115</v>
       </c>
       <c r="I206" s="20" t="n">
-        <v>0.4536297311797856</v>
+        <v>0.4815279804051003</v>
       </c>
       <c r="J206" s="20" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K206" s="20" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L206" s="19" t="n">
-        <v>-0.05318646381742838</v>
+        <v>-0.05128201958250349</v>
       </c>
       <c r="M206" s="19" t="n">
-        <v>-0.1016352382517972</v>
+        <v>-0.09975203663394305</v>
       </c>
       <c r="N206" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O206" s="27" t="n">
-        <v>0.926</v>
+        <v>0.839</v>
       </c>
       <c r="P206" s="17" t="inlineStr">
         <is>
@@ -14495,12 +14491,12 @@
       </c>
       <c r="B207" s="12" t="inlineStr">
         <is>
-          <t>TEM @ TOL</t>
+          <t>NDSU @ SAC</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:00</t>
+          <t>2026-09-20 02:30</t>
         </is>
       </c>
       <c r="D207" s="22" t="n">
@@ -14508,38 +14504,40 @@
       </c>
       <c r="E207" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F207" s="12" t="inlineStr">
         <is>
-          <t>TEM ML</t>
-        </is>
-      </c>
-      <c r="G207" s="23" t="n"/>
+          <t>Over 52.5</t>
+        </is>
+      </c>
+      <c r="G207" s="23" t="n">
+        <v>52.5</v>
+      </c>
       <c r="H207" s="13" t="n">
-        <v>180</v>
+        <v>-102</v>
       </c>
       <c r="I207" s="15" t="n">
-        <v>0.3218143749297715</v>
+        <v>0.4536297311797856</v>
       </c>
       <c r="J207" s="15" t="n">
-        <v>0.3425247738043947</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K207" s="15" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L207" s="14" t="n">
-        <v>-0.05343618392095172</v>
+        <v>-0.05318646381742838</v>
       </c>
       <c r="M207" s="14" t="n">
-        <v>-0.0989197501966399</v>
+        <v>-0.1016352382517972</v>
       </c>
       <c r="N207" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O207" s="24" t="n">
-        <v>0.839</v>
+        <v>0.926</v>
       </c>
       <c r="P207" s="12" t="inlineStr">
         <is>
@@ -14556,12 +14554,12 @@
       </c>
       <c r="B208" s="17" t="inlineStr">
         <is>
-          <t>GASO @ JVST</t>
+          <t>TEM @ TOL</t>
         </is>
       </c>
       <c r="C208" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 19:00</t>
         </is>
       </c>
       <c r="D208" s="25" t="n">
@@ -14569,37 +14567,35 @@
       </c>
       <c r="E208" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F208" s="17" t="inlineStr">
         <is>
-          <t>GASO +3</t>
-        </is>
-      </c>
-      <c r="G208" s="26" t="n">
-        <v>-3</v>
-      </c>
+          <t>TEM ML</t>
+        </is>
+      </c>
+      <c r="G208" s="26" t="n"/>
       <c r="H208" s="18" t="n">
-        <v>-105</v>
+        <v>180</v>
       </c>
       <c r="I208" s="20" t="n">
-        <v>0.4590961606810869</v>
+        <v>0.3218143749297715</v>
       </c>
       <c r="J208" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.3425247738043947</v>
       </c>
       <c r="K208" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L208" s="19" t="n">
-        <v>-0.05412064092361407</v>
+        <v>-0.05343618392095172</v>
       </c>
       <c r="M208" s="19" t="n">
-        <v>-0.09741813572034697</v>
+        <v>-0.0989197501966399</v>
       </c>
       <c r="N208" s="20" t="n">
-        <v>0.0603</v>
+        <v>0</v>
       </c>
       <c r="O208" s="27" t="n">
         <v>0.839</v>
@@ -14680,12 +14676,12 @@
       </c>
       <c r="B210" s="17" t="inlineStr">
         <is>
-          <t>M-OH @ CIN</t>
+          <t>SYR @ PITT</t>
         </is>
       </c>
       <c r="C210" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-17 23:30</t>
         </is>
       </c>
       <c r="D210" s="25" t="n">
@@ -14693,34 +14689,32 @@
       </c>
       <c r="E210" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F210" s="17" t="inlineStr">
         <is>
-          <t>Under 50.5</t>
-        </is>
-      </c>
-      <c r="G210" s="26" t="n">
-        <v>50.5</v>
-      </c>
+          <t>PITT ML</t>
+        </is>
+      </c>
+      <c r="G210" s="26" t="n"/>
       <c r="H210" s="18" t="n">
-        <v>-102</v>
+        <v>-380</v>
       </c>
       <c r="I210" s="20" t="n">
-        <v>0.4497177517892554</v>
+        <v>0.7096889400846278</v>
       </c>
       <c r="J210" s="20" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.7600000000000001</v>
       </c>
       <c r="K210" s="20" t="n">
-        <v>0.504950495049505</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="L210" s="19" t="n">
-        <v>-0.0584853695896224</v>
+        <v>-0.0572233653165885</v>
       </c>
       <c r="M210" s="19" t="n">
-        <v>-0.1093824915546118</v>
+        <v>-0.1035508125246807</v>
       </c>
       <c r="N210" s="20" t="n">
         <v>0</v>
@@ -14743,12 +14737,12 @@
       </c>
       <c r="B211" s="12" t="inlineStr">
         <is>
-          <t>COLO @ NU</t>
+          <t>M-OH @ CIN</t>
         </is>
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D211" s="22" t="n">
@@ -14756,38 +14750,40 @@
       </c>
       <c r="E211" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F211" s="12" t="inlineStr">
         <is>
-          <t>COLO ML</t>
-        </is>
-      </c>
-      <c r="G211" s="23" t="n"/>
+          <t>Under 50.5</t>
+        </is>
+      </c>
+      <c r="G211" s="23" t="n">
+        <v>50.5</v>
+      </c>
       <c r="H211" s="13" t="n">
-        <v>150</v>
+        <v>-102</v>
       </c>
       <c r="I211" s="15" t="n">
-        <v>0.3571954489739273</v>
+        <v>0.4497177517892554</v>
       </c>
       <c r="J211" s="15" t="n">
-        <v>0.3835616438356164</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K211" s="15" t="n">
-        <v>0.4</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L211" s="14" t="n">
-        <v>-0.05881679195126074</v>
+        <v>-0.0584853695896224</v>
       </c>
       <c r="M211" s="14" t="n">
-        <v>-0.1070113775651818</v>
+        <v>-0.1093824915546118</v>
       </c>
       <c r="N211" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O211" s="24" t="n">
-        <v>0.725</v>
+        <v>0.839</v>
       </c>
       <c r="P211" s="12" t="inlineStr">
         <is>
@@ -14804,12 +14800,12 @@
       </c>
       <c r="B212" s="17" t="inlineStr">
         <is>
-          <t>GASO @ JVST</t>
+          <t>COLO @ NU</t>
         </is>
       </c>
       <c r="C212" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D212" s="25" t="n">
@@ -14822,33 +14818,33 @@
       </c>
       <c r="F212" s="17" t="inlineStr">
         <is>
-          <t>GASO ML</t>
+          <t>COLO ML</t>
         </is>
       </c>
       <c r="G212" s="26" t="n"/>
       <c r="H212" s="18" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="I212" s="20" t="n">
-        <v>0.3711573324871098</v>
+        <v>0.3571954489739273</v>
       </c>
       <c r="J212" s="20" t="n">
-        <v>0.4003612281757977</v>
+        <v>0.3835616438356164</v>
       </c>
       <c r="K212" s="20" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="L212" s="19" t="n">
-        <v>-0.06133826608661176</v>
+        <v>-0.05881679195126074</v>
       </c>
       <c r="M212" s="19" t="n">
-        <v>-0.1092224020309365</v>
+        <v>-0.1070113775651818</v>
       </c>
       <c r="N212" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O212" s="27" t="n">
-        <v>0.839</v>
+        <v>0.725</v>
       </c>
       <c r="P212" s="17" t="inlineStr">
         <is>
@@ -14865,12 +14861,12 @@
       </c>
       <c r="B213" s="12" t="inlineStr">
         <is>
-          <t>ECU @ ODU</t>
+          <t>GASO @ JVST</t>
         </is>
       </c>
       <c r="C213" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D213" s="22" t="n">
@@ -14878,34 +14874,32 @@
       </c>
       <c r="E213" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F213" s="12" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
-        </is>
-      </c>
-      <c r="G213" s="23" t="n">
-        <v>49.5</v>
-      </c>
+          <t>GASO ML</t>
+        </is>
+      </c>
+      <c r="G213" s="23" t="n"/>
       <c r="H213" s="13" t="n">
-        <v>-110</v>
+        <v>140</v>
       </c>
       <c r="I213" s="15" t="n">
-        <v>0.4623117303209874</v>
+        <v>0.3711573324871098</v>
       </c>
       <c r="J213" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4003612281757977</v>
       </c>
       <c r="K213" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="L213" s="14" t="n">
-        <v>-0.0627334237387708</v>
+        <v>-0.06133826608661176</v>
       </c>
       <c r="M213" s="14" t="n">
-        <v>-0.117404878478115</v>
+        <v>-0.1092224020309365</v>
       </c>
       <c r="N213" s="15" t="n">
         <v>0</v>
@@ -14928,12 +14922,12 @@
       </c>
       <c r="B214" s="17" t="inlineStr">
         <is>
-          <t>SYR @ PITT</t>
+          <t>ECU @ ODU</t>
         </is>
       </c>
       <c r="C214" s="17" t="inlineStr">
         <is>
-          <t>2026-09-17 23:30</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D214" s="25" t="n">
@@ -14941,32 +14935,34 @@
       </c>
       <c r="E214" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F214" s="17" t="inlineStr">
         <is>
-          <t>PITT ML</t>
-        </is>
-      </c>
-      <c r="G214" s="26" t="n"/>
+          <t>Under 49.5</t>
+        </is>
+      </c>
+      <c r="G214" s="26" t="n">
+        <v>49.5</v>
+      </c>
       <c r="H214" s="18" t="n">
-        <v>-440</v>
+        <v>-110</v>
       </c>
       <c r="I214" s="20" t="n">
-        <v>0.7206420903269541</v>
+        <v>0.4623117303209874</v>
       </c>
       <c r="J214" s="20" t="n">
-        <v>0.7819063004846527</v>
+        <v>0.5</v>
       </c>
       <c r="K214" s="20" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L214" s="19" t="n">
-        <v>-0.0643770624597795</v>
+        <v>-0.0627334237387708</v>
       </c>
       <c r="M214" s="19" t="n">
-        <v>-0.1155756164169199</v>
+        <v>-0.117404878478115</v>
       </c>
       <c r="N214" s="20" t="n">
         <v>0</v>
@@ -14979,11 +14975,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q214" s="17" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q214" s="17" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="12" t="inlineStr">
@@ -14993,12 +14985,12 @@
       </c>
       <c r="B215" s="12" t="inlineStr">
         <is>
-          <t>FSU @ ALA</t>
+          <t>FLA @ AUB</t>
         </is>
       </c>
       <c r="C215" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D215" s="22" t="n">
@@ -15011,29 +15003,29 @@
       </c>
       <c r="F215" s="12" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G215" s="23" t="n">
-        <v>49.5</v>
+        <v>53.5</v>
       </c>
       <c r="H215" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I215" s="15" t="n">
-        <v>0.4562349261900701</v>
+        <v>0.4614513123747238</v>
       </c>
       <c r="J215" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5021949078138718</v>
       </c>
       <c r="K215" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L215" s="14" t="n">
-        <v>-0.06502430088521186</v>
+        <v>-0.0658501126740325</v>
       </c>
       <c r="M215" s="14" t="n">
-        <v>-0.1213253273376427</v>
+        <v>-0.1190474945573454</v>
       </c>
       <c r="N215" s="15" t="n">
         <v>0</v>
@@ -15180,7 +15172,7 @@
       </c>
       <c r="B218" s="17" t="inlineStr">
         <is>
-          <t>FLA @ AUB</t>
+          <t>CONN @ USM</t>
         </is>
       </c>
       <c r="C218" s="17" t="inlineStr">
@@ -15198,17 +15190,17 @@
       </c>
       <c r="F218" s="17" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>Over 54.5</t>
         </is>
       </c>
       <c r="G218" s="26" t="n">
-        <v>53.5</v>
+        <v>54.5</v>
       </c>
       <c r="H218" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I218" s="20" t="n">
-        <v>0.4625187355027723</v>
+        <v>0.4625187268183728</v>
       </c>
       <c r="J218" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -15217,10 +15209,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L218" s="19" t="n">
-        <v>-0.06675941633376785</v>
+        <v>-0.06675942504984723</v>
       </c>
       <c r="M218" s="19" t="n">
-        <v>-0.1245181077983238</v>
+        <v>-0.1245181242366515</v>
       </c>
       <c r="N218" s="20" t="n">
         <v>0</v>
@@ -15243,12 +15235,12 @@
       </c>
       <c r="B219" s="12" t="inlineStr">
         <is>
-          <t>CONN @ USM</t>
+          <t>PUR @ UCLA</t>
         </is>
       </c>
       <c r="C219" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-20 03:00</t>
         </is>
       </c>
       <c r="D219" s="22" t="n">
@@ -15256,34 +15248,32 @@
       </c>
       <c r="E219" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F219" s="12" t="inlineStr">
         <is>
-          <t>Over 54.5</t>
-        </is>
-      </c>
-      <c r="G219" s="23" t="n">
-        <v>54.5</v>
-      </c>
+          <t>UCLA ML</t>
+        </is>
+      </c>
+      <c r="G219" s="23" t="n"/>
       <c r="H219" s="13" t="n">
-        <v>-112</v>
+        <v>-700</v>
       </c>
       <c r="I219" s="15" t="n">
-        <v>0.4625187268183728</v>
+        <v>0.7691944299789779</v>
       </c>
       <c r="J219" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.84</v>
       </c>
       <c r="K219" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.875</v>
       </c>
       <c r="L219" s="14" t="n">
-        <v>-0.06675942504984723</v>
+        <v>-0.06745489826432</v>
       </c>
       <c r="M219" s="14" t="n">
-        <v>-0.1245181242366515</v>
+        <v>-0.1209206514525967</v>
       </c>
       <c r="N219" s="15" t="n">
         <v>0</v>
@@ -15296,7 +15286,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q219" s="12" t="n"/>
+      <c r="Q219" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="17" t="inlineStr">
@@ -15306,12 +15300,12 @@
       </c>
       <c r="B220" s="17" t="inlineStr">
         <is>
-          <t>PUR @ UCLA</t>
+          <t>JMU @ SDSU</t>
         </is>
       </c>
       <c r="C220" s="17" t="inlineStr">
         <is>
-          <t>2026-09-20 03:00</t>
+          <t>2026-09-20 02:00</t>
         </is>
       </c>
       <c r="D220" s="25" t="n">
@@ -15319,32 +15313,34 @@
       </c>
       <c r="E220" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F220" s="17" t="inlineStr">
         <is>
-          <t>UCLA ML</t>
-        </is>
-      </c>
-      <c r="G220" s="26" t="n"/>
+          <t>JMU +2.5</t>
+        </is>
+      </c>
+      <c r="G220" s="26" t="n">
+        <v>-2.5</v>
+      </c>
       <c r="H220" s="18" t="n">
-        <v>-700</v>
+        <v>-108</v>
       </c>
       <c r="I220" s="20" t="n">
-        <v>0.7691944299789779</v>
+        <v>0.4537735800127758</v>
       </c>
       <c r="J220" s="20" t="n">
-        <v>0.84</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K220" s="20" t="n">
-        <v>0.875</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L220" s="19" t="n">
-        <v>-0.06745489826432</v>
+        <v>-0.06757019217948999</v>
       </c>
       <c r="M220" s="19" t="n">
-        <v>-0.1209206514525967</v>
+        <v>-0.1260656977531724</v>
       </c>
       <c r="N220" s="20" t="n">
         <v>0</v>
@@ -15357,11 +15353,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q220" s="17" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q220" s="17" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="12" t="inlineStr">
@@ -15371,12 +15363,12 @@
       </c>
       <c r="B221" s="12" t="inlineStr">
         <is>
-          <t>JMU @ SDSU</t>
+          <t>UK @ TA&amp;M</t>
         </is>
       </c>
       <c r="C221" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 02:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D221" s="22" t="n">
@@ -15384,34 +15376,32 @@
       </c>
       <c r="E221" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F221" s="12" t="inlineStr">
         <is>
-          <t>JMU +2.5</t>
-        </is>
-      </c>
-      <c r="G221" s="23" t="n">
-        <v>-2.5</v>
-      </c>
+          <t>TA&amp;M ML</t>
+        </is>
+      </c>
+      <c r="G221" s="23" t="n"/>
       <c r="H221" s="13" t="n">
-        <v>-108</v>
+        <v>-850</v>
       </c>
       <c r="I221" s="15" t="n">
-        <v>0.4537735800127758</v>
+        <v>0.7840769193671434</v>
       </c>
       <c r="J221" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.8579439252336449</v>
       </c>
       <c r="K221" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="L221" s="14" t="n">
-        <v>-0.06757019217948999</v>
+        <v>-0.06833802271869539</v>
       </c>
       <c r="M221" s="14" t="n">
-        <v>-0.1260656977531724</v>
+        <v>-0.1236787371778986</v>
       </c>
       <c r="N221" s="15" t="n">
         <v>0</v>
@@ -15424,7 +15414,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q221" s="12" t="n"/>
+      <c r="Q221" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="17" t="inlineStr">
@@ -15434,7 +15428,7 @@
       </c>
       <c r="B222" s="17" t="inlineStr">
         <is>
-          <t>UK @ TA&amp;M</t>
+          <t>FSU @ ALA</t>
         </is>
       </c>
       <c r="C222" s="17" t="inlineStr">
@@ -15447,32 +15441,34 @@
       </c>
       <c r="E222" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F222" s="17" t="inlineStr">
         <is>
-          <t>TA&amp;M ML</t>
-        </is>
-      </c>
-      <c r="G222" s="26" t="n"/>
+          <t>Under 49.5</t>
+        </is>
+      </c>
+      <c r="G222" s="26" t="n">
+        <v>49.5</v>
+      </c>
       <c r="H222" s="18" t="n">
-        <v>-850</v>
+        <v>-112</v>
       </c>
       <c r="I222" s="20" t="n">
-        <v>0.7840769193671434</v>
+        <v>0.4605646802600389</v>
       </c>
       <c r="J222" s="20" t="n">
-        <v>0.8579439252336449</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K222" s="20" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L222" s="19" t="n">
-        <v>-0.06833802271869539</v>
+        <v>-0.06866493014955929</v>
       </c>
       <c r="M222" s="19" t="n">
-        <v>-0.1236787371778986</v>
+        <v>-0.1282168552220692</v>
       </c>
       <c r="N222" s="20" t="n">
         <v>0</v>
@@ -15485,11 +15481,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q222" s="17" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q222" s="17" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="12" t="inlineStr">
@@ -15562,12 +15554,12 @@
       </c>
       <c r="B224" s="17" t="inlineStr">
         <is>
-          <t>ASU @ KU</t>
+          <t>COLO @ NU</t>
         </is>
       </c>
       <c r="C224" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D224" s="25" t="n">
@@ -15575,38 +15567,40 @@
       </c>
       <c r="E224" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F224" s="17" t="inlineStr">
         <is>
-          <t>ASU ML</t>
-        </is>
-      </c>
-      <c r="G224" s="26" t="n"/>
+          <t>Under 48.5</t>
+        </is>
+      </c>
+      <c r="G224" s="26" t="n">
+        <v>48.5</v>
+      </c>
       <c r="H224" s="18" t="n">
-        <v>-205</v>
+        <v>-105</v>
       </c>
       <c r="I224" s="20" t="n">
-        <v>0.5868967326755149</v>
+        <v>0.445209524275868</v>
       </c>
       <c r="J224" s="20" t="n">
-        <v>0.6447291788002329</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K224" s="20" t="n">
-        <v>0.6721311475409836</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L224" s="19" t="n">
-        <v>-0.07002949419066838</v>
+        <v>-0.07010210931374714</v>
       </c>
       <c r="M224" s="19" t="n">
-        <v>-0.1268121782144779</v>
+        <v>-0.1307814049852101</v>
       </c>
       <c r="N224" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O224" s="27" t="n">
-        <v>0.839</v>
+        <v>0.725</v>
       </c>
       <c r="P224" s="17" t="inlineStr">
         <is>
@@ -15623,12 +15617,12 @@
       </c>
       <c r="B225" s="12" t="inlineStr">
         <is>
-          <t>COLO @ NU</t>
+          <t>ECU @ ODU</t>
         </is>
       </c>
       <c r="C225" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D225" s="22" t="n">
@@ -15636,40 +15630,40 @@
       </c>
       <c r="E225" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F225" s="12" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>ECU +3</t>
         </is>
       </c>
       <c r="G225" s="23" t="n">
-        <v>48.5</v>
+        <v>-3</v>
       </c>
       <c r="H225" s="13" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I225" s="15" t="n">
-        <v>0.445209524275868</v>
+        <v>0.4587228120660992</v>
       </c>
       <c r="J225" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K225" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L225" s="14" t="n">
-        <v>-0.07010210931374714</v>
+        <v>-0.07036112565367562</v>
       </c>
       <c r="M225" s="14" t="n">
-        <v>-0.1307814049852101</v>
+        <v>-0.1238273943235371</v>
       </c>
       <c r="N225" s="15" t="n">
-        <v>0</v>
+        <v>0.0598</v>
       </c>
       <c r="O225" s="24" t="n">
-        <v>0.725</v>
+        <v>0.839</v>
       </c>
       <c r="P225" s="12" t="inlineStr">
         <is>
@@ -15686,12 +15680,12 @@
       </c>
       <c r="B226" s="17" t="inlineStr">
         <is>
-          <t>ECU @ ODU</t>
+          <t>SMU @ LOU</t>
         </is>
       </c>
       <c r="C226" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D226" s="25" t="n">
@@ -15704,17 +15698,17 @@
       </c>
       <c r="F226" s="17" t="inlineStr">
         <is>
-          <t>ECU +3</t>
+          <t>SMU +1.5</t>
         </is>
       </c>
       <c r="G226" s="26" t="n">
-        <v>-3</v>
+        <v>-1.5</v>
       </c>
       <c r="H226" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I226" s="20" t="n">
-        <v>0.4587228120660992</v>
+        <v>0.458506286674047</v>
       </c>
       <c r="J226" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -15723,13 +15717,13 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L226" s="19" t="n">
-        <v>-0.07036112565367562</v>
+        <v>-0.07055429896792037</v>
       </c>
       <c r="M226" s="19" t="n">
-        <v>-0.1238273943235371</v>
+        <v>-0.1321131002241253</v>
       </c>
       <c r="N226" s="20" t="n">
-        <v>0.0598</v>
+        <v>0</v>
       </c>
       <c r="O226" s="27" t="n">
         <v>0.839</v>
@@ -15749,12 +15743,12 @@
       </c>
       <c r="B227" s="12" t="inlineStr">
         <is>
-          <t>SMU @ LOU</t>
+          <t>WYO @ CMU</t>
         </is>
       </c>
       <c r="C227" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 17:00</t>
         </is>
       </c>
       <c r="D227" s="22" t="n">
@@ -15767,29 +15761,29 @@
       </c>
       <c r="F227" s="12" t="inlineStr">
         <is>
-          <t>SMU +1.5</t>
+          <t>WYO +1.5</t>
         </is>
       </c>
       <c r="G227" s="23" t="n">
         <v>-1.5</v>
       </c>
       <c r="H227" s="13" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I227" s="15" t="n">
-        <v>0.458506286674047</v>
+        <v>0.4505236120046303</v>
       </c>
       <c r="J227" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K227" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L227" s="14" t="n">
-        <v>-0.07055429896792037</v>
+        <v>-0.07065361651501766</v>
       </c>
       <c r="M227" s="14" t="n">
-        <v>-0.1321131002241253</v>
+        <v>-0.1323248953984897</v>
       </c>
       <c r="N227" s="15" t="n">
         <v>0</v>
@@ -15812,12 +15806,12 @@
       </c>
       <c r="B228" s="17" t="inlineStr">
         <is>
-          <t>WYO @ CMU</t>
+          <t>CLT @ APP</t>
         </is>
       </c>
       <c r="C228" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 17:00</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D228" s="25" t="n">
@@ -15825,34 +15819,32 @@
       </c>
       <c r="E228" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F228" s="17" t="inlineStr">
         <is>
-          <t>WYO +1.5</t>
-        </is>
-      </c>
-      <c r="G228" s="26" t="n">
-        <v>-1.5</v>
-      </c>
+          <t>APP ML</t>
+        </is>
+      </c>
+      <c r="G228" s="26" t="n"/>
       <c r="H228" s="18" t="n">
-        <v>-108</v>
+        <v>-1050</v>
       </c>
       <c r="I228" s="20" t="n">
-        <v>0.4505236120046303</v>
+        <v>0.7946862521841903</v>
       </c>
       <c r="J228" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.8761776581426649</v>
       </c>
       <c r="K228" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.9130434782608695</v>
       </c>
       <c r="L228" s="19" t="n">
-        <v>-0.07065361651501766</v>
+        <v>-0.07150134368871548</v>
       </c>
       <c r="M228" s="19" t="n">
-        <v>-0.1323248953984897</v>
+        <v>-0.1296293428458867</v>
       </c>
       <c r="N228" s="20" t="n">
         <v>0</v>
@@ -15865,7 +15857,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q228" s="17" t="n"/>
+      <c r="Q228" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="12" t="inlineStr">
@@ -15875,12 +15871,12 @@
       </c>
       <c r="B229" s="12" t="inlineStr">
         <is>
-          <t>CLT @ APP</t>
+          <t>UAB @ UL</t>
         </is>
       </c>
       <c r="C229" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D229" s="22" t="n">
@@ -15888,32 +15884,34 @@
       </c>
       <c r="E229" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F229" s="12" t="inlineStr">
         <is>
-          <t>APP ML</t>
-        </is>
-      </c>
-      <c r="G229" s="23" t="n"/>
+          <t>UL -7.5</t>
+        </is>
+      </c>
+      <c r="G229" s="23" t="n">
+        <v>-7.5</v>
+      </c>
       <c r="H229" s="13" t="n">
-        <v>-1050</v>
+        <v>-110</v>
       </c>
       <c r="I229" s="15" t="n">
-        <v>0.7946862521841903</v>
+        <v>0.4527904060105175</v>
       </c>
       <c r="J229" s="15" t="n">
-        <v>0.8761776581426649</v>
+        <v>0.5</v>
       </c>
       <c r="K229" s="15" t="n">
-        <v>0.9130434782608695</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L229" s="14" t="n">
-        <v>-0.07150134368871548</v>
+        <v>-0.07210638064482937</v>
       </c>
       <c r="M229" s="14" t="n">
-        <v>-0.1296293428458867</v>
+        <v>-0.1355819521617394</v>
       </c>
       <c r="N229" s="15" t="n">
         <v>0</v>
@@ -15926,11 +15924,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q229" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q229" s="12" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="17" t="inlineStr">
@@ -15940,12 +15934,12 @@
       </c>
       <c r="B230" s="17" t="inlineStr">
         <is>
-          <t>UAB @ UL</t>
+          <t>WVU @ UVA</t>
         </is>
       </c>
       <c r="C230" s="17" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D230" s="25" t="n">
@@ -15953,34 +15947,34 @@
       </c>
       <c r="E230" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F230" s="17" t="inlineStr">
         <is>
-          <t>UL -7.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="G230" s="26" t="n">
-        <v>-7.5</v>
+        <v>52.5</v>
       </c>
       <c r="H230" s="18" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I230" s="20" t="n">
-        <v>0.4527904060105175</v>
+        <v>0.4566692266748813</v>
       </c>
       <c r="J230" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K230" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L230" s="19" t="n">
-        <v>-0.07210638064482937</v>
+        <v>-0.07214176083278304</v>
       </c>
       <c r="M230" s="19" t="n">
-        <v>-0.1355819521617394</v>
+        <v>-0.1355903923654033</v>
       </c>
       <c r="N230" s="20" t="n">
         <v>0</v>
@@ -16003,12 +15997,12 @@
       </c>
       <c r="B231" s="12" t="inlineStr">
         <is>
-          <t>MIA @ WAKE</t>
+          <t>ASU @ KU</t>
         </is>
       </c>
       <c r="C231" s="12" t="inlineStr">
         <is>
-          <t>2026-09-18 23:30</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D231" s="22" t="n">
@@ -16016,34 +16010,32 @@
       </c>
       <c r="E231" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F231" s="12" t="inlineStr">
         <is>
-          <t>Over 55.5</t>
-        </is>
-      </c>
-      <c r="G231" s="23" t="n">
-        <v>55.5</v>
-      </c>
+          <t>ASU ML</t>
+        </is>
+      </c>
+      <c r="G231" s="23" t="n"/>
       <c r="H231" s="13" t="n">
-        <v>-110</v>
+        <v>-225</v>
       </c>
       <c r="I231" s="15" t="n">
-        <v>0.4467684171752324</v>
+        <v>0.5963562053711293</v>
       </c>
       <c r="J231" s="15" t="n">
-        <v>0.5</v>
+        <v>0.6636481241914618</v>
       </c>
       <c r="K231" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="L231" s="14" t="n">
-        <v>-0.07674100634293535</v>
+        <v>-0.07490329167741676</v>
       </c>
       <c r="M231" s="14" t="n">
-        <v>-0.1470784763018291</v>
+        <v>-0.1385965922417021</v>
       </c>
       <c r="N231" s="15" t="n">
         <v>0</v>
@@ -16066,12 +16058,12 @@
       </c>
       <c r="B232" s="17" t="inlineStr">
         <is>
-          <t>M-OH @ CIN</t>
+          <t>MIA @ WAKE</t>
         </is>
       </c>
       <c r="C232" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-18 23:30</t>
         </is>
       </c>
       <c r="D232" s="25" t="n">
@@ -16079,32 +16071,34 @@
       </c>
       <c r="E232" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F232" s="17" t="inlineStr">
         <is>
-          <t>CIN ML</t>
-        </is>
-      </c>
-      <c r="G232" s="26" t="n"/>
+          <t>Over 55.5</t>
+        </is>
+      </c>
+      <c r="G232" s="26" t="n">
+        <v>55.5</v>
+      </c>
       <c r="H232" s="18" t="n">
-        <v>-675</v>
+        <v>-108</v>
       </c>
       <c r="I232" s="20" t="n">
-        <v>0.7463724280947415</v>
+        <v>0.4446035401402479</v>
       </c>
       <c r="J232" s="20" t="n">
-        <v>0.8370993168681029</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K232" s="20" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L232" s="19" t="n">
-        <v>-0.07739708824387737</v>
+        <v>-0.07551116788271293</v>
       </c>
       <c r="M232" s="19" t="n">
-        <v>-0.1430538788541857</v>
+        <v>-0.1437265152854483</v>
       </c>
       <c r="N232" s="20" t="n">
         <v>0</v>
@@ -16117,11 +16111,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q232" s="17" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q232" s="17" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="12" t="inlineStr">
@@ -16131,12 +16121,12 @@
       </c>
       <c r="B233" s="12" t="inlineStr">
         <is>
-          <t>FIU @ FAU</t>
+          <t>M-OH @ CIN</t>
         </is>
       </c>
       <c r="C233" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D233" s="22" t="n">
@@ -16144,37 +16134,35 @@
       </c>
       <c r="E233" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F233" s="12" t="inlineStr">
         <is>
-          <t>FAU -7</t>
-        </is>
-      </c>
-      <c r="G233" s="23" t="n">
-        <v>-7</v>
-      </c>
+          <t>CIN ML</t>
+        </is>
+      </c>
+      <c r="G233" s="23" t="n"/>
       <c r="H233" s="13" t="n">
-        <v>-102</v>
+        <v>-675</v>
       </c>
       <c r="I233" s="15" t="n">
-        <v>0.4281409397439165</v>
+        <v>0.7463724280947415</v>
       </c>
       <c r="J233" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.8370993168681029</v>
       </c>
       <c r="K233" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.8709677419354839</v>
       </c>
       <c r="L233" s="14" t="n">
-        <v>-0.07886185356718828</v>
+        <v>-0.07739708824387737</v>
       </c>
       <c r="M233" s="14" t="n">
-        <v>-0.1445986566788771</v>
+        <v>-0.1430538788541857</v>
       </c>
       <c r="N233" s="15" t="n">
-        <v>0.0494</v>
+        <v>0</v>
       </c>
       <c r="O233" s="24" t="n">
         <v>0.839</v>
@@ -16184,7 +16172,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q233" s="12" t="n"/>
+      <c r="Q233" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="17" t="inlineStr">
@@ -16194,12 +16186,12 @@
       </c>
       <c r="B234" s="17" t="inlineStr">
         <is>
-          <t>WYO @ CMU</t>
+          <t>JMU @ SDSU</t>
         </is>
       </c>
       <c r="C234" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 17:00</t>
+          <t>2026-09-20 02:00</t>
         </is>
       </c>
       <c r="D234" s="25" t="n">
@@ -16212,27 +16204,27 @@
       </c>
       <c r="F234" s="17" t="inlineStr">
         <is>
-          <t>WYO ML</t>
+          <t>JMU ML</t>
         </is>
       </c>
       <c r="G234" s="26" t="n"/>
       <c r="H234" s="18" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="I234" s="20" t="n">
-        <v>0.4240150238839833</v>
+        <v>0.3994036172506539</v>
       </c>
       <c r="J234" s="20" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.448558885283451</v>
       </c>
       <c r="K234" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4672897196261682</v>
       </c>
       <c r="L234" s="19" t="n">
-        <v>-0.07902033828117308</v>
+        <v>-0.07779725391011615</v>
       </c>
       <c r="M234" s="19" t="n">
-        <v>-0.1519699522320335</v>
+        <v>-0.1452762590836009</v>
       </c>
       <c r="N234" s="20" t="n">
         <v>0</v>
@@ -16255,12 +16247,12 @@
       </c>
       <c r="B235" s="12" t="inlineStr">
         <is>
-          <t>UK @ TA&amp;M</t>
+          <t>FIU @ FAU</t>
         </is>
       </c>
       <c r="C235" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D235" s="22" t="n">
@@ -16268,37 +16260,37 @@
       </c>
       <c r="E235" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F235" s="12" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>FAU -7</t>
         </is>
       </c>
       <c r="G235" s="23" t="n">
-        <v>49.5</v>
+        <v>-7</v>
       </c>
       <c r="H235" s="13" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="I235" s="15" t="n">
-        <v>0.4429309109103309</v>
+        <v>0.4281409397439165</v>
       </c>
       <c r="J235" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K235" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L235" s="14" t="n">
-        <v>-0.07923928370038286</v>
+        <v>-0.07886185356718828</v>
       </c>
       <c r="M235" s="14" t="n">
-        <v>-0.1544046246257319</v>
+        <v>-0.1445986566788771</v>
       </c>
       <c r="N235" s="15" t="n">
-        <v>0</v>
+        <v>0.0494</v>
       </c>
       <c r="O235" s="24" t="n">
         <v>0.839</v>
@@ -16318,12 +16310,12 @@
       </c>
       <c r="B236" s="17" t="inlineStr">
         <is>
-          <t>SMU @ LOU</t>
+          <t>WYO @ CMU</t>
         </is>
       </c>
       <c r="C236" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 17:00</t>
         </is>
       </c>
       <c r="D236" s="25" t="n">
@@ -16336,27 +16328,27 @@
       </c>
       <c r="F236" s="17" t="inlineStr">
         <is>
-          <t>SMU ML</t>
+          <t>WYO ML</t>
         </is>
       </c>
       <c r="G236" s="26" t="n"/>
       <c r="H236" s="18" t="n">
-        <v>-105</v>
+        <v>100</v>
       </c>
       <c r="I236" s="20" t="n">
-        <v>0.4330326427741102</v>
+        <v>0.4240150238839833</v>
       </c>
       <c r="J236" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="K236" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5</v>
       </c>
       <c r="L236" s="19" t="n">
-        <v>-0.07942528273414519</v>
+        <v>-0.07902033828117308</v>
       </c>
       <c r="M236" s="19" t="n">
-        <v>-0.154555316488642</v>
+        <v>-0.1519699522320335</v>
       </c>
       <c r="N236" s="20" t="n">
         <v>0</v>
@@ -16379,12 +16371,12 @@
       </c>
       <c r="B237" s="12" t="inlineStr">
         <is>
-          <t>BALL @ LIB</t>
+          <t>UK @ TA&amp;M</t>
         </is>
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D237" s="22" t="n">
@@ -16392,32 +16384,34 @@
       </c>
       <c r="E237" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F237" s="12" t="inlineStr">
         <is>
-          <t>LIB ML</t>
-        </is>
-      </c>
-      <c r="G237" s="23" t="n"/>
+          <t>Under 49.5</t>
+        </is>
+      </c>
+      <c r="G237" s="23" t="n">
+        <v>49.5</v>
+      </c>
       <c r="H237" s="13" t="n">
-        <v>-650</v>
+        <v>-110</v>
       </c>
       <c r="I237" s="15" t="n">
-        <v>0.7361130634217865</v>
+        <v>0.4429309109103309</v>
       </c>
       <c r="J237" s="15" t="n">
-        <v>0.8316498316498315</v>
+        <v>0.5</v>
       </c>
       <c r="K237" s="15" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L237" s="14" t="n">
-        <v>-0.0794623979688158</v>
+        <v>-0.07923928370038286</v>
       </c>
       <c r="M237" s="14" t="n">
-        <v>-0.1506387729748618</v>
+        <v>-0.1544046246257319</v>
       </c>
       <c r="N237" s="15" t="n">
         <v>0</v>
@@ -16430,11 +16424,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q237" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q237" s="12" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="17" t="inlineStr">
@@ -16444,12 +16434,12 @@
       </c>
       <c r="B238" s="17" t="inlineStr">
         <is>
-          <t>ECU @ ODU</t>
+          <t>SMU @ LOU</t>
         </is>
       </c>
       <c r="C238" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D238" s="25" t="n">
@@ -16462,27 +16452,27 @@
       </c>
       <c r="F238" s="17" t="inlineStr">
         <is>
-          <t>ECU ML</t>
+          <t>SMU ML</t>
         </is>
       </c>
       <c r="G238" s="26" t="n"/>
       <c r="H238" s="18" t="n">
-        <v>124</v>
+        <v>-105</v>
       </c>
       <c r="I238" s="20" t="n">
-        <v>0.3779393751763391</v>
+        <v>0.4330326427741102</v>
       </c>
       <c r="J238" s="20" t="n">
-        <v>0.4279403644395361</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K238" s="20" t="n">
-        <v>0.4464285714285715</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L238" s="19" t="n">
-        <v>-0.08004243138577664</v>
+        <v>-0.07942528273414519</v>
       </c>
       <c r="M238" s="19" t="n">
-        <v>-0.1534157996050003</v>
+        <v>-0.154555316488642</v>
       </c>
       <c r="N238" s="20" t="n">
         <v>0</v>
@@ -16505,12 +16495,12 @@
       </c>
       <c r="B239" s="12" t="inlineStr">
         <is>
-          <t>JMU @ SDSU</t>
+          <t>BALL @ LIB</t>
         </is>
       </c>
       <c r="C239" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 02:00</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D239" s="22" t="n">
@@ -16523,27 +16513,27 @@
       </c>
       <c r="F239" s="12" t="inlineStr">
         <is>
-          <t>JMU ML</t>
+          <t>LIB ML</t>
         </is>
       </c>
       <c r="G239" s="23" t="n"/>
       <c r="H239" s="13" t="n">
-        <v>110</v>
+        <v>-650</v>
       </c>
       <c r="I239" s="15" t="n">
-        <v>0.4037524052252306</v>
+        <v>0.7361130634217865</v>
       </c>
       <c r="J239" s="15" t="n">
-        <v>0.4572564612326044</v>
+        <v>0.8316498316498315</v>
       </c>
       <c r="K239" s="15" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L239" s="14" t="n">
-        <v>-0.08009168176742731</v>
+        <v>-0.0794623979688158</v>
       </c>
       <c r="M239" s="14" t="n">
-        <v>-0.1521199490270158</v>
+        <v>-0.1506387729748618</v>
       </c>
       <c r="N239" s="15" t="n">
         <v>0</v>
@@ -16556,7 +16546,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q239" s="12" t="n"/>
+      <c r="Q239" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="17" t="inlineStr">
@@ -16566,12 +16560,12 @@
       </c>
       <c r="B240" s="17" t="inlineStr">
         <is>
-          <t>BGSU @ ISU</t>
+          <t>ECU @ ODU</t>
         </is>
       </c>
       <c r="C240" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D240" s="25" t="n">
@@ -16584,27 +16578,27 @@
       </c>
       <c r="F240" s="17" t="inlineStr">
         <is>
-          <t>ISU ML</t>
+          <t>ECU ML</t>
         </is>
       </c>
       <c r="G240" s="26" t="n"/>
       <c r="H240" s="18" t="n">
-        <v>-3600</v>
+        <v>124</v>
       </c>
       <c r="I240" s="20" t="n">
-        <v>0.8254237633576067</v>
+        <v>0.3779393751763391</v>
       </c>
       <c r="J240" s="20" t="n">
-        <v>0.9396411092985318</v>
+        <v>0.4279403644395361</v>
       </c>
       <c r="K240" s="20" t="n">
-        <v>0.972972972972973</v>
+        <v>0.4464285714285715</v>
       </c>
       <c r="L240" s="19" t="n">
-        <v>-0.08135386568885872</v>
+        <v>-0.08004243138577664</v>
       </c>
       <c r="M240" s="19" t="n">
-        <v>-0.1516477987713487</v>
+        <v>-0.1534157996050003</v>
       </c>
       <c r="N240" s="20" t="n">
         <v>0</v>
@@ -16617,11 +16611,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q240" s="17" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q240" s="17" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="12" t="inlineStr">
@@ -16654,22 +16644,22 @@
       </c>
       <c r="G241" s="23" t="n"/>
       <c r="H241" s="13" t="n">
-        <v>-1650</v>
+        <v>-1450</v>
       </c>
       <c r="I241" s="15" t="n">
-        <v>0.7944662589943697</v>
+        <v>0.7897668561477887</v>
       </c>
       <c r="J241" s="15" t="n">
-        <v>0.9082568807339451</v>
+        <v>0.8988580750407831</v>
       </c>
       <c r="K241" s="15" t="n">
-        <v>0.9428571428571428</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="L241" s="14" t="n">
-        <v>-0.08231575065048438</v>
+        <v>-0.08130371180141044</v>
       </c>
       <c r="M241" s="14" t="n">
-        <v>-0.1573842707635473</v>
+        <v>-0.1557664641178811</v>
       </c>
       <c r="N241" s="15" t="n">
         <v>0</v>
@@ -16696,12 +16686,12 @@
       </c>
       <c r="B242" s="17" t="inlineStr">
         <is>
-          <t>TROY @ MIZ</t>
+          <t>BGSU @ ISU</t>
         </is>
       </c>
       <c r="C242" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D242" s="25" t="n">
@@ -16714,27 +16704,27 @@
       </c>
       <c r="F242" s="17" t="inlineStr">
         <is>
-          <t>MIZ ML</t>
+          <t>ISU ML</t>
         </is>
       </c>
       <c r="G242" s="26" t="n"/>
       <c r="H242" s="18" t="n">
-        <v>-6500</v>
+        <v>-3600</v>
       </c>
       <c r="I242" s="20" t="n">
-        <v>0.8317947492251805</v>
+        <v>0.8254237633576067</v>
       </c>
       <c r="J242" s="20" t="n">
-        <v>0.9538784067085954</v>
+        <v>0.9396411092985318</v>
       </c>
       <c r="K242" s="20" t="n">
-        <v>0.9848484848484849</v>
+        <v>0.972972972972973</v>
       </c>
       <c r="L242" s="19" t="n">
-        <v>-0.08297274179583243</v>
+        <v>-0.08135386568885872</v>
       </c>
       <c r="M242" s="19" t="n">
-        <v>-0.1554084084790476</v>
+        <v>-0.1516477987713487</v>
       </c>
       <c r="N242" s="20" t="n">
         <v>0</v>
@@ -16761,12 +16751,12 @@
       </c>
       <c r="B243" s="12" t="inlineStr">
         <is>
-          <t>UAB @ UL</t>
+          <t>TROY @ MIZ</t>
         </is>
       </c>
       <c r="C243" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D243" s="22" t="n">
@@ -16774,34 +16764,32 @@
       </c>
       <c r="E243" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F243" s="12" t="inlineStr">
         <is>
-          <t>Over 56.5</t>
-        </is>
-      </c>
-      <c r="G243" s="23" t="n">
-        <v>56.5</v>
-      </c>
+          <t>MIZ ML</t>
+        </is>
+      </c>
+      <c r="G243" s="23" t="n"/>
       <c r="H243" s="13" t="n">
-        <v>-112</v>
+        <v>-6500</v>
       </c>
       <c r="I243" s="15" t="n">
-        <v>0.4393816764752666</v>
+        <v>0.8317947492251805</v>
       </c>
       <c r="J243" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.9538784067085954</v>
       </c>
       <c r="K243" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.9848484848484849</v>
       </c>
       <c r="L243" s="14" t="n">
-        <v>-0.0831597783271758</v>
+        <v>-0.08297274179583243</v>
       </c>
       <c r="M243" s="14" t="n">
-        <v>-0.1683132552432454</v>
+        <v>-0.1554084084790476</v>
       </c>
       <c r="N243" s="15" t="n">
         <v>0</v>
@@ -16814,7 +16802,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q243" s="12" t="n"/>
+      <c r="Q243" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="17" t="inlineStr">
@@ -16824,12 +16816,12 @@
       </c>
       <c r="B244" s="17" t="inlineStr">
         <is>
-          <t>TULN @ KSU</t>
+          <t>UAB @ UL</t>
         </is>
       </c>
       <c r="C244" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D244" s="25" t="n">
@@ -16837,32 +16829,34 @@
       </c>
       <c r="E244" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F244" s="17" t="inlineStr">
         <is>
-          <t>KSU ML</t>
-        </is>
-      </c>
-      <c r="G244" s="26" t="n"/>
+          <t>Over 56.5</t>
+        </is>
+      </c>
+      <c r="G244" s="26" t="n">
+        <v>56.5</v>
+      </c>
       <c r="H244" s="18" t="n">
-        <v>-1800</v>
+        <v>-112</v>
       </c>
       <c r="I244" s="20" t="n">
-        <v>0.7942152473020465</v>
+        <v>0.4393816764752666</v>
       </c>
       <c r="J244" s="20" t="n">
-        <v>0.912442396313364</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K244" s="20" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L244" s="19" t="n">
-        <v>-0.08334336689120363</v>
+        <v>-0.0831597783271758</v>
       </c>
       <c r="M244" s="19" t="n">
-        <v>-0.1616616834033954</v>
+        <v>-0.1683132552432454</v>
       </c>
       <c r="N244" s="20" t="n">
         <v>0</v>
@@ -16875,11 +16869,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q244" s="17" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q244" s="17" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="12" t="inlineStr">
@@ -16889,12 +16879,12 @@
       </c>
       <c r="B245" s="12" t="inlineStr">
         <is>
-          <t>EMU @ WIS</t>
+          <t>ARST @ TCU</t>
         </is>
       </c>
       <c r="C245" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 16:30</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D245" s="22" t="n">
@@ -16907,29 +16897,29 @@
       </c>
       <c r="F245" s="12" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>Over 55.5</t>
         </is>
       </c>
       <c r="G245" s="23" t="n">
-        <v>45.5</v>
+        <v>55.5</v>
       </c>
       <c r="H245" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I245" s="15" t="n">
-        <v>0.431272438741787</v>
+        <v>0.4353240072943866</v>
       </c>
       <c r="J245" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K245" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L245" s="14" t="n">
-        <v>-0.08342338155527183</v>
+        <v>-0.08329254278965623</v>
       </c>
       <c r="M245" s="14" t="n">
-        <v>-0.1694012290898916</v>
+        <v>-0.1689268951652619</v>
       </c>
       <c r="N245" s="15" t="n">
         <v>0</v>
@@ -16952,12 +16942,12 @@
       </c>
       <c r="B246" s="17" t="inlineStr">
         <is>
-          <t>WVU @ UVA</t>
+          <t>TULN @ KSU</t>
         </is>
       </c>
       <c r="C246" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D246" s="25" t="n">
@@ -16965,34 +16955,32 @@
       </c>
       <c r="E246" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F246" s="17" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
-        </is>
-      </c>
-      <c r="G246" s="26" t="n">
-        <v>53.5</v>
-      </c>
+          <t>KSU ML</t>
+        </is>
+      </c>
+      <c r="G246" s="26" t="n"/>
       <c r="H246" s="18" t="n">
-        <v>-112</v>
+        <v>-1800</v>
       </c>
       <c r="I246" s="20" t="n">
-        <v>0.4374889082941585</v>
+        <v>0.7942152473020465</v>
       </c>
       <c r="J246" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.912442396313364</v>
       </c>
       <c r="K246" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="L246" s="19" t="n">
-        <v>-0.08400724365321681</v>
+        <v>-0.08334336689120363</v>
       </c>
       <c r="M246" s="19" t="n">
-        <v>-0.1718959950146285</v>
+        <v>-0.1616616834033954</v>
       </c>
       <c r="N246" s="20" t="n">
         <v>0</v>
@@ -17005,7 +16993,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q246" s="17" t="n"/>
+      <c r="Q246" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="12" t="inlineStr">
@@ -17015,12 +17007,12 @@
       </c>
       <c r="B247" s="12" t="inlineStr">
         <is>
-          <t>UNM @ OU</t>
+          <t>EMU @ WIS</t>
         </is>
       </c>
       <c r="C247" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 16:30</t>
         </is>
       </c>
       <c r="D247" s="22" t="n">
@@ -17033,29 +17025,29 @@
       </c>
       <c r="F247" s="12" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>Under 45.5</t>
         </is>
       </c>
       <c r="G247" s="23" t="n">
-        <v>46.5</v>
+        <v>45.5</v>
       </c>
       <c r="H247" s="13" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I247" s="15" t="n">
-        <v>0.4242665320851896</v>
+        <v>0.431272438741787</v>
       </c>
       <c r="J247" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K247" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L247" s="14" t="n">
-        <v>-0.08403757223048447</v>
+        <v>-0.08342338155527183</v>
       </c>
       <c r="M247" s="14" t="n">
-        <v>-0.1716701040241536</v>
+        <v>-0.1694012290898916</v>
       </c>
       <c r="N247" s="15" t="n">
         <v>0</v>
@@ -17078,12 +17070,12 @@
       </c>
       <c r="B248" s="17" t="inlineStr">
         <is>
-          <t>KENN @ TENN</t>
+          <t>UNM @ OU</t>
         </is>
       </c>
       <c r="C248" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:45</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D248" s="25" t="n">
@@ -17091,32 +17083,34 @@
       </c>
       <c r="E248" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F248" s="17" t="inlineStr">
         <is>
-          <t>TENN ML</t>
-        </is>
-      </c>
-      <c r="G248" s="26" t="n"/>
+          <t>Under 46.5</t>
+        </is>
+      </c>
+      <c r="G248" s="26" t="n">
+        <v>46.5</v>
+      </c>
       <c r="H248" s="18" t="n">
-        <v>-100000</v>
+        <v>-105</v>
       </c>
       <c r="I248" s="20" t="n">
-        <v>0.8499367258373444</v>
+        <v>0.4242665320851896</v>
       </c>
       <c r="J248" s="20" t="n">
-        <v>0.9807503701851887</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K248" s="20" t="n">
-        <v>0.999000999000999</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L248" s="19" t="n">
-        <v>-0.08419050806545607</v>
+        <v>-0.08403757223048447</v>
       </c>
       <c r="M248" s="19" t="n">
-        <v>-0.1492133374368184</v>
+        <v>-0.1716701040241536</v>
       </c>
       <c r="N248" s="20" t="n">
         <v>0</v>
@@ -17129,11 +17123,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q248" s="17" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q248" s="17" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="12" t="inlineStr">
@@ -17143,12 +17133,12 @@
       </c>
       <c r="B249" s="12" t="inlineStr">
         <is>
-          <t>GASO @ JVST</t>
+          <t>KENN @ TENN</t>
         </is>
       </c>
       <c r="C249" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 23:45</t>
         </is>
       </c>
       <c r="D249" s="22" t="n">
@@ -17156,34 +17146,32 @@
       </c>
       <c r="E249" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F249" s="12" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
-        </is>
-      </c>
-      <c r="G249" s="23" t="n">
-        <v>52.5</v>
-      </c>
+          <t>TENN ML</t>
+        </is>
+      </c>
+      <c r="G249" s="23" t="n"/>
       <c r="H249" s="13" t="n">
-        <v>-115</v>
+        <v>-100000</v>
       </c>
       <c r="I249" s="15" t="n">
-        <v>0.4407411742778912</v>
+        <v>0.8499367258373444</v>
       </c>
       <c r="J249" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.9807503701851887</v>
       </c>
       <c r="K249" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.999000999000999</v>
       </c>
       <c r="L249" s="14" t="n">
-        <v>-0.08498408637536668</v>
+        <v>-0.08419050806545607</v>
       </c>
       <c r="M249" s="14" t="n">
-        <v>-0.1760056306978557</v>
+        <v>-0.1492133374368184</v>
       </c>
       <c r="N249" s="15" t="n">
         <v>0</v>
@@ -17196,7 +17184,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q249" s="12" t="n"/>
+      <c r="Q249" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="17" t="inlineStr">
@@ -17206,12 +17198,12 @@
       </c>
       <c r="B250" s="17" t="inlineStr">
         <is>
-          <t>LT @ BAY</t>
+          <t>GASO @ JVST</t>
         </is>
       </c>
       <c r="C250" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D250" s="25" t="n">
@@ -17219,32 +17211,34 @@
       </c>
       <c r="E250" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F250" s="17" t="inlineStr">
         <is>
-          <t>BAY ML</t>
-        </is>
-      </c>
-      <c r="G250" s="26" t="n"/>
+          <t>Over 52.5</t>
+        </is>
+      </c>
+      <c r="G250" s="26" t="n">
+        <v>52.5</v>
+      </c>
       <c r="H250" s="18" t="n">
-        <v>-1200</v>
+        <v>-115</v>
       </c>
       <c r="I250" s="20" t="n">
-        <v>0.7647141463477202</v>
+        <v>0.4407411742778912</v>
       </c>
       <c r="J250" s="20" t="n">
-        <v>0.8869565217391304</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K250" s="20" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L250" s="19" t="n">
-        <v>-0.08510510669348836</v>
+        <v>-0.08498408637536668</v>
       </c>
       <c r="M250" s="19" t="n">
-        <v>-0.1715596747899699</v>
+        <v>-0.1760056306978557</v>
       </c>
       <c r="N250" s="20" t="n">
         <v>0</v>
@@ -17257,11 +17251,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q250" s="17" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q250" s="17" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="12" t="inlineStr">
@@ -17271,12 +17261,12 @@
       </c>
       <c r="B251" s="12" t="inlineStr">
         <is>
-          <t>MSU @ ND</t>
+          <t>LT @ BAY</t>
         </is>
       </c>
       <c r="C251" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D251" s="22" t="n">
@@ -17289,27 +17279,27 @@
       </c>
       <c r="F251" s="12" t="inlineStr">
         <is>
-          <t>ND ML</t>
+          <t>BAY ML</t>
         </is>
       </c>
       <c r="G251" s="23" t="n"/>
       <c r="H251" s="13" t="n">
-        <v>-6500</v>
+        <v>-1200</v>
       </c>
       <c r="I251" s="15" t="n">
-        <v>0.8214101582527794</v>
+        <v>0.7647141463477202</v>
       </c>
       <c r="J251" s="15" t="n">
-        <v>0.9538784067085954</v>
+        <v>0.8869565217391304</v>
       </c>
       <c r="K251" s="15" t="n">
-        <v>0.9848484848484849</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="L251" s="14" t="n">
-        <v>-0.08531060133862964</v>
+        <v>-0.08510510669348836</v>
       </c>
       <c r="M251" s="14" t="n">
-        <v>-0.1659527623894855</v>
+        <v>-0.1715596747899699</v>
       </c>
       <c r="N251" s="15" t="n">
         <v>0</v>
@@ -17336,12 +17326,12 @@
       </c>
       <c r="B252" s="17" t="inlineStr">
         <is>
-          <t>ASU @ KU</t>
+          <t>MSU @ ND</t>
         </is>
       </c>
       <c r="C252" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D252" s="25" t="n">
@@ -17349,34 +17339,32 @@
       </c>
       <c r="E252" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F252" s="17" t="inlineStr">
         <is>
-          <t>ASU -5.5</t>
-        </is>
-      </c>
-      <c r="G252" s="26" t="n">
-        <v>5.5</v>
-      </c>
+          <t>ND ML</t>
+        </is>
+      </c>
+      <c r="G252" s="26" t="n"/>
       <c r="H252" s="18" t="n">
-        <v>-105</v>
+        <v>-6500</v>
       </c>
       <c r="I252" s="20" t="n">
-        <v>0.4200889240930783</v>
+        <v>0.8214101582527794</v>
       </c>
       <c r="J252" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.9538784067085954</v>
       </c>
       <c r="K252" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.9848484848484849</v>
       </c>
       <c r="L252" s="19" t="n">
-        <v>-0.0857537459757826</v>
+        <v>-0.08531060133862964</v>
       </c>
       <c r="M252" s="19" t="n">
-        <v>-0.1798263862944662</v>
+        <v>-0.1659527623894855</v>
       </c>
       <c r="N252" s="20" t="n">
         <v>0</v>
@@ -17389,7 +17377,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q252" s="17" t="n"/>
+      <c r="Q252" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="12" t="inlineStr">
@@ -17399,12 +17391,12 @@
       </c>
       <c r="B253" s="12" t="inlineStr">
         <is>
-          <t>ARST @ TCU</t>
+          <t>EMU @ WIS</t>
         </is>
       </c>
       <c r="C253" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-19 16:30</t>
         </is>
       </c>
       <c r="D253" s="22" t="n">
@@ -17412,34 +17404,32 @@
       </c>
       <c r="E253" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F253" s="12" t="inlineStr">
         <is>
-          <t>Over 55.5</t>
-        </is>
-      </c>
-      <c r="G253" s="23" t="n">
-        <v>55.5</v>
-      </c>
+          <t>WIS ML</t>
+        </is>
+      </c>
+      <c r="G253" s="23" t="n"/>
       <c r="H253" s="13" t="n">
-        <v>-118</v>
+        <v>-2800</v>
       </c>
       <c r="I253" s="15" t="n">
-        <v>0.4440060701525216</v>
+        <v>0.7982970475808102</v>
       </c>
       <c r="J253" s="15" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.9311163895486935</v>
       </c>
       <c r="K253" s="15" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="L253" s="14" t="n">
-        <v>-0.08586026363623361</v>
+        <v>-0.08601529772470062</v>
       </c>
       <c r="M253" s="14" t="n">
-        <v>-0.1797175992097483</v>
+        <v>-0.173192343577018</v>
       </c>
       <c r="N253" s="15" t="n">
         <v>0</v>
@@ -17452,7 +17442,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q253" s="12" t="n"/>
+      <c r="Q253" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="17" t="inlineStr">
@@ -17462,12 +17456,12 @@
       </c>
       <c r="B254" s="17" t="inlineStr">
         <is>
-          <t>EMU @ WIS</t>
+          <t>USU @ UTAH</t>
         </is>
       </c>
       <c r="C254" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:30</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D254" s="25" t="n">
@@ -17480,27 +17474,27 @@
       </c>
       <c r="F254" s="17" t="inlineStr">
         <is>
-          <t>WIS ML</t>
+          <t>UTAH ML</t>
         </is>
       </c>
       <c r="G254" s="26" t="n"/>
       <c r="H254" s="18" t="n">
-        <v>-2800</v>
+        <v>-6500</v>
       </c>
       <c r="I254" s="20" t="n">
-        <v>0.7982970475808102</v>
+        <v>0.8162369969013338</v>
       </c>
       <c r="J254" s="20" t="n">
-        <v>0.9311163895486935</v>
+        <v>0.9538784067085954</v>
       </c>
       <c r="K254" s="20" t="n">
-        <v>0.9655172413793104</v>
+        <v>0.9848484848484849</v>
       </c>
       <c r="L254" s="19" t="n">
-        <v>-0.08601529772470062</v>
+        <v>-0.08630824014848124</v>
       </c>
       <c r="M254" s="19" t="n">
-        <v>-0.173192343577018</v>
+        <v>-0.1712055108386458</v>
       </c>
       <c r="N254" s="20" t="n">
         <v>0</v>
@@ -17527,12 +17521,12 @@
       </c>
       <c r="B255" s="12" t="inlineStr">
         <is>
-          <t>USU @ UTAH</t>
+          <t>ARST @ TCU</t>
         </is>
       </c>
       <c r="C255" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D255" s="22" t="n">
@@ -17545,27 +17539,27 @@
       </c>
       <c r="F255" s="12" t="inlineStr">
         <is>
-          <t>UTAH ML</t>
+          <t>TCU ML</t>
         </is>
       </c>
       <c r="G255" s="23" t="n"/>
       <c r="H255" s="13" t="n">
-        <v>-6500</v>
+        <v>-1350</v>
       </c>
       <c r="I255" s="15" t="n">
-        <v>0.8162369969013338</v>
+        <v>0.7616698450434658</v>
       </c>
       <c r="J255" s="15" t="n">
-        <v>0.9538784067085954</v>
+        <v>0.8933823529411765</v>
       </c>
       <c r="K255" s="15" t="n">
-        <v>0.9848484848484849</v>
+        <v>0.9310344827586207</v>
       </c>
       <c r="L255" s="14" t="n">
-        <v>-0.08630824014848124</v>
+        <v>-0.0868394806998839</v>
       </c>
       <c r="M255" s="14" t="n">
-        <v>-0.1712055108386458</v>
+        <v>-0.1819101664347961</v>
       </c>
       <c r="N255" s="15" t="n">
         <v>0</v>
@@ -17592,12 +17586,12 @@
       </c>
       <c r="B256" s="17" t="inlineStr">
         <is>
-          <t>ARST @ TCU</t>
+          <t>WVU @ UVA</t>
         </is>
       </c>
       <c r="C256" s="17" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D256" s="25" t="n">
@@ -17610,27 +17604,27 @@
       </c>
       <c r="F256" s="17" t="inlineStr">
         <is>
-          <t>TCU ML</t>
+          <t>UVA ML</t>
         </is>
       </c>
       <c r="G256" s="26" t="n"/>
       <c r="H256" s="18" t="n">
-        <v>-1350</v>
+        <v>-395</v>
       </c>
       <c r="I256" s="20" t="n">
-        <v>0.7616698450434658</v>
+        <v>0.6519324025282154</v>
       </c>
       <c r="J256" s="20" t="n">
-        <v>0.8933823529411765</v>
+        <v>0.7659021045164341</v>
       </c>
       <c r="K256" s="20" t="n">
-        <v>0.9310344827586207</v>
+        <v>0.797979797979798</v>
       </c>
       <c r="L256" s="19" t="n">
-        <v>-0.0868394806998839</v>
+        <v>-0.08706231180975971</v>
       </c>
       <c r="M256" s="19" t="n">
-        <v>-0.1819101664347961</v>
+        <v>-0.1830214196165402</v>
       </c>
       <c r="N256" s="20" t="n">
         <v>0</v>
@@ -17643,11 +17637,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q256" s="17" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q256" s="17" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="12" t="inlineStr">
@@ -17657,12 +17647,12 @@
       </c>
       <c r="B257" s="12" t="inlineStr">
         <is>
-          <t>WVU @ UVA</t>
+          <t>GAST @ UCF</t>
         </is>
       </c>
       <c r="C257" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D257" s="22" t="n">
@@ -17675,27 +17665,27 @@
       </c>
       <c r="F257" s="12" t="inlineStr">
         <is>
-          <t>UVA ML</t>
+          <t>UCF ML</t>
         </is>
       </c>
       <c r="G257" s="23" t="n"/>
       <c r="H257" s="13" t="n">
-        <v>-395</v>
+        <v>-1200</v>
       </c>
       <c r="I257" s="15" t="n">
-        <v>0.6519324025282154</v>
+        <v>0.7540652140144954</v>
       </c>
       <c r="J257" s="15" t="n">
-        <v>0.7659021045164341</v>
+        <v>0.8869565217391304</v>
       </c>
       <c r="K257" s="15" t="n">
-        <v>0.797979797979798</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="L257" s="14" t="n">
-        <v>-0.08706231180975971</v>
+        <v>-0.08722465784831755</v>
       </c>
       <c r="M257" s="14" t="n">
-        <v>-0.1830214196165402</v>
+        <v>-0.1830960181509633</v>
       </c>
       <c r="N257" s="15" t="n">
         <v>0</v>
@@ -17708,7 +17698,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q257" s="12" t="n"/>
+      <c r="Q257" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="17" t="inlineStr">
@@ -17718,12 +17712,12 @@
       </c>
       <c r="B258" s="17" t="inlineStr">
         <is>
-          <t>GAST @ UCF</t>
+          <t>STAN @ DUKE</t>
         </is>
       </c>
       <c r="C258" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D258" s="25" t="n">
@@ -17731,32 +17725,34 @@
       </c>
       <c r="E258" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F258" s="17" t="inlineStr">
         <is>
-          <t>UCF ML</t>
-        </is>
-      </c>
-      <c r="G258" s="26" t="n"/>
+          <t>DUKE -9.5</t>
+        </is>
+      </c>
+      <c r="G258" s="26" t="n">
+        <v>-9.5</v>
+      </c>
       <c r="H258" s="18" t="n">
-        <v>-1200</v>
+        <v>-112</v>
       </c>
       <c r="I258" s="20" t="n">
-        <v>0.7540652140144954</v>
+        <v>0.4284774069304556</v>
       </c>
       <c r="J258" s="20" t="n">
-        <v>0.8869565217391304</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K258" s="20" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L258" s="19" t="n">
-        <v>-0.08722465784831755</v>
+        <v>-0.08731425001538265</v>
       </c>
       <c r="M258" s="19" t="n">
-        <v>-0.1830960181509633</v>
+        <v>-0.1889534797387806</v>
       </c>
       <c r="N258" s="20" t="n">
         <v>0</v>
@@ -17769,11 +17765,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q258" s="17" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q258" s="17" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="12" t="inlineStr">
@@ -17783,12 +17775,12 @@
       </c>
       <c r="B259" s="12" t="inlineStr">
         <is>
-          <t>STAN @ DUKE</t>
+          <t>UNM @ OU</t>
         </is>
       </c>
       <c r="C259" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D259" s="22" t="n">
@@ -17796,34 +17788,32 @@
       </c>
       <c r="E259" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F259" s="12" t="inlineStr">
         <is>
-          <t>DUKE -9.5</t>
-        </is>
-      </c>
-      <c r="G259" s="23" t="n">
-        <v>-9.5</v>
-      </c>
+          <t>OU ML</t>
+        </is>
+      </c>
+      <c r="G259" s="23" t="n"/>
       <c r="H259" s="13" t="n">
-        <v>-112</v>
+        <v>-2100</v>
       </c>
       <c r="I259" s="15" t="n">
-        <v>0.4284774069304556</v>
+        <v>0.7800066377068618</v>
       </c>
       <c r="J259" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.9197080291970804</v>
       </c>
       <c r="K259" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="L259" s="14" t="n">
-        <v>-0.08731425001538265</v>
+        <v>-0.08754307503525306</v>
       </c>
       <c r="M259" s="14" t="n">
-        <v>-0.1889534797387806</v>
+        <v>-0.1828501890690019</v>
       </c>
       <c r="N259" s="15" t="n">
         <v>0</v>
@@ -17836,7 +17826,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q259" s="12" t="n"/>
+      <c r="Q259" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="17" t="inlineStr">
@@ -17846,12 +17840,12 @@
       </c>
       <c r="B260" s="17" t="inlineStr">
         <is>
-          <t>UNM @ OU</t>
+          <t>UNC @ CLEM</t>
         </is>
       </c>
       <c r="C260" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D260" s="25" t="n">
@@ -17859,32 +17853,34 @@
       </c>
       <c r="E260" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F260" s="17" t="inlineStr">
         <is>
-          <t>OU ML</t>
-        </is>
-      </c>
-      <c r="G260" s="26" t="n"/>
+          <t>Under 44.5</t>
+        </is>
+      </c>
+      <c r="G260" s="26" t="n">
+        <v>44.5</v>
+      </c>
       <c r="H260" s="18" t="n">
-        <v>-2100</v>
+        <v>-118</v>
       </c>
       <c r="I260" s="20" t="n">
-        <v>0.7800066377068618</v>
+        <v>0.4364987662400414</v>
       </c>
       <c r="J260" s="20" t="n">
-        <v>0.9197080291970804</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K260" s="20" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L260" s="19" t="n">
-        <v>-0.08754307503525306</v>
+        <v>-0.08817981134676509</v>
       </c>
       <c r="M260" s="19" t="n">
-        <v>-0.1828501890690019</v>
+        <v>-0.1935870250819575</v>
       </c>
       <c r="N260" s="20" t="n">
         <v>0</v>
@@ -17897,11 +17893,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q260" s="17" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q260" s="17" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="12" t="inlineStr">
@@ -17911,7 +17903,7 @@
       </c>
       <c r="B261" s="12" t="inlineStr">
         <is>
-          <t>UNC @ CLEM</t>
+          <t>ASU @ KU</t>
         </is>
       </c>
       <c r="C261" s="12" t="inlineStr">
@@ -17924,37 +17916,37 @@
       </c>
       <c r="E261" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F261" s="12" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>ASU -6</t>
         </is>
       </c>
       <c r="G261" s="23" t="n">
-        <v>44.5</v>
+        <v>6</v>
       </c>
       <c r="H261" s="13" t="n">
-        <v>-118</v>
+        <v>-108</v>
       </c>
       <c r="I261" s="15" t="n">
-        <v>0.4364987662400414</v>
+        <v>0.4145116732425067</v>
       </c>
       <c r="J261" s="15" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K261" s="15" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L261" s="14" t="n">
-        <v>-0.08817981134676509</v>
+        <v>-0.08913719440859406</v>
       </c>
       <c r="M261" s="14" t="n">
-        <v>-0.1935870250819575</v>
+        <v>-0.1963366695228824</v>
       </c>
       <c r="N261" s="15" t="n">
-        <v>0</v>
+        <v>0.0265</v>
       </c>
       <c r="O261" s="24" t="n">
         <v>0.839</v>
@@ -18098,12 +18090,12 @@
       </c>
       <c r="B264" s="17" t="inlineStr">
         <is>
-          <t>BGSU @ ISU</t>
+          <t>SYR @ PITT</t>
         </is>
       </c>
       <c r="C264" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-17 23:30</t>
         </is>
       </c>
       <c r="D264" s="25" t="n">
@@ -18111,34 +18103,34 @@
       </c>
       <c r="E264" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F264" s="17" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>PITT -10.5</t>
         </is>
       </c>
       <c r="G264" s="26" t="n">
-        <v>44.5</v>
+        <v>-10.5</v>
       </c>
       <c r="H264" s="18" t="n">
-        <v>-118</v>
+        <v>-105</v>
       </c>
       <c r="I264" s="20" t="n">
-        <v>0.4095536349313933</v>
+        <v>0.4017007150714805</v>
       </c>
       <c r="J264" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K264" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L264" s="19" t="n">
-        <v>-0.0908760475434153</v>
+        <v>-0.09069490424715211</v>
       </c>
       <c r="M264" s="19" t="n">
-        <v>-0.2433670134318328</v>
+        <v>-0.2157271753366333</v>
       </c>
       <c r="N264" s="20" t="n">
         <v>0</v>
@@ -18161,7 +18153,7 @@
       </c>
       <c r="B265" s="12" t="inlineStr">
         <is>
-          <t>AKR @ MINN</t>
+          <t>BGSU @ ISU</t>
         </is>
       </c>
       <c r="C265" s="12" t="inlineStr">
@@ -18174,32 +18166,34 @@
       </c>
       <c r="E265" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F265" s="12" t="inlineStr">
         <is>
-          <t>MINN ML</t>
-        </is>
-      </c>
-      <c r="G265" s="23" t="n"/>
+          <t>Under 44.5</t>
+        </is>
+      </c>
+      <c r="G265" s="23" t="n">
+        <v>44.5</v>
+      </c>
       <c r="H265" s="13" t="n">
-        <v>-3200</v>
+        <v>-118</v>
       </c>
       <c r="I265" s="15" t="n">
-        <v>0.7657795759688519</v>
+        <v>0.4095536349313933</v>
       </c>
       <c r="J265" s="15" t="n">
-        <v>0.9356725146198831</v>
+        <v>0.5</v>
       </c>
       <c r="K265" s="15" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L265" s="14" t="n">
-        <v>-0.09093343917488417</v>
+        <v>-0.0908760475434153</v>
       </c>
       <c r="M265" s="14" t="n">
-        <v>-0.2102898122821214</v>
+        <v>-0.2433670134318328</v>
       </c>
       <c r="N265" s="15" t="n">
         <v>0</v>
@@ -18212,11 +18206,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q265" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q265" s="12" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="17" t="inlineStr">
@@ -18226,12 +18216,12 @@
       </c>
       <c r="B266" s="17" t="inlineStr">
         <is>
-          <t>LSU @ MISS</t>
+          <t>AKR @ MINN</t>
         </is>
       </c>
       <c r="C266" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D266" s="25" t="n">
@@ -18244,27 +18234,27 @@
       </c>
       <c r="F266" s="17" t="inlineStr">
         <is>
-          <t>LSU ML</t>
+          <t>MINN ML</t>
         </is>
       </c>
       <c r="G266" s="26" t="n"/>
       <c r="H266" s="18" t="n">
-        <v>-155</v>
+        <v>-3200</v>
       </c>
       <c r="I266" s="20" t="n">
-        <v>0.4743335200201259</v>
+        <v>0.7657795759688519</v>
       </c>
       <c r="J266" s="20" t="n">
-        <v>0.5829926410466066</v>
+        <v>0.9356725146198831</v>
       </c>
       <c r="K266" s="20" t="n">
-        <v>0.6078431372549019</v>
+        <v>0.9696969696969697</v>
       </c>
       <c r="L266" s="19" t="n">
-        <v>-0.09131736831628295</v>
+        <v>-0.09093343917488417</v>
       </c>
       <c r="M266" s="19" t="n">
-        <v>-0.2196448541604382</v>
+        <v>-0.2102898122821214</v>
       </c>
       <c r="N266" s="20" t="n">
         <v>0</v>
@@ -18277,7 +18267,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q266" s="17" t="n"/>
+      <c r="Q266" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="12" t="inlineStr">
@@ -18287,12 +18281,12 @@
       </c>
       <c r="B267" s="12" t="inlineStr">
         <is>
-          <t>UTSA @ TEX</t>
+          <t>LSU @ MISS</t>
         </is>
       </c>
       <c r="C267" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D267" s="22" t="n">
@@ -18305,27 +18299,27 @@
       </c>
       <c r="F267" s="12" t="inlineStr">
         <is>
-          <t>TEX ML</t>
+          <t>LSU ML</t>
         </is>
       </c>
       <c r="G267" s="23" t="n"/>
       <c r="H267" s="13" t="n">
-        <v>-6500</v>
+        <v>-155</v>
       </c>
       <c r="I267" s="15" t="n">
-        <v>0.7754426564399982</v>
+        <v>0.4743335200201259</v>
       </c>
       <c r="J267" s="15" t="n">
-        <v>0.9538784067085954</v>
+        <v>0.5829926410466066</v>
       </c>
       <c r="K267" s="15" t="n">
-        <v>0.9848484848484849</v>
+        <v>0.6078431372549019</v>
       </c>
       <c r="L267" s="14" t="n">
-        <v>-0.09136884551946439</v>
+        <v>-0.09131736831628295</v>
       </c>
       <c r="M267" s="14" t="n">
-        <v>-0.212627456537848</v>
+        <v>-0.2196448541604382</v>
       </c>
       <c r="N267" s="15" t="n">
         <v>0</v>
@@ -18338,11 +18332,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q267" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q267" s="12" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="17" t="inlineStr">
@@ -18352,12 +18342,12 @@
       </c>
       <c r="B268" s="17" t="inlineStr">
         <is>
-          <t>SYR @ PITT</t>
+          <t>UTSA @ TEX</t>
         </is>
       </c>
       <c r="C268" s="17" t="inlineStr">
         <is>
-          <t>2026-09-17 23:30</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D268" s="25" t="n">
@@ -18365,34 +18355,32 @@
       </c>
       <c r="E268" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F268" s="17" t="inlineStr">
         <is>
-          <t>PITT -10.5</t>
-        </is>
-      </c>
-      <c r="G268" s="26" t="n">
-        <v>-10.5</v>
-      </c>
+          <t>TEX ML</t>
+        </is>
+      </c>
+      <c r="G268" s="26" t="n"/>
       <c r="H268" s="18" t="n">
-        <v>-112</v>
+        <v>-6500</v>
       </c>
       <c r="I268" s="20" t="n">
-        <v>0.4092827101996394</v>
+        <v>0.7754426564399982</v>
       </c>
       <c r="J268" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.9538784067085954</v>
       </c>
       <c r="K268" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.9848484848484849</v>
       </c>
       <c r="L268" s="19" t="n">
-        <v>-0.09147225335581981</v>
+        <v>-0.09136884551946439</v>
       </c>
       <c r="M268" s="19" t="n">
-        <v>-0.2252862985506826</v>
+        <v>-0.212627456537848</v>
       </c>
       <c r="N268" s="20" t="n">
         <v>0</v>
@@ -18405,7 +18393,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q268" s="17" t="n"/>
+      <c r="Q268" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="12" t="inlineStr">
@@ -18926,37 +18918,37 @@
       </c>
       <c r="E277" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F277" s="12" t="inlineStr">
         <is>
-          <t>LSU -3</t>
+          <t>Over 58.5</t>
         </is>
       </c>
       <c r="G277" s="23" t="n">
-        <v>3</v>
+        <v>58.5</v>
       </c>
       <c r="H277" s="13" t="n">
-        <v>-110</v>
+        <v>-118</v>
       </c>
       <c r="I277" s="15" t="n">
-        <v>0.385169289010895</v>
+        <v>0.3991199502400786</v>
       </c>
       <c r="J277" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K277" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L277" s="14" t="n">
-        <v>-0.09350199936537928</v>
+        <v>-0.0934668589126937</v>
       </c>
       <c r="M277" s="14" t="n">
-        <v>-0.2510988914384221</v>
+        <v>-0.262642803793753</v>
       </c>
       <c r="N277" s="15" t="n">
-        <v>0.0513</v>
+        <v>0</v>
       </c>
       <c r="O277" s="24" t="n">
         <v>0.839</v>
@@ -18976,12 +18968,12 @@
       </c>
       <c r="B278" s="17" t="inlineStr">
         <is>
-          <t>USC @ RUTG</t>
+          <t>LSU @ MISS</t>
         </is>
       </c>
       <c r="C278" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D278" s="25" t="n">
@@ -18989,37 +18981,37 @@
       </c>
       <c r="E278" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F278" s="17" t="inlineStr">
         <is>
-          <t>Over 59.5</t>
+          <t>LSU -3</t>
         </is>
       </c>
       <c r="G278" s="26" t="n">
-        <v>59.5</v>
+        <v>3</v>
       </c>
       <c r="H278" s="18" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I278" s="20" t="n">
-        <v>0.3799658053215573</v>
+        <v>0.385169289010895</v>
       </c>
       <c r="J278" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K278" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L278" s="19" t="n">
-        <v>-0.0936154313326031</v>
+        <v>-0.09350199936537928</v>
       </c>
       <c r="M278" s="19" t="n">
-        <v>-0.2682140045658895</v>
+        <v>-0.2510988914384221</v>
       </c>
       <c r="N278" s="20" t="n">
-        <v>0</v>
+        <v>0.0513</v>
       </c>
       <c r="O278" s="27" t="n">
         <v>0.839</v>
@@ -19039,12 +19031,12 @@
       </c>
       <c r="B279" s="12" t="inlineStr">
         <is>
-          <t>WMU @ RICE</t>
+          <t>USC @ RUTG</t>
         </is>
       </c>
       <c r="C279" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D279" s="22" t="n">
@@ -19052,32 +19044,34 @@
       </c>
       <c r="E279" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F279" s="12" t="inlineStr">
         <is>
-          <t>WMU ML</t>
-        </is>
-      </c>
-      <c r="G279" s="23" t="n"/>
+          <t>Over 59.5</t>
+        </is>
+      </c>
+      <c r="G279" s="23" t="n">
+        <v>59.5</v>
+      </c>
       <c r="H279" s="13" t="n">
-        <v>-375</v>
+        <v>-108</v>
       </c>
       <c r="I279" s="15" t="n">
-        <v>0.5770168407509679</v>
+        <v>0.3799658053215573</v>
       </c>
       <c r="J279" s="15" t="n">
-        <v>0.7571884984025559</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K279" s="15" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L279" s="14" t="n">
-        <v>-0.09374022225691331</v>
+        <v>-0.0936154313326031</v>
       </c>
       <c r="M279" s="14" t="n">
-        <v>-0.2691120017154407</v>
+        <v>-0.2682140045658895</v>
       </c>
       <c r="N279" s="15" t="n">
         <v>0</v>
@@ -19090,11 +19084,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q279" s="12" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
+      <c r="Q279" s="12" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="17" t="inlineStr">
@@ -19104,12 +19094,12 @@
       </c>
       <c r="B280" s="17" t="inlineStr">
         <is>
-          <t>WKU @ IU</t>
+          <t>WMU @ RICE</t>
         </is>
       </c>
       <c r="C280" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D280" s="25" t="n">
@@ -19117,34 +19107,32 @@
       </c>
       <c r="E280" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F280" s="17" t="inlineStr">
         <is>
-          <t>Over 60.5</t>
-        </is>
-      </c>
-      <c r="G280" s="26" t="n">
-        <v>60.5</v>
-      </c>
+          <t>WMU ML</t>
+        </is>
+      </c>
+      <c r="G280" s="26" t="n"/>
       <c r="H280" s="18" t="n">
-        <v>-110</v>
+        <v>-375</v>
       </c>
       <c r="I280" s="20" t="n">
-        <v>0.3804997784954824</v>
+        <v>0.5770168407509679</v>
       </c>
       <c r="J280" s="20" t="n">
-        <v>0.5</v>
+        <v>0.7571884984025559</v>
       </c>
       <c r="K280" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="L280" s="19" t="n">
-        <v>-0.09376764301607408</v>
+        <v>-0.09374022225691331</v>
       </c>
       <c r="M280" s="19" t="n">
-        <v>-0.2735913319631699</v>
+        <v>-0.2691120017154407</v>
       </c>
       <c r="N280" s="20" t="n">
         <v>0</v>
@@ -19157,7 +19145,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q280" s="17" t="n"/>
+      <c r="Q280" s="17" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="12" t="inlineStr">
@@ -19192,22 +19184,22 @@
         <v>59.5</v>
       </c>
       <c r="H281" s="13" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I281" s="15" t="n">
-        <v>0.3826646578267929</v>
+        <v>0.3804997807918085</v>
       </c>
       <c r="J281" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K281" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L281" s="14" t="n">
-        <v>-0.09382407573615809</v>
+        <v>-0.0937676428976935</v>
       </c>
       <c r="M281" s="14" t="n">
-        <v>-0.2756704691135705</v>
+        <v>-0.2735913275792747</v>
       </c>
       <c r="N281" s="15" t="n">
         <v>0</v>
@@ -19230,12 +19222,12 @@
       </c>
       <c r="B282" s="17" t="inlineStr">
         <is>
-          <t>LSU @ MISS</t>
+          <t>WKU @ IU</t>
         </is>
       </c>
       <c r="C282" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D282" s="25" t="n">
@@ -19248,29 +19240,29 @@
       </c>
       <c r="F282" s="17" t="inlineStr">
         <is>
-          <t>Over 59.5</t>
+          <t>Over 60.5</t>
         </is>
       </c>
       <c r="G282" s="26" t="n">
-        <v>59.5</v>
+        <v>60.5</v>
       </c>
       <c r="H282" s="18" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="I282" s="20" t="n">
-        <v>0.3653991748346024</v>
+        <v>0.3804997784954824</v>
       </c>
       <c r="J282" s="20" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.5</v>
       </c>
       <c r="K282" s="20" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L282" s="19" t="n">
-        <v>-0.09386441126080745</v>
+        <v>-0.09376764301607408</v>
       </c>
       <c r="M282" s="19" t="n">
-        <v>-0.2763663400334344</v>
+        <v>-0.2735913319631699</v>
       </c>
       <c r="N282" s="20" t="n">
         <v>0</v>
@@ -19761,22 +19753,22 @@
       </c>
       <c r="G290" s="26" t="n"/>
       <c r="H290" s="18" t="n">
-        <v>-1800</v>
+        <v>-1650</v>
       </c>
       <c r="I290" s="20" t="n">
-        <v>0.6605220662452306</v>
+        <v>0.6584293084555211</v>
       </c>
       <c r="J290" s="20" t="n">
-        <v>0.912442396313364</v>
+        <v>0.9082568807339451</v>
       </c>
       <c r="K290" s="20" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="L290" s="19" t="n">
-        <v>-0.09443361273520971</v>
+        <v>-0.09442121262798674</v>
       </c>
       <c r="M290" s="19" t="n">
-        <v>-0.3027822634078121</v>
+        <v>-0.3016658849714171</v>
       </c>
       <c r="N290" s="20" t="n">
         <v>0</v>
@@ -19931,12 +19923,12 @@
       </c>
       <c r="B293" s="12" t="inlineStr">
         <is>
-          <t>WVU @ UVA</t>
+          <t>NDSU @ SAC</t>
         </is>
       </c>
       <c r="C293" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-20 02:30</t>
         </is>
       </c>
       <c r="D293" s="22" t="n">
@@ -19944,47 +19936,49 @@
       </c>
       <c r="E293" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F293" s="12" t="inlineStr">
         <is>
-          <t>UVA -10</t>
-        </is>
-      </c>
-      <c r="G293" s="23" t="n">
-        <v>-10</v>
-      </c>
+          <t>NDSU ML</t>
+        </is>
+      </c>
+      <c r="G293" s="23" t="n"/>
       <c r="H293" s="13" t="n">
-        <v>-112</v>
+        <v>-9000</v>
       </c>
       <c r="I293" s="15" t="n">
-        <v>0.3611819500961256</v>
+        <v>0.6867085145453984</v>
       </c>
       <c r="J293" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.9625668449197861</v>
       </c>
       <c r="K293" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.9890109890109891</v>
       </c>
       <c r="L293" s="14" t="n">
-        <v>-0.09451859369654776</v>
+        <v>-0.0945455935096015</v>
       </c>
       <c r="M293" s="14" t="n">
-        <v>-0.3061482057478355</v>
+        <v>-0.3056613908485417</v>
       </c>
       <c r="N293" s="15" t="n">
-        <v>0.0322</v>
+        <v>0</v>
       </c>
       <c r="O293" s="24" t="n">
-        <v>0.839</v>
+        <v>0.926</v>
       </c>
       <c r="P293" s="12" t="inlineStr">
         <is>
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q293" s="12" t="n"/>
+      <c r="Q293" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="17" t="inlineStr">
@@ -19994,12 +19988,12 @@
       </c>
       <c r="B294" s="17" t="inlineStr">
         <is>
-          <t>NDSU @ SAC</t>
+          <t>WVU @ UVA</t>
         </is>
       </c>
       <c r="C294" s="17" t="inlineStr">
         <is>
-          <t>2026-09-20 02:30</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D294" s="25" t="n">
@@ -20007,49 +20001,47 @@
       </c>
       <c r="E294" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F294" s="17" t="inlineStr">
         <is>
-          <t>NDSU ML</t>
-        </is>
-      </c>
-      <c r="G294" s="26" t="n"/>
+          <t>UVA -10</t>
+        </is>
+      </c>
+      <c r="G294" s="26" t="n">
+        <v>-10</v>
+      </c>
       <c r="H294" s="18" t="n">
-        <v>-9000</v>
+        <v>-115</v>
       </c>
       <c r="I294" s="20" t="n">
-        <v>0.6867085145453984</v>
+        <v>0.3644341911543156</v>
       </c>
       <c r="J294" s="20" t="n">
-        <v>0.9625668449197861</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K294" s="20" t="n">
-        <v>0.9890109890109891</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L294" s="19" t="n">
-        <v>-0.0945455935096015</v>
+        <v>-0.09454563135434635</v>
       </c>
       <c r="M294" s="19" t="n">
-        <v>-0.3056613908485417</v>
+        <v>-0.3084054504972476</v>
       </c>
       <c r="N294" s="20" t="n">
-        <v>0</v>
+        <v>0.0322</v>
       </c>
       <c r="O294" s="27" t="n">
-        <v>0.926</v>
+        <v>0.839</v>
       </c>
       <c r="P294" s="17" t="inlineStr">
         <is>
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q294" s="17" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q294" s="17" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="12" t="inlineStr">
@@ -20315,12 +20307,12 @@
       </c>
       <c r="B299" s="12" t="inlineStr">
         <is>
-          <t>BALL @ LIB</t>
+          <t>NEV @ MTSU</t>
         </is>
       </c>
       <c r="C299" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D299" s="22" t="n">
@@ -20333,29 +20325,29 @@
       </c>
       <c r="F299" s="12" t="inlineStr">
         <is>
-          <t>LIB -14.5</t>
+          <t>NEV -3.5</t>
         </is>
       </c>
       <c r="G299" s="23" t="n">
-        <v>-14.5</v>
+        <v>3.5</v>
       </c>
       <c r="H299" s="13" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I299" s="15" t="n">
-        <v>0.3435133294129906</v>
+        <v>0.3543219121372638</v>
       </c>
       <c r="J299" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K299" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L299" s="14" t="n">
-        <v>-0.09464064099423691</v>
+        <v>-0.09463824079587989</v>
       </c>
       <c r="M299" s="14" t="n">
-        <v>-0.3293311187651136</v>
+        <v>-0.3293192377401792</v>
       </c>
       <c r="N299" s="15" t="n">
         <v>0</v>
@@ -20368,7 +20360,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q299" s="12" t="n"/>
+      <c r="Q299" s="12" t="inlineStr">
+        <is>
+          <t>raw model/market disagreement exceeds the safety limit</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="17" t="inlineStr">
@@ -20378,12 +20374,12 @@
       </c>
       <c r="B300" s="17" t="inlineStr">
         <is>
-          <t>KENT @ OSU</t>
+          <t>BALL @ LIB</t>
         </is>
       </c>
       <c r="C300" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D300" s="25" t="n">
@@ -20391,22 +20387,22 @@
       </c>
       <c r="E300" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F300" s="17" t="inlineStr">
         <is>
-          <t>Over 59.5</t>
+          <t>LIB -14.5</t>
         </is>
       </c>
       <c r="G300" s="26" t="n">
-        <v>59.5</v>
+        <v>-14.5</v>
       </c>
       <c r="H300" s="18" t="n">
         <v>-105</v>
       </c>
       <c r="I300" s="20" t="n">
-        <v>0.3433649069662547</v>
+        <v>0.3435133294129906</v>
       </c>
       <c r="J300" s="20" t="n">
         <v>0.4891657638136511</v>
@@ -20415,10 +20411,10 @@
         <v>0.5121951219512195</v>
       </c>
       <c r="L300" s="19" t="n">
-        <v>-0.09464292488406345</v>
+        <v>-0.09464064099423691</v>
       </c>
       <c r="M300" s="19" t="n">
-        <v>-0.3296208959230267</v>
+        <v>-0.3293311187651136</v>
       </c>
       <c r="N300" s="20" t="n">
         <v>0</v>
@@ -20441,7 +20437,7 @@
       </c>
       <c r="B301" s="12" t="inlineStr">
         <is>
-          <t>UNT @ TXST</t>
+          <t>KENT @ OSU</t>
         </is>
       </c>
       <c r="C301" s="12" t="inlineStr">
@@ -20459,17 +20455,17 @@
       </c>
       <c r="F301" s="12" t="inlineStr">
         <is>
-          <t>Over 63.5</t>
+          <t>Over 59.5</t>
         </is>
       </c>
       <c r="G301" s="23" t="n">
-        <v>63.5</v>
+        <v>59.5</v>
       </c>
       <c r="H301" s="13" t="n">
         <v>-105</v>
       </c>
       <c r="I301" s="15" t="n">
-        <v>0.3419807297963899</v>
+        <v>0.3433649069662547</v>
       </c>
       <c r="J301" s="15" t="n">
         <v>0.4891657638136511</v>
@@ -20478,10 +20474,10 @@
         <v>0.5121951219512195</v>
       </c>
       <c r="L301" s="14" t="n">
-        <v>-0.09466353878471044</v>
+        <v>-0.09464292488406345</v>
       </c>
       <c r="M301" s="14" t="n">
-        <v>-0.332323337064191</v>
+        <v>-0.3296208959230267</v>
       </c>
       <c r="N301" s="15" t="n">
         <v>0</v>
@@ -20504,12 +20500,12 @@
       </c>
       <c r="B302" s="17" t="inlineStr">
         <is>
-          <t>FIU @ FAU</t>
+          <t>UNT @ TXST</t>
         </is>
       </c>
       <c r="C302" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D302" s="25" t="n">
@@ -20522,29 +20518,29 @@
       </c>
       <c r="F302" s="17" t="inlineStr">
         <is>
-          <t>Over 62.5</t>
+          <t>Over 63.5</t>
         </is>
       </c>
       <c r="G302" s="26" t="n">
-        <v>62.5</v>
+        <v>63.5</v>
       </c>
       <c r="H302" s="18" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="I302" s="20" t="n">
-        <v>0.3473978489977779</v>
+        <v>0.3419807297963899</v>
       </c>
       <c r="J302" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K302" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L302" s="19" t="n">
-        <v>-0.09469270537580907</v>
+        <v>-0.09466353878471044</v>
       </c>
       <c r="M302" s="19" t="n">
-        <v>-0.3367859246406057</v>
+        <v>-0.332323337064191</v>
       </c>
       <c r="N302" s="20" t="n">
         <v>0</v>
@@ -20557,11 +20553,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q302" s="17" t="inlineStr">
-        <is>
-          <t>raw model/market disagreement exceeds the safety limit</t>
-        </is>
-      </c>
+      <c r="Q302" s="17" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="12" t="inlineStr">
@@ -20571,7 +20563,7 @@
       </c>
       <c r="B303" s="12" t="inlineStr">
         <is>
-          <t>CLT @ APP</t>
+          <t>FIU @ FAU</t>
         </is>
       </c>
       <c r="C303" s="12" t="inlineStr">
@@ -20584,22 +20576,22 @@
       </c>
       <c r="E303" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F303" s="12" t="inlineStr">
         <is>
-          <t>APP -17.5</t>
+          <t>Over 62.5</t>
         </is>
       </c>
       <c r="G303" s="23" t="n">
-        <v>-17.5</v>
+        <v>62.5</v>
       </c>
       <c r="H303" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I303" s="15" t="n">
-        <v>0.3461203709004106</v>
+        <v>0.3473978489977779</v>
       </c>
       <c r="J303" s="15" t="n">
         <v>0.5</v>
@@ -20608,10 +20600,10 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="L303" s="14" t="n">
-        <v>-0.09470877297328392</v>
+        <v>-0.09469270537580907</v>
       </c>
       <c r="M303" s="14" t="n">
-        <v>-0.3392247464628525</v>
+        <v>-0.3367859246406057</v>
       </c>
       <c r="N303" s="15" t="n">
         <v>0</v>
@@ -20638,12 +20630,12 @@
       </c>
       <c r="B304" s="17" t="inlineStr">
         <is>
-          <t>NEV @ MTSU</t>
+          <t>CLT @ APP</t>
         </is>
       </c>
       <c r="C304" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D304" s="25" t="n">
@@ -20656,32 +20648,32 @@
       </c>
       <c r="F304" s="17" t="inlineStr">
         <is>
-          <t>NEV -4</t>
+          <t>APP -17.5</t>
         </is>
       </c>
       <c r="G304" s="26" t="n">
-        <v>4</v>
+        <v>-17.5</v>
       </c>
       <c r="H304" s="18" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="I304" s="20" t="n">
-        <v>0.3378416092268735</v>
+        <v>0.3461203709004106</v>
       </c>
       <c r="J304" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5</v>
       </c>
       <c r="K304" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L304" s="19" t="n">
-        <v>-0.09471835902390353</v>
+        <v>-0.09470877297328392</v>
       </c>
       <c r="M304" s="19" t="n">
-        <v>-0.3329496191725237</v>
+        <v>-0.3392247464628525</v>
       </c>
       <c r="N304" s="20" t="n">
-        <v>0.0219</v>
+        <v>0</v>
       </c>
       <c r="O304" s="27" t="n">
         <v>0.839</v>
@@ -20857,29 +20849,29 @@
       </c>
       <c r="F307" s="12" t="inlineStr">
         <is>
-          <t>ALA -20.5</t>
+          <t>ALA -19.5</t>
         </is>
       </c>
       <c r="G307" s="23" t="n">
-        <v>-20.5</v>
+        <v>-19.5</v>
       </c>
       <c r="H307" s="13" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I307" s="15" t="n">
-        <v>0.3112246289976402</v>
+        <v>0.3206557336886854</v>
       </c>
       <c r="J307" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K307" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L307" s="14" t="n">
-        <v>-0.09493291305090019</v>
+        <v>-0.09491113990263532</v>
       </c>
       <c r="M307" s="14" t="n">
-        <v>-0.4058438900954141</v>
+        <v>-0.393044504089274</v>
       </c>
       <c r="N307" s="15" t="n">
         <v>0</v>
@@ -21728,32 +21720,32 @@
       </c>
       <c r="F320" s="17" t="inlineStr">
         <is>
-          <t>MIA -21</t>
+          <t>MIA -20.5</t>
         </is>
       </c>
       <c r="G320" s="26" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="H320" s="18" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I320" s="20" t="n">
-        <v>0.2607217956540986</v>
+        <v>0.270235977757914</v>
       </c>
       <c r="J320" s="20" t="n">
-        <v>0.497865072587532</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K320" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L320" s="19" t="n">
-        <v>-0.09499161086113772</v>
+        <v>-0.0949906148109799</v>
       </c>
       <c r="M320" s="19" t="n">
-        <v>-0.4991443880961903</v>
+        <v>-0.4947762154960739</v>
       </c>
       <c r="N320" s="20" t="n">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="O320" s="27" t="n">
         <v>0.839</v>
@@ -22271,22 +22263,22 @@
         <v>-39.5</v>
       </c>
       <c r="H328" s="18" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I328" s="20" t="n">
-        <v>0.2551173061165828</v>
+        <v>0.2583695471747728</v>
       </c>
       <c r="J328" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K328" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L328" s="19" t="n">
-        <v>-0.09499423572849579</v>
+        <v>-0.09499424476695811</v>
       </c>
       <c r="M328" s="19" t="n">
-        <v>-0.517099384850754</v>
+        <v>-0.5169612813689031</v>
       </c>
       <c r="N328" s="20" t="n">
         <v>0</v>
@@ -43234,13 +43226,13 @@
         <v>-10.5</v>
       </c>
       <c r="J190" s="30" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="K190" s="18" t="n">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="L190" s="18" t="n">
-        <v>-440</v>
+        <v>-380</v>
       </c>
       <c r="M190" s="17" t="inlineStr">
         <is>
@@ -43280,16 +43272,16 @@
       </c>
       <c r="H191" s="12" t="inlineStr"/>
       <c r="I191" s="23" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="J191" s="29" t="n">
         <v>55.5</v>
       </c>
       <c r="K191" s="13" t="n">
-        <v>-1800</v>
+        <v>-1650</v>
       </c>
       <c r="L191" s="13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="M191" s="12" t="inlineStr">
         <is>
@@ -43609,16 +43601,16 @@
         </is>
       </c>
       <c r="I198" s="26" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J198" s="30" t="n">
         <v>51.5</v>
       </c>
       <c r="K198" s="18" t="n">
-        <v>-205</v>
+        <v>-225</v>
       </c>
       <c r="L198" s="18" t="n">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="M198" s="17" t="inlineStr">
         <is>
@@ -43987,10 +43979,10 @@
         <v>51.5</v>
       </c>
       <c r="K206" s="18" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="L206" s="18" t="n">
-        <v>-175</v>
+        <v>-170</v>
       </c>
       <c r="M206" s="17" t="inlineStr">
         <is>
@@ -44202,16 +44194,16 @@
       </c>
       <c r="H211" s="12" t="inlineStr"/>
       <c r="I211" s="23" t="n">
-        <v>-20.5</v>
+        <v>-19.5</v>
       </c>
       <c r="J211" s="29" t="n">
         <v>49.5</v>
       </c>
       <c r="K211" s="13" t="n">
-        <v>950</v>
+        <v>850</v>
       </c>
       <c r="L211" s="13" t="n">
-        <v>-1650</v>
+        <v>-1450</v>
       </c>
       <c r="M211" s="12" t="inlineStr">
         <is>
@@ -45519,7 +45511,7 @@
       </c>
       <c r="H240" s="17" t="inlineStr"/>
       <c r="I240" s="26" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J240" s="30" t="n">
         <v>50.5</v>
@@ -45780,7 +45772,7 @@
         <v>3</v>
       </c>
       <c r="J246" s="30" t="n">
-        <v>59.5</v>
+        <v>58.5</v>
       </c>
       <c r="K246" s="18" t="n">
         <v>-155</v>
@@ -45980,7 +45972,7 @@
         <v>-10</v>
       </c>
       <c r="J250" s="30" t="n">
-        <v>53.5</v>
+        <v>52.5</v>
       </c>
       <c r="K250" s="18" t="n">
         <v>310</v>
@@ -46400,10 +46392,10 @@
         <v>46.5</v>
       </c>
       <c r="K259" s="13" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="L259" s="13" t="n">
-        <v>-130</v>
+        <v>-135</v>
       </c>
       <c r="M259" s="12" t="inlineStr">
         <is>

--- a/NCAAF_Edge_Model.xlsx
+++ b/NCAAF_Edge_Model.xlsx
@@ -642,7 +642,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-15T03:05:08+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
+          <t>Generated 2026-09-15T13:09:14+00:00 from live ESPN data. This file is a snapshot, not the model. Re-run the pipeline to refresh it.</t>
         </is>
       </c>
     </row>
@@ -2201,22 +2201,22 @@
       </c>
       <c r="G16" s="26" t="n"/>
       <c r="H16" s="18" t="n">
-        <v>1700</v>
+        <v>1500</v>
       </c>
       <c r="I16" s="20" t="n">
-        <v>0.3198960198651413</v>
+        <v>0.3232063063373707</v>
       </c>
       <c r="J16" s="20" t="n">
-        <v>0.05373831775700934</v>
+        <v>0.06035889070146819</v>
       </c>
       <c r="K16" s="20" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.0625</v>
       </c>
       <c r="L16" s="19" t="n">
         <v>0.095</v>
       </c>
       <c r="M16" s="19" t="n">
-        <v>4.758128357572543</v>
+        <v>4.171300901397931</v>
       </c>
       <c r="N16" s="20" t="n">
         <v>0</v>
@@ -3153,12 +3153,12 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>GAST @ UCF</t>
+          <t>LT @ BAY</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D31" s="22" t="n">
@@ -3171,27 +3171,27 @@
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>GAST ML</t>
+          <t>LT ML</t>
         </is>
       </c>
       <c r="G31" s="23" t="n"/>
       <c r="H31" s="13" t="n">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>0.2459347859855046</v>
+        <v>0.2320729380512567</v>
       </c>
       <c r="J31" s="15" t="n">
-        <v>0.1130434782608696</v>
+        <v>0.1066176470588235</v>
       </c>
       <c r="K31" s="15" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="L31" s="14" t="n">
-        <v>0.09499999999660841</v>
+        <v>0.09499999999668654</v>
       </c>
       <c r="M31" s="14" t="n">
-        <v>1.090445680876789</v>
+        <v>1.088656442461311</v>
       </c>
       <c r="N31" s="15" t="n">
         <v>0</v>
@@ -3218,12 +3218,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>LT @ BAY</t>
+          <t>GAST @ UCF</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D32" s="25" t="n">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>LT ML</t>
+          <t>GAST ML</t>
         </is>
       </c>
       <c r="G32" s="26" t="n"/>
@@ -3244,7 +3244,7 @@
         <v>750</v>
       </c>
       <c r="I32" s="20" t="n">
-        <v>0.2352858536522798</v>
+        <v>0.2459347859855046</v>
       </c>
       <c r="J32" s="20" t="n">
         <v>0.1130434782608696</v>
@@ -3253,10 +3253,10 @@
         <v>0.1176470588235294</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>0.09499999997535674</v>
+        <v>0.09499999999660841</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>0.9999297560443785</v>
+        <v>1.090445680876789</v>
       </c>
       <c r="N32" s="20" t="n">
         <v>0</v>
@@ -3306,22 +3306,22 @@
       </c>
       <c r="G33" s="23" t="n"/>
       <c r="H33" s="13" t="n">
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>0.2102331438522113</v>
+        <v>0.2076847802426594</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>0.101141924959217</v>
+        <v>0.096045197740113</v>
       </c>
       <c r="K33" s="15" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.1</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>0.09499999997387173</v>
+        <v>0.09499999999552079</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>0.997214866596007</v>
+        <v>1.076847802426594</v>
       </c>
       <c r="N33" s="15" t="n">
         <v>0</v>
@@ -4548,12 +4548,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>UNM @ OU</t>
+          <t>AKR @ MINN</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -4566,29 +4566,29 @@
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>UNM +22.5</t>
+          <t>AKR +24.5</t>
         </is>
       </c>
       <c r="G52" s="26" t="n">
-        <v>-22.5</v>
+        <v>-24.5</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I52" s="20" t="n">
-        <v>0.7104303180891165</v>
+        <v>0.7328064074310523</v>
       </c>
       <c r="J52" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5091659028414299</v>
       </c>
       <c r="K52" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L52" s="19" t="n">
-        <v>0.09497923740891739</v>
+        <v>0.09498168439254574</v>
       </c>
       <c r="M52" s="19" t="n">
-        <v>0.368236168171632</v>
+        <v>0.3989940505501908</v>
       </c>
       <c r="N52" s="20" t="n">
         <v>0</v>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>USU @ UTAH</t>
+          <t>UNM @ OU</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D53" s="22" t="n">
@@ -4633,29 +4633,29 @@
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>USU +28.5</t>
+          <t>UNM +22.5</t>
         </is>
       </c>
       <c r="G53" s="23" t="n">
-        <v>-28.5</v>
+        <v>-22.5</v>
       </c>
       <c r="H53" s="13" t="n">
-        <v>-118</v>
+        <v>-108</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>0.7395037347650635</v>
+        <v>0.7104303180891165</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K53" s="15" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L53" s="14" t="n">
-        <v>0.09497745904175824</v>
+        <v>0.09497923740891739</v>
       </c>
       <c r="M53" s="14" t="n">
-        <v>0.3662018150744393</v>
+        <v>0.368236168171632</v>
       </c>
       <c r="N53" s="15" t="n">
         <v>0</v>
@@ -4682,12 +4682,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>AKR @ MINN</t>
+          <t>USU @ UTAH</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -4700,17 +4700,17 @@
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>AKR +24.5</t>
+          <t>USU +28.5</t>
         </is>
       </c>
       <c r="G54" s="26" t="n">
-        <v>-24.5</v>
+        <v>-28.5</v>
       </c>
       <c r="H54" s="18" t="n">
         <v>-118</v>
       </c>
       <c r="I54" s="20" t="n">
-        <v>0.7369055188684724</v>
+        <v>0.7395037347650635</v>
       </c>
       <c r="J54" s="20" t="n">
         <v>0.5173641257162701</v>
@@ -4719,10 +4719,10 @@
         <v>0.5412844036697247</v>
       </c>
       <c r="L54" s="19" t="n">
-        <v>0.09497494564547271</v>
+        <v>0.09497745904175824</v>
       </c>
       <c r="M54" s="19" t="n">
-        <v>0.3614017212993812</v>
+        <v>0.3662018150744393</v>
       </c>
       <c r="N54" s="20" t="n">
         <v>0</v>
@@ -4906,22 +4906,22 @@
         <v>-20.5</v>
       </c>
       <c r="H57" s="13" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>0.7042893350401672</v>
+        <v>0.7021244580051829</v>
       </c>
       <c r="J57" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K57" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L57" s="14" t="n">
-        <v>0.09495496351110942</v>
+        <v>0.09496175264016267</v>
       </c>
       <c r="M57" s="14" t="n">
-        <v>0.3331190984688879</v>
+        <v>0.3708144180101189</v>
       </c>
       <c r="N57" s="15" t="n">
         <v>0</v>
@@ -5015,12 +5015,12 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>FSU @ ALA</t>
+          <t>LT @ BAY</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D59" s="22" t="n">
@@ -5033,29 +5033,29 @@
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>FSU +19.5</t>
+          <t>LT +19.5</t>
         </is>
       </c>
       <c r="G59" s="23" t="n">
         <v>-19.5</v>
       </c>
       <c r="H59" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>0.6793442663113145</v>
+        <v>0.6948752167385044</v>
       </c>
       <c r="J59" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K59" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v>0.0949222753312902</v>
+        <v>0.09493329100288043</v>
       </c>
       <c r="M59" s="14" t="n">
-        <v>0.3083667351180872</v>
+        <v>0.3152995173978832</v>
       </c>
       <c r="N59" s="15" t="n">
         <v>0</v>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>TULN @ KSU</t>
+          <t>FSU @ ALA</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -5100,29 +5100,29 @@
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>TULN +20.5</t>
+          <t>FSU +19.5</t>
         </is>
       </c>
       <c r="G60" s="26" t="n">
-        <v>-20.5</v>
+        <v>-19.5</v>
       </c>
       <c r="H60" s="18" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I60" s="20" t="n">
-        <v>0.6955628426805947</v>
+        <v>0.681509143346299</v>
       </c>
       <c r="J60" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5</v>
       </c>
       <c r="K60" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L60" s="19" t="n">
-        <v>0.09490619643988871</v>
+        <v>0.09490891350155506</v>
       </c>
       <c r="M60" s="19" t="n">
-        <v>0.3004000971854595</v>
+        <v>0.3010629100247526</v>
       </c>
       <c r="N60" s="20" t="n">
         <v>0</v>
@@ -5149,12 +5149,12 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>WMU @ RICE</t>
+          <t>TULN @ KSU</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D61" s="22" t="n">
@@ -5167,29 +5167,29 @@
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>RICE +9.5</t>
+          <t>TULN +20.5</t>
         </is>
       </c>
       <c r="G61" s="23" t="n">
-        <v>9.5</v>
+        <v>-20.5</v>
       </c>
       <c r="H61" s="13" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>0.6747946529062397</v>
+        <v>0.6955628426805947</v>
       </c>
       <c r="J61" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K61" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L61" s="14" t="n">
-        <v>0.09490571505817344</v>
+        <v>0.09490619643988871</v>
       </c>
       <c r="M61" s="14" t="n">
-        <v>0.2996045167083137</v>
+        <v>0.3004000971854595</v>
       </c>
       <c r="N61" s="15" t="n">
         <v>0</v>
@@ -5216,12 +5216,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>LT @ BAY</t>
+          <t>WMU @ RICE</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -5234,29 +5234,29 @@
       </c>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>LT +19.5</t>
+          <t>RICE +9.5</t>
         </is>
       </c>
       <c r="G62" s="26" t="n">
-        <v>-19.5</v>
+        <v>9.5</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>-118</v>
+        <v>-108</v>
       </c>
       <c r="I62" s="20" t="n">
-        <v>0.701392402561655</v>
+        <v>0.6747946529062397</v>
       </c>
       <c r="J62" s="20" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K62" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L62" s="19" t="n">
-        <v>0.09489375758755755</v>
+        <v>0.09490571505817344</v>
       </c>
       <c r="M62" s="19" t="n">
-        <v>0.2957927437155998</v>
+        <v>0.2996045167083137</v>
       </c>
       <c r="N62" s="20" t="n">
         <v>0</v>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>UNC @ CLEM</t>
+          <t>ASU @ KU</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
@@ -7428,37 +7428,37 @@
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>KU +6</t>
         </is>
       </c>
       <c r="G95" s="23" t="n">
-        <v>44.5</v>
+        <v>6</v>
       </c>
       <c r="H95" s="13" t="n">
-        <v>-102</v>
+        <v>-112</v>
       </c>
       <c r="I95" s="15" t="n">
-        <v>0.5635012337599586</v>
+        <v>0.5854883267574933</v>
       </c>
       <c r="J95" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K95" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L95" s="14" t="n">
-        <v>0.08957667652072997</v>
+        <v>0.08879139890596684</v>
       </c>
       <c r="M95" s="14" t="n">
-        <v>0.1159534237207025</v>
+        <v>0.1053772486862944</v>
       </c>
       <c r="N95" s="15" t="n">
-        <v>0</v>
+        <v>0.0265</v>
       </c>
       <c r="O95" s="24" t="n">
         <v>0.839</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="Q95" s="12" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -7482,12 +7482,12 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>ASU @ KU</t>
+          <t>FIU @ FAU</t>
         </is>
       </c>
       <c r="C96" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D96" s="25" t="n">
@@ -7495,37 +7495,35 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F96" s="17" t="inlineStr">
         <is>
-          <t>KU +6</t>
-        </is>
-      </c>
-      <c r="G96" s="26" t="n">
-        <v>6</v>
-      </c>
+          <t>FIU ML</t>
+        </is>
+      </c>
+      <c r="G96" s="26" t="n"/>
       <c r="H96" s="18" t="n">
-        <v>-112</v>
+        <v>225</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>0.5854883267574933</v>
+        <v>0.3410405987539735</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.2949668357393679</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="L96" s="19" t="n">
-        <v>0.08879139890596684</v>
+        <v>0.08816556722163803</v>
       </c>
       <c r="M96" s="19" t="n">
-        <v>0.1053772486862944</v>
+        <v>0.1083819459504141</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>0.0265</v>
+        <v>0</v>
       </c>
       <c r="O96" s="27" t="n">
         <v>0.839</v>
@@ -7537,7 +7535,7 @@
       </c>
       <c r="Q96" s="17" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -7616,12 +7614,12 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>GASO @ JVST</t>
+          <t>UNC @ CLEM</t>
         </is>
       </c>
       <c r="C98" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D98" s="25" t="n">
@@ -7634,29 +7632,29 @@
       </c>
       <c r="F98" s="17" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="G98" s="26" t="n">
-        <v>52.5</v>
+        <v>44.5</v>
       </c>
       <c r="H98" s="18" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I98" s="20" t="n">
-        <v>0.5592588257221088</v>
+        <v>0.5700184195831093</v>
       </c>
       <c r="J98" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K98" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L98" s="19" t="n">
-        <v>0.08613095438643457</v>
+        <v>0.08725080159618478</v>
       </c>
       <c r="M98" s="19" t="n">
-        <v>0.09188627879078393</v>
+        <v>0.09781325253043271</v>
       </c>
       <c r="N98" s="20" t="n">
         <v>0</v>
@@ -7683,12 +7681,12 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>UAB @ UL</t>
+          <t>GASO @ JVST</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D99" s="22" t="n">
@@ -7701,29 +7699,29 @@
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>Under 56.5</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="G99" s="23" t="n">
-        <v>56.5</v>
+        <v>52.5</v>
       </c>
       <c r="H99" s="13" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I99" s="15" t="n">
-        <v>0.5606183235247334</v>
+        <v>0.5592588257221088</v>
       </c>
       <c r="J99" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K99" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L99" s="14" t="n">
-        <v>0.08367486886758746</v>
+        <v>0.08613095438643457</v>
       </c>
       <c r="M99" s="14" t="n">
-        <v>0.07970936382541249</v>
+        <v>0.09188627879078393</v>
       </c>
       <c r="N99" s="15" t="n">
         <v>0</v>
@@ -7750,12 +7748,12 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>ARST @ TCU</t>
+          <t>EMU @ WIS</t>
         </is>
       </c>
       <c r="C100" s="17" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-19 16:30</t>
         </is>
       </c>
       <c r="D100" s="25" t="n">
@@ -7768,29 +7766,29 @@
       </c>
       <c r="F100" s="17" t="inlineStr">
         <is>
-          <t>Under 55.5</t>
+          <t>Over 45.5</t>
         </is>
       </c>
       <c r="G100" s="26" t="n">
-        <v>55.5</v>
+        <v>45.5</v>
       </c>
       <c r="H100" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>0.5646759927056134</v>
+        <v>0.5643978071882442</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L100" s="19" t="n">
-        <v>0.08329254278965623</v>
+        <v>0.08526841137980082</v>
       </c>
       <c r="M100" s="19" t="n">
-        <v>0.07801780425617122</v>
+        <v>0.08698836939958143</v>
       </c>
       <c r="N100" s="20" t="n">
         <v>0</v>
@@ -7817,12 +7815,12 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>EMU @ WIS</t>
+          <t>WVU @ UVA</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 16:30</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D101" s="22" t="n">
@@ -7835,29 +7833,29 @@
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>Over 45.5</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="G101" s="23" t="n">
-        <v>45.5</v>
+        <v>53.5</v>
       </c>
       <c r="H101" s="13" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I101" s="15" t="n">
-        <v>0.568727561258213</v>
+        <v>0.5625110917058415</v>
       </c>
       <c r="J101" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K101" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L101" s="14" t="n">
-        <v>0.08290217412435039</v>
+        <v>0.08450134139163748</v>
       </c>
       <c r="M101" s="14" t="n">
-        <v>0.07652002666733182</v>
+        <v>0.08335469513717619</v>
       </c>
       <c r="N101" s="15" t="n">
         <v>0</v>
@@ -7872,7 +7870,7 @@
       </c>
       <c r="Q101" s="12" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -7884,12 +7882,12 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>UNM @ OU</t>
+          <t>UAB @ UL</t>
         </is>
       </c>
       <c r="C102" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D102" s="25" t="n">
@@ -7902,29 +7900,29 @@
       </c>
       <c r="F102" s="17" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>Under 56.5</t>
         </is>
       </c>
       <c r="G102" s="26" t="n">
-        <v>46.5</v>
+        <v>56.5</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I102" s="20" t="n">
-        <v>0.5757334679148104</v>
+        <v>0.5606183235247334</v>
       </c>
       <c r="J102" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K102" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L102" s="19" t="n">
-        <v>0.08274761209707551</v>
+        <v>0.08367486886758746</v>
       </c>
       <c r="M102" s="19" t="n">
-        <v>0.07637126610160205</v>
+        <v>0.07970936382541249</v>
       </c>
       <c r="N102" s="20" t="n">
         <v>0</v>
@@ -7951,7 +7949,7 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>UAB @ UL</t>
+          <t>ARST @ TCU</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
@@ -7964,32 +7962,34 @@
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>UAB ML</t>
-        </is>
-      </c>
-      <c r="G103" s="23" t="n"/>
+          <t>Under 55.5</t>
+        </is>
+      </c>
+      <c r="G103" s="23" t="n">
+        <v>55.5</v>
+      </c>
       <c r="H103" s="13" t="n">
-        <v>250</v>
+        <v>-110</v>
       </c>
       <c r="I103" s="15" t="n">
-        <v>0.3059736485675911</v>
+        <v>0.5646759927056134</v>
       </c>
       <c r="J103" s="15" t="n">
-        <v>0.274247491638796</v>
+        <v>0.5</v>
       </c>
       <c r="K103" s="15" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L103" s="14" t="n">
-        <v>0.07970342793993671</v>
+        <v>0.08329254278965623</v>
       </c>
       <c r="M103" s="14" t="n">
-        <v>0.070907769986569</v>
+        <v>0.07801780425617122</v>
       </c>
       <c r="N103" s="15" t="n">
         <v>0</v>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="Q103" s="12" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>FIU @ FAU</t>
+          <t>UNM @ OU</t>
         </is>
       </c>
       <c r="C104" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D104" s="25" t="n">
@@ -8029,32 +8029,34 @@
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F104" s="17" t="inlineStr">
         <is>
-          <t>FIU ML</t>
-        </is>
-      </c>
-      <c r="G104" s="26" t="n"/>
+          <t>Over 46.5</t>
+        </is>
+      </c>
+      <c r="G104" s="26" t="n">
+        <v>46.5</v>
+      </c>
       <c r="H104" s="18" t="n">
-        <v>205</v>
+        <v>-115</v>
       </c>
       <c r="I104" s="20" t="n">
-        <v>0.3508605516708063</v>
+        <v>0.5757334679148104</v>
       </c>
       <c r="J104" s="20" t="n">
-        <v>0.3146067415730336</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K104" s="20" t="n">
-        <v>0.3278688524590164</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L104" s="19" t="n">
-        <v>0.07956992486452395</v>
+        <v>0.08274761209707551</v>
       </c>
       <c r="M104" s="19" t="n">
-        <v>0.07012468259595916</v>
+        <v>0.07637126610160205</v>
       </c>
       <c r="N104" s="20" t="n">
         <v>0</v>
@@ -8081,12 +8083,12 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>UK @ TA&amp;M</t>
+          <t>UAB @ UL</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D105" s="22" t="n">
@@ -8094,34 +8096,32 @@
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
-        </is>
-      </c>
-      <c r="G105" s="23" t="n">
-        <v>49.5</v>
-      </c>
+          <t>UAB ML</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="n"/>
       <c r="H105" s="13" t="n">
-        <v>-110</v>
+        <v>250</v>
       </c>
       <c r="I105" s="15" t="n">
-        <v>0.5570690890896691</v>
+        <v>0.3059736485675911</v>
       </c>
       <c r="J105" s="15" t="n">
-        <v>0.5</v>
+        <v>0.274247491638796</v>
       </c>
       <c r="K105" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="L105" s="14" t="n">
-        <v>0.07923928370038286</v>
+        <v>0.07970342793993671</v>
       </c>
       <c r="M105" s="14" t="n">
-        <v>0.06349553371664118</v>
+        <v>0.070907769986569</v>
       </c>
       <c r="N105" s="15" t="n">
         <v>0</v>
@@ -8148,12 +8148,12 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>SMU @ LOU</t>
+          <t>FIU @ FAU</t>
         </is>
       </c>
       <c r="C106" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D106" s="25" t="n">
@@ -8161,20 +8161,22 @@
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F106" s="17" t="inlineStr">
         <is>
-          <t>LOU ML</t>
-        </is>
-      </c>
-      <c r="G106" s="26" t="n"/>
+          <t>FIU +7</t>
+        </is>
+      </c>
+      <c r="G106" s="26" t="n">
+        <v>-7</v>
+      </c>
       <c r="H106" s="18" t="n">
         <v>-115</v>
       </c>
       <c r="I106" s="20" t="n">
-        <v>0.5669673572258898</v>
+        <v>0.5685941154911228</v>
       </c>
       <c r="J106" s="20" t="n">
         <v>0.5108342361863488</v>
@@ -8183,13 +8185,13 @@
         <v>0.5348837209302325</v>
       </c>
       <c r="L106" s="19" t="n">
-        <v>0.07789591719715193</v>
+        <v>0.07891110451166122</v>
       </c>
       <c r="M106" s="19" t="n">
-        <v>0.05998245046579376</v>
+        <v>0.05991040634747986</v>
       </c>
       <c r="N106" s="20" t="n">
-        <v>0</v>
+        <v>0.0494</v>
       </c>
       <c r="O106" s="27" t="n">
         <v>0.839</v>
@@ -8201,7 +8203,7 @@
       </c>
       <c r="Q106" s="17" t="inlineStr">
         <is>
-          <t>outside the top 10 plays for this week</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -8213,12 +8215,12 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>FIU @ FAU</t>
+          <t>SMU @ LOU</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D107" s="22" t="n">
@@ -8226,37 +8228,35 @@
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>FIU +7</t>
-        </is>
-      </c>
-      <c r="G107" s="23" t="n">
-        <v>-7</v>
-      </c>
+          <t>LOU ML</t>
+        </is>
+      </c>
+      <c r="G107" s="23" t="n"/>
       <c r="H107" s="13" t="n">
-        <v>-118</v>
+        <v>-115</v>
       </c>
       <c r="I107" s="15" t="n">
-        <v>0.5718590602560836</v>
+        <v>0.5669673572258898</v>
       </c>
       <c r="J107" s="15" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K107" s="15" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L107" s="14" t="n">
-        <v>0.07634413092525391</v>
+        <v>0.07789591719715193</v>
       </c>
       <c r="M107" s="14" t="n">
-        <v>0.05369500461115586</v>
+        <v>0.05998245046579376</v>
       </c>
       <c r="N107" s="15" t="n">
-        <v>0.0494</v>
+        <v>0</v>
       </c>
       <c r="O107" s="24" t="n">
         <v>0.839</v>
@@ -8268,7 +8268,7 @@
       </c>
       <c r="Q107" s="12" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>outside the top 10 plays for this week</t>
         </is>
       </c>
     </row>
@@ -8345,12 +8345,12 @@
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>MIA @ WAKE</t>
+          <t>UAB @ UL</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>2026-09-18 23:30</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D109" s="22" t="n">
@@ -8358,34 +8358,34 @@
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>Under 55.5</t>
+          <t>UAB +7.5</t>
         </is>
       </c>
       <c r="G109" s="23" t="n">
-        <v>55.5</v>
+        <v>-7.5</v>
       </c>
       <c r="H109" s="13" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I109" s="15" t="n">
-        <v>0.5553964598597521</v>
+        <v>0.5472095939894825</v>
       </c>
       <c r="J109" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K109" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L109" s="14" t="n">
-        <v>0.07485010906805592</v>
+        <v>0.07210638064482937</v>
       </c>
       <c r="M109" s="14" t="n">
-        <v>0.05128615616310217</v>
+        <v>0.04467286125264858</v>
       </c>
       <c r="N109" s="15" t="n">
         <v>0</v>
@@ -8398,11 +8398,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q109" s="12" t="inlineStr">
-        <is>
-          <t>outside the top 10 plays for this week</t>
-        </is>
-      </c>
+      <c r="Q109" s="12" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="17" t="inlineStr">
@@ -8412,12 +8408,12 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>WVU @ UVA</t>
+          <t>MIA @ WAKE</t>
         </is>
       </c>
       <c r="C110" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-18 23:30</t>
         </is>
       </c>
       <c r="D110" s="25" t="n">
@@ -8430,29 +8426,29 @@
       </c>
       <c r="F110" s="17" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>Under 55.5</t>
         </is>
       </c>
       <c r="G110" s="26" t="n">
-        <v>52.5</v>
+        <v>55.5</v>
       </c>
       <c r="H110" s="18" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I110" s="20" t="n">
-        <v>0.5433307733251187</v>
+        <v>0.5586487009179421</v>
       </c>
       <c r="J110" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K110" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L110" s="19" t="n">
-        <v>0.07283150494346662</v>
+        <v>0.07175717001437433</v>
       </c>
       <c r="M110" s="19" t="n">
-        <v>0.04641482270022856</v>
+        <v>0.04443017997702192</v>
       </c>
       <c r="N110" s="20" t="n">
         <v>0</v>
@@ -8465,11 +8461,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q110" s="17" t="inlineStr">
-        <is>
-          <t>correlated with a stronger play on the same game</t>
-        </is>
-      </c>
+      <c r="Q110" s="17" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
@@ -8479,12 +8471,12 @@
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>UAB @ UL</t>
+          <t>SMU @ LOU</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D111" s="22" t="n">
@@ -8497,29 +8489,29 @@
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>UAB +7.5</t>
+          <t>LOU -1.5</t>
         </is>
       </c>
       <c r="G111" s="23" t="n">
-        <v>-7.5</v>
+        <v>-1.5</v>
       </c>
       <c r="H111" s="13" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I111" s="15" t="n">
-        <v>0.5472095939894825</v>
+        <v>0.541493713325953</v>
       </c>
       <c r="J111" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K111" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L111" s="14" t="n">
-        <v>0.07210638064482937</v>
+        <v>0.07125732823047302</v>
       </c>
       <c r="M111" s="14" t="n">
-        <v>0.04467286125264858</v>
+        <v>0.04287678122035388</v>
       </c>
       <c r="N111" s="15" t="n">
         <v>0</v>
@@ -8542,12 +8534,12 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>SMU @ LOU</t>
+          <t>AKR @ MINN</t>
         </is>
       </c>
       <c r="C112" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D112" s="25" t="n">
@@ -8555,34 +8547,34 @@
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F112" s="17" t="inlineStr">
         <is>
-          <t>LOU -1.5</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="G112" s="26" t="n">
-        <v>-1.5</v>
+        <v>49.5</v>
       </c>
       <c r="H112" s="18" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I112" s="20" t="n">
-        <v>0.541493713325953</v>
+        <v>0.5342290726844449</v>
       </c>
       <c r="J112" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K112" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L112" s="19" t="n">
-        <v>0.07125732823047302</v>
+        <v>0.07111494203374541</v>
       </c>
       <c r="M112" s="19" t="n">
-        <v>0.04287678122035388</v>
+        <v>0.04301866571724955</v>
       </c>
       <c r="N112" s="20" t="n">
         <v>0</v>
@@ -8605,12 +8597,12 @@
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>AKR @ MINN</t>
+          <t>ECU @ ODU</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D113" s="22" t="n">
@@ -8618,37 +8610,37 @@
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>ODU -3</t>
         </is>
       </c>
       <c r="G113" s="23" t="n">
-        <v>49.5</v>
+        <v>-3</v>
       </c>
       <c r="H113" s="13" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I113" s="15" t="n">
-        <v>0.5342290726844449</v>
+        <v>0.5412771879339008</v>
       </c>
       <c r="J113" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K113" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L113" s="14" t="n">
-        <v>0.07111494203374541</v>
+        <v>0.07106560418871048</v>
       </c>
       <c r="M113" s="14" t="n">
-        <v>0.04301866571724955</v>
+        <v>0.03992067514679936</v>
       </c>
       <c r="N113" s="15" t="n">
-        <v>0</v>
+        <v>0.0598</v>
       </c>
       <c r="O113" s="24" t="n">
         <v>0.839</v>
@@ -8668,12 +8660,12 @@
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>ECU @ ODU</t>
+          <t>WYO @ CMU</t>
         </is>
       </c>
       <c r="C114" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 17:00</t>
         </is>
       </c>
       <c r="D114" s="25" t="n">
@@ -8686,32 +8678,32 @@
       </c>
       <c r="F114" s="17" t="inlineStr">
         <is>
-          <t>ODU -3</t>
+          <t>CMU -1.5</t>
         </is>
       </c>
       <c r="G114" s="26" t="n">
-        <v>-3</v>
+        <v>-1.5</v>
       </c>
       <c r="H114" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I114" s="20" t="n">
-        <v>0.5412771879339008</v>
+        <v>0.5494763879953697</v>
       </c>
       <c r="J114" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K114" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L114" s="19" t="n">
-        <v>0.07106560418871048</v>
+        <v>0.06994614391061148</v>
       </c>
       <c r="M114" s="19" t="n">
-        <v>0.03992067514679936</v>
+        <v>0.04008030584837829</v>
       </c>
       <c r="N114" s="20" t="n">
-        <v>0.0598</v>
+        <v>0</v>
       </c>
       <c r="O114" s="27" t="n">
         <v>0.839</v>
@@ -8731,12 +8723,12 @@
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>WYO @ CMU</t>
+          <t>JMU @ SDSU</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 17:00</t>
+          <t>2026-09-20 02:00</t>
         </is>
       </c>
       <c r="D115" s="22" t="n">
@@ -8744,34 +8736,32 @@
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>CMU -1.5</t>
-        </is>
-      </c>
-      <c r="G115" s="23" t="n">
-        <v>-1.5</v>
-      </c>
+          <t>SDSU ML</t>
+        </is>
+      </c>
+      <c r="G115" s="23" t="n"/>
       <c r="H115" s="13" t="n">
-        <v>-112</v>
+        <v>-135</v>
       </c>
       <c r="I115" s="15" t="n">
-        <v>0.5494763879953697</v>
+        <v>0.6005963827493461</v>
       </c>
       <c r="J115" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.551441114716549</v>
       </c>
       <c r="K115" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.574468085106383</v>
       </c>
       <c r="L115" s="14" t="n">
-        <v>0.06994614391061148</v>
+        <v>0.06977235009208492</v>
       </c>
       <c r="M115" s="14" t="n">
-        <v>0.04008030584837829</v>
+        <v>0.04548259219330619</v>
       </c>
       <c r="N115" s="15" t="n">
         <v>0</v>
@@ -8794,12 +8784,12 @@
       </c>
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>JMU @ SDSU</t>
+          <t>FSU @ ALA</t>
         </is>
       </c>
       <c r="C116" s="17" t="inlineStr">
         <is>
-          <t>2026-09-20 02:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D116" s="25" t="n">
@@ -8807,32 +8797,34 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F116" s="17" t="inlineStr">
         <is>
-          <t>SDSU ML</t>
-        </is>
-      </c>
-      <c r="G116" s="26" t="n"/>
+          <t>Over 49.5</t>
+        </is>
+      </c>
+      <c r="G116" s="26" t="n">
+        <v>49.5</v>
+      </c>
       <c r="H116" s="18" t="n">
-        <v>-135</v>
+        <v>-108</v>
       </c>
       <c r="I116" s="20" t="n">
-        <v>0.6005963827493461</v>
+        <v>0.5394353197399611</v>
       </c>
       <c r="J116" s="20" t="n">
-        <v>0.551441114716549</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K116" s="20" t="n">
-        <v>0.574468085106383</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L116" s="19" t="n">
-        <v>0.06977235009208492</v>
+        <v>0.06938064358534374</v>
       </c>
       <c r="M116" s="19" t="n">
-        <v>0.04548259219330619</v>
+        <v>0.03891246764733247</v>
       </c>
       <c r="N116" s="20" t="n">
         <v>0</v>
@@ -8855,12 +8847,12 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>FSU @ ALA</t>
+          <t>ECU @ ODU</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D117" s="22" t="n">
@@ -8868,34 +8860,32 @@
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
-        </is>
-      </c>
-      <c r="G117" s="23" t="n">
-        <v>49.5</v>
-      </c>
+          <t>ODU ML</t>
+        </is>
+      </c>
+      <c r="G117" s="23" t="n"/>
       <c r="H117" s="13" t="n">
-        <v>-108</v>
+        <v>-148</v>
       </c>
       <c r="I117" s="15" t="n">
-        <v>0.5394353197399611</v>
+        <v>0.6220606248236609</v>
       </c>
       <c r="J117" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5720596355604638</v>
       </c>
       <c r="K117" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5967741935483871</v>
       </c>
       <c r="L117" s="14" t="n">
-        <v>0.06938064358534374</v>
+        <v>0.06896271628100531</v>
       </c>
       <c r="M117" s="14" t="n">
-        <v>0.03891246764733247</v>
+        <v>0.04237185781262087</v>
       </c>
       <c r="N117" s="15" t="n">
         <v>0</v>
@@ -8918,12 +8908,12 @@
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>ECU @ ODU</t>
+          <t>COLO @ NU</t>
         </is>
       </c>
       <c r="C118" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D118" s="25" t="n">
@@ -8931,38 +8921,40 @@
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F118" s="17" t="inlineStr">
         <is>
-          <t>ODU ML</t>
-        </is>
-      </c>
-      <c r="G118" s="26" t="n"/>
+          <t>Over 48.5</t>
+        </is>
+      </c>
+      <c r="G118" s="26" t="n">
+        <v>48.5</v>
+      </c>
       <c r="H118" s="18" t="n">
-        <v>-148</v>
+        <v>-115</v>
       </c>
       <c r="I118" s="20" t="n">
-        <v>0.6220606248236609</v>
+        <v>0.554790475724132</v>
       </c>
       <c r="J118" s="20" t="n">
-        <v>0.5720596355604638</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K118" s="20" t="n">
-        <v>0.5967741935483871</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L118" s="19" t="n">
-        <v>0.06896271628100531</v>
+        <v>0.06831400400388417</v>
       </c>
       <c r="M118" s="19" t="n">
-        <v>0.04237185781262087</v>
+        <v>0.03721697635381194</v>
       </c>
       <c r="N118" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O118" s="27" t="n">
-        <v>0.839</v>
+        <v>0.725</v>
       </c>
       <c r="P118" s="17" t="inlineStr">
         <is>
@@ -8979,12 +8971,12 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>COLO @ NU</t>
+          <t>CONN @ USM</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D119" s="22" t="n">
@@ -8997,35 +8989,35 @@
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>Under 54.5</t>
         </is>
       </c>
       <c r="G119" s="23" t="n">
-        <v>48.5</v>
+        <v>54.5</v>
       </c>
       <c r="H119" s="13" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I119" s="15" t="n">
-        <v>0.554790475724132</v>
+        <v>0.5374812731816272</v>
       </c>
       <c r="J119" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K119" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L119" s="14" t="n">
-        <v>0.06831400400388417</v>
+        <v>0.06748471401583311</v>
       </c>
       <c r="M119" s="14" t="n">
-        <v>0.03721697635381194</v>
+        <v>0.0351491187201709</v>
       </c>
       <c r="N119" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O119" s="24" t="n">
-        <v>0.725</v>
+        <v>0.839</v>
       </c>
       <c r="P119" s="12" t="inlineStr">
         <is>
@@ -9042,12 +9034,12 @@
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>CONN @ USM</t>
+          <t>JMU @ SDSU</t>
         </is>
       </c>
       <c r="C120" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-20 02:00</t>
         </is>
       </c>
       <c r="D120" s="25" t="n">
@@ -9055,34 +9047,34 @@
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F120" s="17" t="inlineStr">
         <is>
-          <t>Under 54.5</t>
+          <t>SDSU -2.5</t>
         </is>
       </c>
       <c r="G120" s="26" t="n">
-        <v>54.5</v>
+        <v>-2.5</v>
       </c>
       <c r="H120" s="18" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I120" s="20" t="n">
-        <v>0.5374812731816272</v>
+        <v>0.5462264199872242</v>
       </c>
       <c r="J120" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K120" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L120" s="19" t="n">
-        <v>0.06748471401583311</v>
+        <v>0.06684526818819336</v>
       </c>
       <c r="M120" s="19" t="n">
-        <v>0.0351491187201709</v>
+        <v>0.03392858069010285</v>
       </c>
       <c r="N120" s="20" t="n">
         <v>0</v>
@@ -9105,12 +9097,12 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>JMU @ SDSU</t>
+          <t>HOU @ TTU</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 02:00</t>
+          <t>2026-09-19 00:00</t>
         </is>
       </c>
       <c r="D121" s="22" t="n">
@@ -9123,29 +9115,29 @@
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>SDSU -2.5</t>
+          <t>HOU +7.5</t>
         </is>
       </c>
       <c r="G121" s="23" t="n">
-        <v>-2.5</v>
+        <v>-7.5</v>
       </c>
       <c r="H121" s="13" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I121" s="15" t="n">
-        <v>0.5462264199872242</v>
+        <v>0.5366533409410109</v>
       </c>
       <c r="J121" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K121" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L121" s="14" t="n">
-        <v>0.06684526818819336</v>
+        <v>0.06664688686685612</v>
       </c>
       <c r="M121" s="14" t="n">
-        <v>0.03392858069010285</v>
+        <v>0.0335545825530581</v>
       </c>
       <c r="N121" s="15" t="n">
         <v>0</v>
@@ -9168,12 +9160,12 @@
       </c>
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>HOU @ TTU</t>
+          <t>FLA @ AUB</t>
         </is>
       </c>
       <c r="C122" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 00:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D122" s="25" t="n">
@@ -9181,34 +9173,34 @@
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F122" s="17" t="inlineStr">
         <is>
-          <t>HOU +7.5</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="G122" s="26" t="n">
-        <v>-7.5</v>
+        <v>53.5</v>
       </c>
       <c r="H122" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I122" s="20" t="n">
-        <v>0.5366533409410109</v>
+        <v>0.5385486876252762</v>
       </c>
       <c r="J122" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4978050921861282</v>
       </c>
       <c r="K122" s="20" t="n">
         <v>0.5192307692307693</v>
       </c>
       <c r="L122" s="19" t="n">
-        <v>0.06664688686685612</v>
+        <v>0.06621986905376226</v>
       </c>
       <c r="M122" s="19" t="n">
-        <v>0.0335545825530581</v>
+        <v>0.03720487987090237</v>
       </c>
       <c r="N122" s="20" t="n">
         <v>0</v>
@@ -9231,12 +9223,12 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>FLA @ AUB</t>
+          <t>UK @ TA&amp;M</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D123" s="22" t="n">
@@ -9249,29 +9241,29 @@
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>Over 50.5</t>
         </is>
       </c>
       <c r="G123" s="23" t="n">
-        <v>53.5</v>
+        <v>50.5</v>
       </c>
       <c r="H123" s="13" t="n">
         <v>-108</v>
       </c>
       <c r="I123" s="15" t="n">
-        <v>0.5385486876252762</v>
+        <v>0.5355233801273183</v>
       </c>
       <c r="J123" s="15" t="n">
-        <v>0.4978050921861282</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K123" s="15" t="n">
         <v>0.5192307692307693</v>
       </c>
       <c r="L123" s="14" t="n">
-        <v>0.06621986905376226</v>
+        <v>0.06546960606282656</v>
       </c>
       <c r="M123" s="14" t="n">
-        <v>0.03720487987090237</v>
+        <v>0.03137836172668718</v>
       </c>
       <c r="N123" s="15" t="n">
         <v>0</v>
@@ -9609,12 +9601,12 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>OHIO @ USA</t>
+          <t>ASU @ KU</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D129" s="22" t="n">
@@ -9622,22 +9614,22 @@
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F129" s="12" t="inlineStr">
         <is>
-          <t>USA -4.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G129" s="23" t="n">
-        <v>-4.5</v>
+        <v>51.5</v>
       </c>
       <c r="H129" s="13" t="n">
         <v>-105</v>
       </c>
       <c r="I129" s="15" t="n">
-        <v>0.5155053290436606</v>
+        <v>0.5145050930527586</v>
       </c>
       <c r="J129" s="15" t="n">
         <v>0.4891657638136511</v>
@@ -9646,10 +9638,10 @@
         <v>0.5121951219512195</v>
       </c>
       <c r="L129" s="14" t="n">
-        <v>0.04873542224059591</v>
+        <v>0.04721219069057992</v>
       </c>
       <c r="M129" s="14" t="n">
-        <v>0.006462785275718419</v>
+        <v>0.004509943579195319</v>
       </c>
       <c r="N129" s="15" t="n">
         <v>0</v>
@@ -9672,12 +9664,12 @@
       </c>
       <c r="B130" s="17" t="inlineStr">
         <is>
-          <t>GASO @ JVST</t>
+          <t>NCSU @ VAN</t>
         </is>
       </c>
       <c r="C130" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 16:45</t>
         </is>
       </c>
       <c r="D130" s="25" t="n">
@@ -9685,37 +9677,37 @@
       </c>
       <c r="E130" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F130" s="17" t="inlineStr">
         <is>
-          <t>JVST -3</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G130" s="26" t="n">
-        <v>-3</v>
+        <v>51.5</v>
       </c>
       <c r="H130" s="18" t="n">
-        <v>-118</v>
+        <v>-105</v>
       </c>
       <c r="I130" s="20" t="n">
-        <v>0.5441687840838737</v>
+        <v>0.5125185508338179</v>
       </c>
       <c r="J130" s="20" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K130" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L130" s="19" t="n">
-        <v>0.04721891868696465</v>
+        <v>0.04408967848061744</v>
       </c>
       <c r="M130" s="19" t="n">
-        <v>0.005007445728714528</v>
+        <v>0.0006314563898348613</v>
       </c>
       <c r="N130" s="20" t="n">
-        <v>0.0603</v>
+        <v>0</v>
       </c>
       <c r="O130" s="27" t="n">
         <v>0.839</v>
@@ -9735,12 +9727,12 @@
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>GASO @ JVST</t>
+          <t>COLO @ NU</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D131" s="22" t="n">
@@ -9753,33 +9745,33 @@
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
-          <t>JVST ML</t>
+          <t>NU ML</t>
         </is>
       </c>
       <c r="G131" s="23" t="n"/>
       <c r="H131" s="13" t="n">
-        <v>-166</v>
+        <v>-180</v>
       </c>
       <c r="I131" s="15" t="n">
-        <v>0.6288426675128902</v>
+        <v>0.6428045510260727</v>
       </c>
       <c r="J131" s="15" t="n">
-        <v>0.5996387718242023</v>
+        <v>0.6164383561643836</v>
       </c>
       <c r="K131" s="15" t="n">
-        <v>0.6240601503759399</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="L131" s="14" t="n">
-        <v>0.04484126873372907</v>
+        <v>0.04009834576111896</v>
       </c>
       <c r="M131" s="14" t="n">
-        <v>0.007663551556799986</v>
+        <v>-8.180951499803246e-05</v>
       </c>
       <c r="N131" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O131" s="24" t="n">
-        <v>0.839</v>
+        <v>0.725</v>
       </c>
       <c r="P131" s="12" t="inlineStr">
         <is>
@@ -9796,12 +9788,12 @@
       </c>
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>BALL @ LIB</t>
+          <t>GASO @ JVST</t>
         </is>
       </c>
       <c r="C132" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D132" s="25" t="n">
@@ -9809,37 +9801,37 @@
       </c>
       <c r="E132" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F132" s="17" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>JVST -3</t>
         </is>
       </c>
       <c r="G132" s="26" t="n">
-        <v>49.5</v>
+        <v>-3</v>
       </c>
       <c r="H132" s="18" t="n">
-        <v>-108</v>
+        <v>-122</v>
       </c>
       <c r="I132" s="20" t="n">
-        <v>0.5197419177567473</v>
+        <v>0.5485300138565985</v>
       </c>
       <c r="J132" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5260865852617197</v>
       </c>
       <c r="K132" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5495495495495496</v>
       </c>
       <c r="L132" s="19" t="n">
-        <v>0.04473347600297891</v>
+        <v>0.04000729476308557</v>
       </c>
       <c r="M132" s="19" t="n">
-        <v>0.0009844341981799509</v>
+        <v>-0.001743350879736706</v>
       </c>
       <c r="N132" s="20" t="n">
-        <v>0</v>
+        <v>0.0603</v>
       </c>
       <c r="O132" s="27" t="n">
         <v>0.839</v>
@@ -9859,12 +9851,12 @@
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>LT @ BAY</t>
+          <t>BUFF @ PSU</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D133" s="22" t="n">
@@ -9877,29 +9869,29 @@
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="G133" s="23" t="n">
-        <v>53.5</v>
+        <v>48.5</v>
       </c>
       <c r="H133" s="13" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I133" s="15" t="n">
-        <v>0.519741860665571</v>
+        <v>0.5199222722476823</v>
       </c>
       <c r="J133" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K133" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L133" s="14" t="n">
-        <v>0.04473338636160695</v>
+        <v>0.03766166193749009</v>
       </c>
       <c r="M133" s="14" t="n">
-        <v>0.0009843242448035472</v>
+        <v>-0.007421116618061108</v>
       </c>
       <c r="N133" s="15" t="n">
         <v>0</v>
@@ -9922,12 +9914,12 @@
       </c>
       <c r="B134" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ VAN</t>
+          <t>TULN @ KSU</t>
         </is>
       </c>
       <c r="C134" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:45</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D134" s="25" t="n">
@@ -9940,29 +9932,29 @@
       </c>
       <c r="F134" s="17" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="G134" s="26" t="n">
-        <v>51.5</v>
+        <v>49.5</v>
       </c>
       <c r="H134" s="18" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="I134" s="20" t="n">
-        <v>0.5125185508338179</v>
+        <v>0.519922241033544</v>
       </c>
       <c r="J134" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5</v>
       </c>
       <c r="K134" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L134" s="19" t="n">
-        <v>0.04408967848061744</v>
+        <v>0.03766160932064762</v>
       </c>
       <c r="M134" s="19" t="n">
-        <v>0.0006314563898348613</v>
+        <v>-0.007421176208688651</v>
       </c>
       <c r="N134" s="20" t="n">
         <v>0</v>
@@ -9985,12 +9977,12 @@
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>OHIO @ USA</t>
+          <t>BALL @ LIB</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D135" s="22" t="n">
@@ -9998,32 +9990,34 @@
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>USA ML</t>
-        </is>
-      </c>
-      <c r="G135" s="23" t="n"/>
+          <t>Over 49.5</t>
+        </is>
+      </c>
+      <c r="G135" s="23" t="n">
+        <v>49.5</v>
+      </c>
       <c r="H135" s="13" t="n">
-        <v>-192</v>
+        <v>-112</v>
       </c>
       <c r="I135" s="15" t="n">
-        <v>0.6609675373481816</v>
+        <v>0.5240716718267162</v>
       </c>
       <c r="J135" s="15" t="n">
-        <v>0.6309403437815976</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K135" s="15" t="n">
-        <v>0.6575342465753424</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L135" s="14" t="n">
-        <v>0.04397280406027947</v>
+        <v>0.03707022637045459</v>
       </c>
       <c r="M135" s="14" t="n">
-        <v>0.005221463050359532</v>
+        <v>-0.008007192613715741</v>
       </c>
       <c r="N135" s="15" t="n">
         <v>0</v>
@@ -10046,12 +10040,12 @@
       </c>
       <c r="B136" s="17" t="inlineStr">
         <is>
-          <t>COLO @ NU</t>
+          <t>LT @ BAY</t>
         </is>
       </c>
       <c r="C136" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D136" s="25" t="n">
@@ -10059,38 +10053,40 @@
       </c>
       <c r="E136" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F136" s="17" t="inlineStr">
         <is>
-          <t>NU ML</t>
-        </is>
-      </c>
-      <c r="G136" s="26" t="n"/>
+          <t>Under 53.5</t>
+        </is>
+      </c>
+      <c r="G136" s="26" t="n">
+        <v>53.5</v>
+      </c>
       <c r="H136" s="18" t="n">
-        <v>-180</v>
+        <v>-112</v>
       </c>
       <c r="I136" s="20" t="n">
-        <v>0.6428045510260727</v>
+        <v>0.5240716147355399</v>
       </c>
       <c r="J136" s="20" t="n">
-        <v>0.6164383561643836</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K136" s="20" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L136" s="19" t="n">
-        <v>0.04009834576111896</v>
+        <v>0.03707013040517221</v>
       </c>
       <c r="M136" s="19" t="n">
-        <v>-8.180951499803246e-05</v>
+        <v>-0.00800730067915667</v>
       </c>
       <c r="N136" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O136" s="27" t="n">
-        <v>0.725</v>
+        <v>0.839</v>
       </c>
       <c r="P136" s="17" t="inlineStr">
         <is>
@@ -10107,12 +10103,12 @@
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>BUFF @ PSU</t>
+          <t>COLO @ NU</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D137" s="22" t="n">
@@ -10120,40 +10116,40 @@
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>NU -3.5</t>
         </is>
       </c>
       <c r="G137" s="23" t="n">
-        <v>48.5</v>
+        <v>-3.5</v>
       </c>
       <c r="H137" s="13" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I137" s="15" t="n">
-        <v>0.5199222722476823</v>
+        <v>0.5297299584649824</v>
       </c>
       <c r="J137" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K137" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L137" s="14" t="n">
-        <v>0.03766166193749009</v>
+        <v>0.03522742304385739</v>
       </c>
       <c r="M137" s="14" t="n">
-        <v>-0.007421116618061108</v>
+        <v>-0.00963529504372862</v>
       </c>
       <c r="N137" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O137" s="24" t="n">
-        <v>0.839</v>
+        <v>0.725</v>
       </c>
       <c r="P137" s="12" t="inlineStr">
         <is>
@@ -10170,12 +10166,12 @@
       </c>
       <c r="B138" s="17" t="inlineStr">
         <is>
-          <t>TULN @ KSU</t>
+          <t>OHIO @ USA</t>
         </is>
       </c>
       <c r="C138" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D138" s="25" t="n">
@@ -10183,34 +10179,34 @@
       </c>
       <c r="E138" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F138" s="17" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>USA -5.5</t>
         </is>
       </c>
       <c r="G138" s="26" t="n">
-        <v>49.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H138" s="18" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="I138" s="20" t="n">
-        <v>0.519922241033544</v>
+        <v>0.4998831279804317</v>
       </c>
       <c r="J138" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K138" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L138" s="19" t="n">
-        <v>0.03766160932064762</v>
+        <v>0.03414025728453774</v>
       </c>
       <c r="M138" s="19" t="n">
-        <v>-0.007421176208688651</v>
+        <v>-0.01003537399953713</v>
       </c>
       <c r="N138" s="20" t="n">
         <v>0</v>
@@ -10233,12 +10229,12 @@
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>ASU @ KU</t>
+          <t>OHIO @ USA</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D139" s="22" t="n">
@@ -10258,22 +10254,22 @@
         <v>51.5</v>
       </c>
       <c r="H139" s="13" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="I139" s="15" t="n">
-        <v>0.5199222111459331</v>
+        <v>0.5220870881809174</v>
       </c>
       <c r="J139" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K139" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L139" s="14" t="n">
-        <v>0.03766155893987126</v>
+        <v>0.03368148032496549</v>
       </c>
       <c r="M139" s="14" t="n">
-        <v>-0.007421233266855065</v>
+        <v>-0.01176372594326347</v>
       </c>
       <c r="N139" s="15" t="n">
         <v>0</v>
@@ -10296,12 +10292,12 @@
       </c>
       <c r="B140" s="17" t="inlineStr">
         <is>
-          <t>COLO @ NU</t>
+          <t>GASO @ JVST</t>
         </is>
       </c>
       <c r="C140" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D140" s="25" t="n">
@@ -10309,40 +10305,38 @@
       </c>
       <c r="E140" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F140" s="17" t="inlineStr">
         <is>
-          <t>NU -3.5</t>
-        </is>
-      </c>
-      <c r="G140" s="26" t="n">
-        <v>-3.5</v>
-      </c>
+          <t>JVST ML</t>
+        </is>
+      </c>
+      <c r="G140" s="26" t="n"/>
       <c r="H140" s="18" t="n">
-        <v>-115</v>
+        <v>-180</v>
       </c>
       <c r="I140" s="20" t="n">
-        <v>0.5297299584649824</v>
+        <v>0.6372424596829809</v>
       </c>
       <c r="J140" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.6164383561643836</v>
       </c>
       <c r="K140" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="L140" s="19" t="n">
-        <v>0.03522742304385739</v>
+        <v>0.03239732413629048</v>
       </c>
       <c r="M140" s="19" t="n">
-        <v>-0.00963529504372862</v>
+        <v>-0.008733951604251944</v>
       </c>
       <c r="N140" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O140" s="27" t="n">
-        <v>0.725</v>
+        <v>0.839</v>
       </c>
       <c r="P140" s="17" t="inlineStr">
         <is>
@@ -10359,12 +10353,12 @@
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>OHIO @ USA</t>
+          <t>UGA @ ARK</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D141" s="22" t="n">
@@ -10377,29 +10371,29 @@
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Under 54.5</t>
         </is>
       </c>
       <c r="G141" s="23" t="n">
-        <v>51.5</v>
+        <v>54.5</v>
       </c>
       <c r="H141" s="13" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I141" s="15" t="n">
-        <v>0.5220870881809174</v>
+        <v>0.5159473127094389</v>
       </c>
       <c r="J141" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K141" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L141" s="14" t="n">
-        <v>0.03368148032496549</v>
+        <v>0.0307479466624253</v>
       </c>
       <c r="M141" s="14" t="n">
-        <v>-0.01176372594326347</v>
+        <v>-0.01500967573652556</v>
       </c>
       <c r="N141" s="15" t="n">
         <v>0</v>
@@ -10422,12 +10416,12 @@
       </c>
       <c r="B142" s="17" t="inlineStr">
         <is>
-          <t>UGA @ ARK</t>
+          <t>TEM @ TOL</t>
         </is>
       </c>
       <c r="C142" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 19:00</t>
         </is>
       </c>
       <c r="D142" s="25" t="n">
@@ -10435,34 +10429,32 @@
       </c>
       <c r="E142" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F142" s="17" t="inlineStr">
         <is>
-          <t>Under 54.5</t>
-        </is>
-      </c>
-      <c r="G142" s="26" t="n">
-        <v>54.5</v>
-      </c>
+          <t>TOL ML</t>
+        </is>
+      </c>
+      <c r="G142" s="26" t="n"/>
       <c r="H142" s="18" t="n">
-        <v>-110</v>
+        <v>-218</v>
       </c>
       <c r="I142" s="20" t="n">
-        <v>0.5159473127094389</v>
+        <v>0.6781856250702285</v>
       </c>
       <c r="J142" s="20" t="n">
-        <v>0.5</v>
+        <v>0.6574752261956054</v>
       </c>
       <c r="K142" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.6855345911949685</v>
       </c>
       <c r="L142" s="19" t="n">
-        <v>0.0307479466624253</v>
+        <v>0.03039409102524932</v>
       </c>
       <c r="M142" s="19" t="n">
-        <v>-0.01500967573652556</v>
+        <v>-0.01072005150306121</v>
       </c>
       <c r="N142" s="20" t="n">
         <v>0</v>
@@ -10485,12 +10477,12 @@
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>TEM @ TOL</t>
+          <t>TROY @ MIZ</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D143" s="22" t="n">
@@ -10498,32 +10490,34 @@
       </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>TOL ML</t>
-        </is>
-      </c>
-      <c r="G143" s="23" t="n"/>
+          <t>Over 50.5</t>
+        </is>
+      </c>
+      <c r="G143" s="23" t="n">
+        <v>50.5</v>
+      </c>
       <c r="H143" s="13" t="n">
-        <v>-218</v>
+        <v>-108</v>
       </c>
       <c r="I143" s="15" t="n">
-        <v>0.6781856250702285</v>
+        <v>0.5098012284358664</v>
       </c>
       <c r="J143" s="15" t="n">
-        <v>0.6574752261956054</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K143" s="15" t="n">
-        <v>0.6855345911949685</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L143" s="14" t="n">
-        <v>0.03039409102524932</v>
+        <v>0.02768278550697907</v>
       </c>
       <c r="M143" s="14" t="n">
-        <v>-0.01072005150306121</v>
+        <v>-0.01816059708647944</v>
       </c>
       <c r="N143" s="15" t="n">
         <v>0</v>
@@ -10546,12 +10540,12 @@
       </c>
       <c r="B144" s="17" t="inlineStr">
         <is>
-          <t>TROY @ MIZ</t>
+          <t>CCU @ DEL</t>
         </is>
       </c>
       <c r="C144" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 15:30</t>
         </is>
       </c>
       <c r="D144" s="25" t="n">
@@ -10559,34 +10553,34 @@
       </c>
       <c r="E144" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F144" s="17" t="inlineStr">
         <is>
-          <t>Over 50.5</t>
+          <t>CCU +5.5</t>
         </is>
       </c>
       <c r="G144" s="26" t="n">
-        <v>50.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H144" s="18" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="I144" s="20" t="n">
-        <v>0.5098012284358664</v>
+        <v>0.5246512561420218</v>
       </c>
       <c r="J144" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K144" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L144" s="19" t="n">
-        <v>0.02768278550697907</v>
+        <v>0.02634003666683046</v>
       </c>
       <c r="M144" s="19" t="n">
-        <v>-0.01816059708647944</v>
+        <v>-0.01913026025622022</v>
       </c>
       <c r="N144" s="20" t="n">
         <v>0</v>
@@ -10609,12 +10603,12 @@
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>CCU @ DEL</t>
+          <t>OHIO @ USA</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 15:30</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D145" s="22" t="n">
@@ -10622,34 +10616,32 @@
       </c>
       <c r="E145" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F145" s="12" t="inlineStr">
         <is>
-          <t>CCU +5.5</t>
-        </is>
-      </c>
-      <c r="G145" s="23" t="n">
-        <v>-5.5</v>
-      </c>
+          <t>USA ML</t>
+        </is>
+      </c>
+      <c r="G145" s="23" t="n"/>
       <c r="H145" s="13" t="n">
-        <v>-115</v>
+        <v>-218</v>
       </c>
       <c r="I145" s="15" t="n">
-        <v>0.5246512561420218</v>
+        <v>0.6742349785551854</v>
       </c>
       <c r="J145" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.6574752261956054</v>
       </c>
       <c r="K145" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.6855345911949685</v>
       </c>
       <c r="L145" s="14" t="n">
-        <v>0.02634003666683046</v>
+        <v>0.02489641715498433</v>
       </c>
       <c r="M145" s="14" t="n">
-        <v>-0.01913026025622022</v>
+        <v>-0.01648292119014239</v>
       </c>
       <c r="N145" s="15" t="n">
         <v>0</v>
@@ -10672,12 +10664,12 @@
       </c>
       <c r="B146" s="17" t="inlineStr">
         <is>
-          <t>TEM @ TOL</t>
+          <t>MSST @ SC</t>
         </is>
       </c>
       <c r="C146" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 19:00</t>
+          <t>2026-09-19 20:15</t>
         </is>
       </c>
       <c r="D146" s="25" t="n">
@@ -10690,32 +10682,32 @@
       </c>
       <c r="F146" s="17" t="inlineStr">
         <is>
-          <t>TOL -5.5</t>
+          <t>MSST +4</t>
         </is>
       </c>
       <c r="G146" s="26" t="n">
-        <v>-5.5</v>
+        <v>-4</v>
       </c>
       <c r="H146" s="18" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I146" s="20" t="n">
-        <v>0.5130654502461751</v>
+        <v>0.523694728211634</v>
       </c>
       <c r="J146" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K146" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L146" s="19" t="n">
-        <v>0.02549123803810194</v>
+        <v>0.02460222982133908</v>
       </c>
       <c r="M146" s="19" t="n">
-        <v>-0.02051141316639293</v>
+        <v>-0.02026589279428123</v>
       </c>
       <c r="N146" s="20" t="n">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
       <c r="O146" s="27" t="n">
         <v>0.839</v>
@@ -10735,12 +10727,12 @@
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>MSST @ SC</t>
+          <t>CCU @ DEL</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 20:15</t>
+          <t>2026-09-19 15:30</t>
         </is>
       </c>
       <c r="D147" s="22" t="n">
@@ -10748,37 +10740,35 @@
       </c>
       <c r="E147" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
-          <t>MSST +4</t>
-        </is>
-      </c>
-      <c r="G147" s="23" t="n">
-        <v>-4</v>
-      </c>
+          <t>CCU ML</t>
+        </is>
+      </c>
+      <c r="G147" s="23" t="n"/>
       <c r="H147" s="13" t="n">
-        <v>-115</v>
+        <v>180</v>
       </c>
       <c r="I147" s="15" t="n">
-        <v>0.523694728211634</v>
+        <v>0.3511097637938756</v>
       </c>
       <c r="J147" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.3425247738043947</v>
       </c>
       <c r="K147" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L147" s="14" t="n">
-        <v>0.02460222982133908</v>
+        <v>0.02449806519387096</v>
       </c>
       <c r="M147" s="14" t="n">
-        <v>-0.02026589279428123</v>
+        <v>-0.0168926613771484</v>
       </c>
       <c r="N147" s="15" t="n">
-        <v>0.0312</v>
+        <v>0</v>
       </c>
       <c r="O147" s="24" t="n">
         <v>0.839</v>
@@ -10798,12 +10788,12 @@
       </c>
       <c r="B148" s="17" t="inlineStr">
         <is>
-          <t>CCU @ DEL</t>
+          <t>MRSH @ MOST</t>
         </is>
       </c>
       <c r="C148" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 15:30</t>
+          <t>2026-09-19 22:30</t>
         </is>
       </c>
       <c r="D148" s="25" t="n">
@@ -10811,32 +10801,34 @@
       </c>
       <c r="E148" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F148" s="17" t="inlineStr">
         <is>
-          <t>CCU ML</t>
-        </is>
-      </c>
-      <c r="G148" s="26" t="n"/>
+          <t>Over 51.5</t>
+        </is>
+      </c>
+      <c r="G148" s="26" t="n">
+        <v>51.5</v>
+      </c>
       <c r="H148" s="18" t="n">
-        <v>180</v>
+        <v>-112</v>
       </c>
       <c r="I148" s="20" t="n">
-        <v>0.3511097637938756</v>
+        <v>0.514130969174035</v>
       </c>
       <c r="J148" s="20" t="n">
-        <v>0.3425247738043947</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K148" s="20" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L148" s="19" t="n">
-        <v>0.02449806519387096</v>
+        <v>0.01916750383849712</v>
       </c>
       <c r="M148" s="19" t="n">
-        <v>-0.0168926613771484</v>
+        <v>-0.02682352263486232</v>
       </c>
       <c r="N148" s="20" t="n">
         <v>0</v>
@@ -10859,12 +10851,12 @@
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>MRSH @ MOST</t>
+          <t>BYU @ CSU</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 22:30</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D149" s="22" t="n">
@@ -10877,29 +10869,29 @@
       </c>
       <c r="F149" s="12" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="G149" s="23" t="n">
-        <v>51.5</v>
+        <v>52.5</v>
       </c>
       <c r="H149" s="13" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I149" s="15" t="n">
-        <v>0.514130969174035</v>
+        <v>0.4985737151668523</v>
       </c>
       <c r="J149" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K149" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L149" s="14" t="n">
-        <v>0.01916750383849712</v>
+        <v>0.01897412855126167</v>
       </c>
       <c r="M149" s="14" t="n">
-        <v>-0.02682352263486232</v>
+        <v>-0.02659417515043117</v>
       </c>
       <c r="N149" s="15" t="n">
         <v>0</v>
@@ -10922,7 +10914,7 @@
       </c>
       <c r="B150" s="17" t="inlineStr">
         <is>
-          <t>BYU @ CSU</t>
+          <t>VT @ MD</t>
         </is>
       </c>
       <c r="C150" s="17" t="inlineStr">
@@ -10940,17 +10932,17 @@
       </c>
       <c r="F150" s="17" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="G150" s="26" t="n">
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
       <c r="H150" s="18" t="n">
         <v>-105</v>
       </c>
       <c r="I150" s="20" t="n">
-        <v>0.4985737151668523</v>
+        <v>0.4985736930994028</v>
       </c>
       <c r="J150" s="20" t="n">
         <v>0.4891657638136511</v>
@@ -10959,10 +10951,10 @@
         <v>0.5121951219512195</v>
       </c>
       <c r="L150" s="19" t="n">
-        <v>0.01897412855126167</v>
+        <v>0.01897408523842711</v>
       </c>
       <c r="M150" s="19" t="n">
-        <v>-0.02659417515043117</v>
+        <v>-0.02659421823449937</v>
       </c>
       <c r="N150" s="20" t="n">
         <v>0</v>
@@ -10985,12 +10977,12 @@
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>VT @ MD</t>
+          <t>NCSU @ VAN</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 16:45</t>
         </is>
       </c>
       <c r="D151" s="22" t="n">
@@ -10998,34 +10990,34 @@
       </c>
       <c r="E151" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F151" s="12" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>VAN -3.5</t>
         </is>
       </c>
       <c r="G151" s="23" t="n">
-        <v>53.5</v>
+        <v>-3.5</v>
       </c>
       <c r="H151" s="13" t="n">
-        <v>-105</v>
+        <v>-102</v>
       </c>
       <c r="I151" s="15" t="n">
-        <v>0.4985736930994028</v>
+        <v>0.4919086194809554</v>
       </c>
       <c r="J151" s="15" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K151" s="15" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L151" s="14" t="n">
-        <v>0.01897408523842711</v>
+        <v>0.01895499242707</v>
       </c>
       <c r="M151" s="14" t="n">
-        <v>-0.02659421823449937</v>
+        <v>-0.02582802808673523</v>
       </c>
       <c r="N151" s="15" t="n">
         <v>0</v>
@@ -11048,12 +11040,12 @@
       </c>
       <c r="B152" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ VAN</t>
+          <t>MSU @ ND</t>
         </is>
       </c>
       <c r="C152" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:45</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D152" s="25" t="n">
@@ -11061,34 +11053,34 @@
       </c>
       <c r="E152" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F152" s="17" t="inlineStr">
         <is>
-          <t>VAN -3.5</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="G152" s="26" t="n">
-        <v>-3.5</v>
+        <v>52.5</v>
       </c>
       <c r="H152" s="18" t="n">
-        <v>-102</v>
+        <v>-118</v>
       </c>
       <c r="I152" s="20" t="n">
-        <v>0.4919086194809554</v>
+        <v>0.5266176939377067</v>
       </c>
       <c r="J152" s="20" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K152" s="20" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L152" s="19" t="n">
-        <v>0.01895499242707</v>
+        <v>0.01767760700769214</v>
       </c>
       <c r="M152" s="19" t="n">
-        <v>-0.02582802808673523</v>
+        <v>-0.02709612475915202</v>
       </c>
       <c r="N152" s="20" t="n">
         <v>0</v>
@@ -11111,12 +11103,12 @@
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>MSU @ ND</t>
+          <t>NCSU @ VAN</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 16:45</t>
         </is>
       </c>
       <c r="D153" s="22" t="n">
@@ -11124,34 +11116,32 @@
       </c>
       <c r="E153" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
-        </is>
-      </c>
-      <c r="G153" s="23" t="n">
-        <v>52.5</v>
-      </c>
+          <t>VAN ML</t>
+        </is>
+      </c>
+      <c r="G153" s="23" t="n"/>
       <c r="H153" s="13" t="n">
-        <v>-118</v>
+        <v>-170</v>
       </c>
       <c r="I153" s="15" t="n">
-        <v>0.5266176939377067</v>
+        <v>0.6142532555304204</v>
       </c>
       <c r="J153" s="15" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.6037569709421778</v>
       </c>
       <c r="K153" s="15" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="L153" s="14" t="n">
-        <v>0.01767760700769214</v>
+        <v>0.01719344752098952</v>
       </c>
       <c r="M153" s="14" t="n">
-        <v>-0.02709612475915202</v>
+        <v>-0.02442130003992038</v>
       </c>
       <c r="N153" s="15" t="n">
         <v>0</v>
@@ -11174,12 +11164,12 @@
       </c>
       <c r="B154" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ VAN</t>
+          <t>TEM @ TOL</t>
         </is>
       </c>
       <c r="C154" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:45</t>
+          <t>2026-09-19 19:00</t>
         </is>
       </c>
       <c r="D154" s="25" t="n">
@@ -11187,32 +11177,34 @@
       </c>
       <c r="E154" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F154" s="17" t="inlineStr">
         <is>
-          <t>VAN ML</t>
-        </is>
-      </c>
-      <c r="G154" s="26" t="n"/>
+          <t>Over 50.5</t>
+        </is>
+      </c>
+      <c r="G154" s="26" t="n">
+        <v>50.5</v>
+      </c>
       <c r="H154" s="18" t="n">
-        <v>-170</v>
+        <v>-115</v>
       </c>
       <c r="I154" s="20" t="n">
-        <v>0.6142532555304204</v>
+        <v>0.5193745424736034</v>
       </c>
       <c r="J154" s="20" t="n">
-        <v>0.6037569709421778</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K154" s="20" t="n">
-        <v>0.6296296296296297</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L154" s="19" t="n">
-        <v>0.01719344752098952</v>
+        <v>0.01654787447595338</v>
       </c>
       <c r="M154" s="19" t="n">
-        <v>-0.02442130003992038</v>
+        <v>-0.02899542059282856</v>
       </c>
       <c r="N154" s="20" t="n">
         <v>0</v>
@@ -11235,12 +11227,12 @@
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>SYR @ PITT</t>
+          <t>TEM @ TOL</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>2026-09-17 23:30</t>
+          <t>2026-09-19 19:00</t>
         </is>
       </c>
       <c r="D155" s="22" t="n">
@@ -11248,34 +11240,34 @@
       </c>
       <c r="E155" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>Over 50.5</t>
+          <t>TOL -5.5</t>
         </is>
       </c>
       <c r="G155" s="23" t="n">
-        <v>50.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H155" s="13" t="n">
-        <v>-118</v>
+        <v>-115</v>
       </c>
       <c r="I155" s="15" t="n">
-        <v>0.5246294116207542</v>
+        <v>0.5184825683393495</v>
       </c>
       <c r="J155" s="15" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K155" s="15" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L155" s="14" t="n">
-        <v>0.0139414906840648</v>
+        <v>0.01484949521733578</v>
       </c>
       <c r="M155" s="14" t="n">
-        <v>-0.03076939209047114</v>
+        <v>-0.03066302440904234</v>
       </c>
       <c r="N155" s="15" t="n">
         <v>0</v>
@@ -11548,12 +11540,12 @@
       </c>
       <c r="B160" s="17" t="inlineStr">
         <is>
-          <t>NIU @ ARIZ</t>
+          <t>UNC @ CLEM</t>
         </is>
       </c>
       <c r="C160" s="17" t="inlineStr">
         <is>
-          <t>2026-09-20 02:30</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D160" s="25" t="n">
@@ -11561,34 +11553,32 @@
       </c>
       <c r="E160" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F160" s="17" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
-        </is>
-      </c>
-      <c r="G160" s="26" t="n">
-        <v>49.5</v>
-      </c>
+          <t>UNC ML</t>
+        </is>
+      </c>
+      <c r="G160" s="26" t="n"/>
       <c r="H160" s="18" t="n">
-        <v>-108</v>
+        <v>145</v>
       </c>
       <c r="I160" s="20" t="n">
-        <v>0.4998305588677219</v>
+        <v>0.3946416664132579</v>
       </c>
       <c r="J160" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.3907637655417407</v>
       </c>
       <c r="K160" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.4081632653061225</v>
       </c>
       <c r="L160" s="19" t="n">
-        <v>0.008371536854861306</v>
+        <v>0.009887960099457084</v>
       </c>
       <c r="M160" s="19" t="n">
-        <v>-0.03736336810660967</v>
+        <v>-0.03312791728751796</v>
       </c>
       <c r="N160" s="20" t="n">
         <v>0</v>
@@ -11611,12 +11601,12 @@
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>UNT @ TXST</t>
+          <t>NIU @ ARIZ</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-20 02:30</t>
         </is>
       </c>
       <c r="D161" s="22" t="n">
@@ -11624,22 +11614,22 @@
       </c>
       <c r="E161" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F161" s="12" t="inlineStr">
         <is>
-          <t>TXST -3</t>
+          <t>Under 49.5</t>
         </is>
       </c>
       <c r="G161" s="23" t="n">
-        <v>-3</v>
+        <v>49.5</v>
       </c>
       <c r="H161" s="13" t="n">
         <v>-108</v>
       </c>
       <c r="I161" s="15" t="n">
-        <v>0.4995829263106649</v>
+        <v>0.4998305588677219</v>
       </c>
       <c r="J161" s="15" t="n">
         <v>0.4956702459300312</v>
@@ -11648,13 +11638,13 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L161" s="14" t="n">
-        <v>0.007875599791871683</v>
+        <v>0.008371536854861306</v>
       </c>
       <c r="M161" s="14" t="n">
-        <v>-0.03552824834517297</v>
+        <v>-0.03736336810660967</v>
       </c>
       <c r="N161" s="15" t="n">
-        <v>0.0611</v>
+        <v>0</v>
       </c>
       <c r="O161" s="24" t="n">
         <v>0.839</v>
@@ -11674,12 +11664,12 @@
       </c>
       <c r="B162" s="17" t="inlineStr">
         <is>
-          <t>MSST @ SC</t>
+          <t>UNT @ TXST</t>
         </is>
       </c>
       <c r="C162" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 20:15</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D162" s="25" t="n">
@@ -11687,35 +11677,37 @@
       </c>
       <c r="E162" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F162" s="17" t="inlineStr">
         <is>
-          <t>MSST ML</t>
-        </is>
-      </c>
-      <c r="G162" s="26" t="n"/>
+          <t>TXST -3</t>
+        </is>
+      </c>
+      <c r="G162" s="26" t="n">
+        <v>-3</v>
+      </c>
       <c r="H162" s="18" t="n">
-        <v>145</v>
+        <v>-108</v>
       </c>
       <c r="I162" s="20" t="n">
-        <v>0.393107494495158</v>
+        <v>0.4995829263106649</v>
       </c>
       <c r="J162" s="20" t="n">
-        <v>0.3907637655417407</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K162" s="20" t="n">
-        <v>0.4081632653061225</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L162" s="19" t="n">
-        <v>0.00598985901507957</v>
+        <v>0.007875599791871683</v>
       </c>
       <c r="M162" s="19" t="n">
-        <v>-0.0368866384868628</v>
+        <v>-0.03552824834517297</v>
       </c>
       <c r="N162" s="20" t="n">
-        <v>0</v>
+        <v>0.0611</v>
       </c>
       <c r="O162" s="27" t="n">
         <v>0.839</v>
@@ -11735,12 +11727,12 @@
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t>GAST @ UCF</t>
+          <t>MSST @ SC</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 20:15</t>
         </is>
       </c>
       <c r="D163" s="22" t="n">
@@ -11748,34 +11740,32 @@
       </c>
       <c r="E163" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
-        </is>
-      </c>
-      <c r="G163" s="23" t="n">
-        <v>51.5</v>
-      </c>
+          <t>MSST ML</t>
+        </is>
+      </c>
+      <c r="G163" s="23" t="n"/>
       <c r="H163" s="13" t="n">
-        <v>-108</v>
+        <v>145</v>
       </c>
       <c r="I163" s="15" t="n">
-        <v>0.4978351475877192</v>
+        <v>0.393107494495158</v>
       </c>
       <c r="J163" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.3907637655417407</v>
       </c>
       <c r="K163" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.4081632653061225</v>
       </c>
       <c r="L163" s="14" t="n">
-        <v>0.004364550113953183</v>
+        <v>0.00598985901507957</v>
       </c>
       <c r="M163" s="14" t="n">
-        <v>-0.04120638242365193</v>
+        <v>-0.0368866384868628</v>
       </c>
       <c r="N163" s="15" t="n">
         <v>0</v>
@@ -11798,7 +11788,7 @@
       </c>
       <c r="B164" s="17" t="inlineStr">
         <is>
-          <t>NEV @ MTSU</t>
+          <t>GAST @ UCF</t>
         </is>
       </c>
       <c r="C164" s="17" t="inlineStr">
@@ -11816,17 +11806,17 @@
       </c>
       <c r="F164" s="17" t="inlineStr">
         <is>
-          <t>Under 50.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G164" s="26" t="n">
-        <v>50.5</v>
+        <v>51.5</v>
       </c>
       <c r="H164" s="18" t="n">
         <v>-108</v>
       </c>
       <c r="I164" s="20" t="n">
-        <v>0.4978350809818011</v>
+        <v>0.4978351475877192</v>
       </c>
       <c r="J164" s="20" t="n">
         <v>0.4956702459300312</v>
@@ -11835,10 +11825,10 @@
         <v>0.5192307692307693</v>
       </c>
       <c r="L164" s="19" t="n">
-        <v>0.004364416022112758</v>
+        <v>0.004364550113953183</v>
       </c>
       <c r="M164" s="19" t="n">
-        <v>-0.04120651070171644</v>
+        <v>-0.04120638242365193</v>
       </c>
       <c r="N164" s="20" t="n">
         <v>0</v>
@@ -11861,12 +11851,12 @@
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t>FRES @ SJSU</t>
+          <t>NEV @ MTSU</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 03:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D165" s="22" t="n">
@@ -11886,22 +11876,22 @@
         <v>50.5</v>
       </c>
       <c r="H165" s="13" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="I165" s="15" t="n">
-        <v>0.5061556513640563</v>
+        <v>0.4978350809818011</v>
       </c>
       <c r="J165" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K165" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L165" s="14" t="n">
-        <v>0.003618691610171043</v>
+        <v>0.004364416022112758</v>
       </c>
       <c r="M165" s="14" t="n">
-        <v>-0.04191965991803637</v>
+        <v>-0.04120651070171644</v>
       </c>
       <c r="N165" s="15" t="n">
         <v>0</v>
@@ -11924,12 +11914,12 @@
       </c>
       <c r="B166" s="17" t="inlineStr">
         <is>
-          <t>UNC @ CLEM</t>
+          <t>FRES @ SJSU</t>
         </is>
       </c>
       <c r="C166" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-20 03:00</t>
         </is>
       </c>
       <c r="D166" s="25" t="n">
@@ -11937,32 +11927,34 @@
       </c>
       <c r="E166" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F166" s="17" t="inlineStr">
         <is>
-          <t>CLEM ML</t>
-        </is>
-      </c>
-      <c r="G166" s="26" t="n"/>
+          <t>Under 50.5</t>
+        </is>
+      </c>
+      <c r="G166" s="26" t="n">
+        <v>50.5</v>
+      </c>
       <c r="H166" s="18" t="n">
-        <v>-166</v>
+        <v>-112</v>
       </c>
       <c r="I166" s="20" t="n">
-        <v>0.6005596022697135</v>
+        <v>0.5061556513640563</v>
       </c>
       <c r="J166" s="20" t="n">
-        <v>0.5996387718242023</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K166" s="20" t="n">
-        <v>0.6240601503759399</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L166" s="19" t="n">
-        <v>0.00153550819937143</v>
+        <v>0.003618691610171043</v>
       </c>
       <c r="M166" s="19" t="n">
-        <v>-0.03765750479672414</v>
+        <v>-0.04191965991803637</v>
       </c>
       <c r="N166" s="20" t="n">
         <v>0</v>
@@ -11985,12 +11977,12 @@
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t>TEM @ TOL</t>
+          <t>SYR @ PITT</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:00</t>
+          <t>2026-09-17 23:30</t>
         </is>
       </c>
       <c r="D167" s="22" t="n">
@@ -12003,29 +11995,29 @@
       </c>
       <c r="F167" s="12" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="G167" s="23" t="n">
         <v>51.5</v>
       </c>
       <c r="H167" s="13" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="I167" s="15" t="n">
-        <v>0.5114028210164896</v>
+        <v>0.49059208864476</v>
       </c>
       <c r="J167" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K167" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L167" s="14" t="n">
-        <v>0.001113000606235724</v>
+        <v>0.002914915989230837</v>
       </c>
       <c r="M167" s="14" t="n">
-        <v>-0.04389907375178037</v>
+        <v>-0.0421773507411829</v>
       </c>
       <c r="N167" s="15" t="n">
         <v>0</v>
@@ -12048,12 +12040,12 @@
       </c>
       <c r="B168" s="17" t="inlineStr">
         <is>
-          <t>TEM @ TOL</t>
+          <t>SYR @ PITT</t>
         </is>
       </c>
       <c r="C168" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 19:00</t>
+          <t>2026-09-17 23:30</t>
         </is>
       </c>
       <c r="D168" s="25" t="n">
@@ -12066,29 +12058,29 @@
       </c>
       <c r="F168" s="17" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G168" s="26" t="n">
         <v>51.5</v>
       </c>
       <c r="H168" s="18" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="I168" s="20" t="n">
-        <v>0.4885971789835103</v>
+        <v>0.50940791135524</v>
       </c>
       <c r="J168" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K168" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L168" s="19" t="n">
-        <v>-0.001162298142880448</v>
+        <v>-0.002791344373401287</v>
       </c>
       <c r="M168" s="19" t="n">
-        <v>-0.04607217436552746</v>
+        <v>-0.04762868746629056</v>
       </c>
       <c r="N168" s="20" t="n">
         <v>0</v>
@@ -12111,12 +12103,12 @@
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>UNC @ CLEM</t>
+          <t>FRES @ SJSU</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-20 03:00</t>
         </is>
       </c>
       <c r="D169" s="22" t="n">
@@ -12124,32 +12116,34 @@
       </c>
       <c r="E169" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F169" s="12" t="inlineStr">
         <is>
-          <t>UNC ML</t>
-        </is>
-      </c>
-      <c r="G169" s="23" t="n"/>
+          <t>Over 50.5</t>
+        </is>
+      </c>
+      <c r="G169" s="23" t="n">
+        <v>50.5</v>
+      </c>
       <c r="H169" s="13" t="n">
-        <v>140</v>
+        <v>-108</v>
       </c>
       <c r="I169" s="15" t="n">
-        <v>0.3994403977302865</v>
+        <v>0.4938443486359437</v>
       </c>
       <c r="J169" s="15" t="n">
-        <v>0.4003612281757977</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K169" s="15" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L169" s="14" t="n">
-        <v>-0.002299549777166658</v>
+        <v>-0.003681848458328739</v>
       </c>
       <c r="M169" s="14" t="n">
-        <v>-0.04134304544731249</v>
+        <v>-0.04889236559003429</v>
       </c>
       <c r="N169" s="15" t="n">
         <v>0</v>
@@ -12172,12 +12166,12 @@
       </c>
       <c r="B170" s="17" t="inlineStr">
         <is>
-          <t>FRES @ SJSU</t>
+          <t>MSST @ SC</t>
         </is>
       </c>
       <c r="C170" s="17" t="inlineStr">
         <is>
-          <t>2026-09-20 03:00</t>
+          <t>2026-09-19 20:15</t>
         </is>
       </c>
       <c r="D170" s="25" t="n">
@@ -12185,34 +12179,32 @@
       </c>
       <c r="E170" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F170" s="17" t="inlineStr">
         <is>
-          <t>Over 50.5</t>
-        </is>
-      </c>
-      <c r="G170" s="26" t="n">
-        <v>50.5</v>
-      </c>
+          <t>SC ML</t>
+        </is>
+      </c>
+      <c r="G170" s="26" t="n"/>
       <c r="H170" s="18" t="n">
-        <v>-108</v>
+        <v>-175</v>
       </c>
       <c r="I170" s="20" t="n">
-        <v>0.4938443486359437</v>
+        <v>0.606892505504842</v>
       </c>
       <c r="J170" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.6092362344582594</v>
       </c>
       <c r="K170" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="L170" s="19" t="n">
-        <v>-0.003681848458328739</v>
+        <v>-0.003844893922938249</v>
       </c>
       <c r="M170" s="19" t="n">
-        <v>-0.04889236559003429</v>
+        <v>-0.04631177706381973</v>
       </c>
       <c r="N170" s="20" t="n">
         <v>0</v>
@@ -12235,12 +12227,12 @@
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t>MSST @ SC</t>
+          <t>NEV @ MTSU</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 20:15</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D171" s="22" t="n">
@@ -12248,32 +12240,34 @@
       </c>
       <c r="E171" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F171" s="12" t="inlineStr">
         <is>
-          <t>SC ML</t>
-        </is>
-      </c>
-      <c r="G171" s="23" t="n"/>
+          <t>Over 50.5</t>
+        </is>
+      </c>
+      <c r="G171" s="23" t="n">
+        <v>50.5</v>
+      </c>
       <c r="H171" s="13" t="n">
-        <v>-175</v>
+        <v>-112</v>
       </c>
       <c r="I171" s="15" t="n">
-        <v>0.606892505504842</v>
+        <v>0.5021649190181989</v>
       </c>
       <c r="J171" s="15" t="n">
-        <v>0.6092362344582594</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K171" s="15" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L171" s="14" t="n">
-        <v>-0.003844893922938249</v>
+        <v>-0.004289580349563814</v>
       </c>
       <c r="M171" s="14" t="n">
-        <v>-0.04631177706381973</v>
+        <v>-0.04947354614412347</v>
       </c>
       <c r="N171" s="15" t="n">
         <v>0</v>
@@ -12296,7 +12290,7 @@
       </c>
       <c r="B172" s="17" t="inlineStr">
         <is>
-          <t>NEV @ MTSU</t>
+          <t>GAST @ UCF</t>
         </is>
       </c>
       <c r="C172" s="17" t="inlineStr">
@@ -12314,17 +12308,17 @@
       </c>
       <c r="F172" s="17" t="inlineStr">
         <is>
-          <t>Over 50.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G172" s="26" t="n">
-        <v>50.5</v>
+        <v>51.5</v>
       </c>
       <c r="H172" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I172" s="20" t="n">
-        <v>0.5021649190181989</v>
+        <v>0.5021648524122808</v>
       </c>
       <c r="J172" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -12333,10 +12327,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L172" s="19" t="n">
-        <v>-0.004289580349563814</v>
+        <v>-0.004289712148480808</v>
       </c>
       <c r="M172" s="19" t="n">
-        <v>-0.04947354614412347</v>
+        <v>-0.0494736722196113</v>
       </c>
       <c r="N172" s="20" t="n">
         <v>0</v>
@@ -12359,12 +12353,12 @@
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t>GAST @ UCF</t>
+          <t>UNC @ CLEM</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D173" s="22" t="n">
@@ -12372,34 +12366,32 @@
       </c>
       <c r="E173" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F173" s="12" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
-        </is>
-      </c>
-      <c r="G173" s="23" t="n">
-        <v>51.5</v>
-      </c>
+          <t>CLEM ML</t>
+        </is>
+      </c>
+      <c r="G173" s="23" t="n"/>
       <c r="H173" s="13" t="n">
-        <v>-112</v>
+        <v>-175</v>
       </c>
       <c r="I173" s="15" t="n">
-        <v>0.5021648524122808</v>
+        <v>0.6053583335867421</v>
       </c>
       <c r="J173" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.6092362344582594</v>
       </c>
       <c r="K173" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="L173" s="14" t="n">
-        <v>-0.004289712148480808</v>
+        <v>-0.006355676313682479</v>
       </c>
       <c r="M173" s="14" t="n">
-        <v>-0.0494736722196113</v>
+        <v>-0.0487226186494053</v>
       </c>
       <c r="N173" s="15" t="n">
         <v>0</v>
@@ -12798,12 +12790,12 @@
       </c>
       <c r="B180" s="17" t="inlineStr">
         <is>
-          <t>SYR @ PITT</t>
+          <t>TEM @ TOL</t>
         </is>
       </c>
       <c r="C180" s="17" t="inlineStr">
         <is>
-          <t>2026-09-17 23:30</t>
+          <t>2026-09-19 19:00</t>
         </is>
       </c>
       <c r="D180" s="25" t="n">
@@ -12811,34 +12803,34 @@
       </c>
       <c r="E180" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F180" s="17" t="inlineStr">
         <is>
-          <t>Under 50.5</t>
+          <t>TEM +5.5</t>
         </is>
       </c>
       <c r="G180" s="26" t="n">
-        <v>50.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H180" s="18" t="n">
-        <v>-102</v>
+        <v>-105</v>
       </c>
       <c r="I180" s="20" t="n">
-        <v>0.4753705883792458</v>
+        <v>0.4815174316606505</v>
       </c>
       <c r="J180" s="20" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K180" s="20" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L180" s="19" t="n">
-        <v>-0.01492861240241163</v>
+        <v>-0.01549579705339152</v>
       </c>
       <c r="M180" s="19" t="n">
-        <v>-0.05857981517051314</v>
+        <v>-0.05989453818634904</v>
       </c>
       <c r="N180" s="20" t="n">
         <v>0</v>
@@ -12922,12 +12914,12 @@
       </c>
       <c r="B182" s="17" t="inlineStr">
         <is>
-          <t>NCSU @ VAN</t>
+          <t>TEM @ TOL</t>
         </is>
       </c>
       <c r="C182" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:45</t>
+          <t>2026-09-19 19:00</t>
         </is>
       </c>
       <c r="D182" s="25" t="n">
@@ -12935,34 +12927,34 @@
       </c>
       <c r="E182" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F182" s="17" t="inlineStr">
         <is>
-          <t>NCSU +3.5</t>
+          <t>Under 50.5</t>
         </is>
       </c>
       <c r="G182" s="26" t="n">
-        <v>-3.5</v>
+        <v>50.5</v>
       </c>
       <c r="H182" s="18" t="n">
-        <v>-118</v>
+        <v>-105</v>
       </c>
       <c r="I182" s="20" t="n">
-        <v>0.5080913805190446</v>
+        <v>0.4806254575263966</v>
       </c>
       <c r="J182" s="20" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K182" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L182" s="19" t="n">
-        <v>-0.01771338763472689</v>
+        <v>-0.0172649854862639</v>
       </c>
       <c r="M182" s="19" t="n">
-        <v>-0.0613227037868499</v>
+        <v>-0.06163601149608278</v>
       </c>
       <c r="N182" s="20" t="n">
         <v>0</v>
@@ -12985,12 +12977,12 @@
       </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t>VT @ MD</t>
+          <t>NCSU @ VAN</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 16:45</t>
         </is>
       </c>
       <c r="D183" s="22" t="n">
@@ -12998,34 +12990,34 @@
       </c>
       <c r="E183" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F183" s="12" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>NCSU +3.5</t>
         </is>
       </c>
       <c r="G183" s="23" t="n">
-        <v>53.5</v>
+        <v>-3.5</v>
       </c>
       <c r="H183" s="13" t="n">
-        <v>-115</v>
+        <v>-118</v>
       </c>
       <c r="I183" s="15" t="n">
-        <v>0.5014263069005972</v>
+        <v>0.5080913805190446</v>
       </c>
       <c r="J183" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K183" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L183" s="14" t="n">
-        <v>-0.018189497221788</v>
+        <v>-0.01771338763472689</v>
       </c>
       <c r="M183" s="14" t="n">
-        <v>-0.0625508175336662</v>
+        <v>-0.0613227037868499</v>
       </c>
       <c r="N183" s="15" t="n">
         <v>0</v>
@@ -13048,7 +13040,7 @@
       </c>
       <c r="B184" s="17" t="inlineStr">
         <is>
-          <t>BYU @ CSU</t>
+          <t>VT @ MD</t>
         </is>
       </c>
       <c r="C184" s="17" t="inlineStr">
@@ -13066,17 +13058,17 @@
       </c>
       <c r="F184" s="17" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G184" s="26" t="n">
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
       <c r="H184" s="18" t="n">
         <v>-115</v>
       </c>
       <c r="I184" s="20" t="n">
-        <v>0.5014262848331477</v>
+        <v>0.5014263069005972</v>
       </c>
       <c r="J184" s="20" t="n">
         <v>0.5108342361863488</v>
@@ -13085,10 +13077,10 @@
         <v>0.5348837209302325</v>
       </c>
       <c r="L184" s="19" t="n">
-        <v>-0.01818953883695447</v>
+        <v>-0.018189497221788</v>
       </c>
       <c r="M184" s="19" t="n">
-        <v>-0.06255085879020228</v>
+        <v>-0.0625508175336662</v>
       </c>
       <c r="N184" s="20" t="n">
         <v>0</v>
@@ -13111,7 +13103,7 @@
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t>MSU @ ND</t>
+          <t>BYU @ CSU</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
@@ -13129,29 +13121,29 @@
       </c>
       <c r="F185" s="12" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="G185" s="23" t="n">
         <v>52.5</v>
       </c>
       <c r="H185" s="13" t="n">
-        <v>-102</v>
+        <v>-115</v>
       </c>
       <c r="I185" s="15" t="n">
-        <v>0.4733823060622933</v>
+        <v>0.5014262848331477</v>
       </c>
       <c r="J185" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K185" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L185" s="14" t="n">
-        <v>-0.0189168372395283</v>
+        <v>-0.01818953883695447</v>
       </c>
       <c r="M185" s="14" t="n">
-        <v>-0.0625173938766348</v>
+        <v>-0.06255085879020228</v>
       </c>
       <c r="N185" s="15" t="n">
         <v>0</v>
@@ -13174,12 +13166,12 @@
       </c>
       <c r="B186" s="17" t="inlineStr">
         <is>
-          <t>MRSH @ MOST</t>
+          <t>MSU @ ND</t>
         </is>
       </c>
       <c r="C186" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 22:30</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D186" s="25" t="n">
@@ -13192,29 +13184,29 @@
       </c>
       <c r="F186" s="17" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="G186" s="26" t="n">
-        <v>51.5</v>
+        <v>52.5</v>
       </c>
       <c r="H186" s="18" t="n">
-        <v>-108</v>
+        <v>-102</v>
       </c>
       <c r="I186" s="20" t="n">
-        <v>0.485869030825965</v>
+        <v>0.4733823060622933</v>
       </c>
       <c r="J186" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K186" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L186" s="19" t="n">
-        <v>-0.01949296671240393</v>
+        <v>-0.0189168372395283</v>
       </c>
       <c r="M186" s="19" t="n">
-        <v>-0.06425223692777104</v>
+        <v>-0.0625173938766348</v>
       </c>
       <c r="N186" s="20" t="n">
         <v>0</v>
@@ -13237,12 +13229,12 @@
       </c>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t>TEM @ TOL</t>
+          <t>MRSH @ MOST</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:00</t>
+          <t>2026-09-19 22:30</t>
         </is>
       </c>
       <c r="D187" s="22" t="n">
@@ -13250,34 +13242,34 @@
       </c>
       <c r="E187" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F187" s="12" t="inlineStr">
         <is>
-          <t>TEM +5.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G187" s="23" t="n">
-        <v>-5.5</v>
+        <v>51.5</v>
       </c>
       <c r="H187" s="13" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I187" s="15" t="n">
-        <v>0.4869345497538249</v>
+        <v>0.485869030825965</v>
       </c>
       <c r="J187" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K187" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L187" s="14" t="n">
-        <v>-0.02549123803810194</v>
+        <v>-0.01949296671240393</v>
       </c>
       <c r="M187" s="14" t="n">
-        <v>-0.0703976777426979</v>
+        <v>-0.06425223692777104</v>
       </c>
       <c r="N187" s="15" t="n">
         <v>0</v>
@@ -13626,34 +13618,34 @@
       </c>
       <c r="E193" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F193" s="12" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>OHIO +5.5</t>
         </is>
       </c>
       <c r="G193" s="23" t="n">
-        <v>51.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H193" s="13" t="n">
-        <v>-108</v>
+        <v>-118</v>
       </c>
       <c r="I193" s="15" t="n">
-        <v>0.4779129118190826</v>
+        <v>0.5001168720195683</v>
       </c>
       <c r="J193" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5173641257162701</v>
       </c>
       <c r="K193" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="L193" s="14" t="n">
-        <v>-0.03421804508283911</v>
+        <v>-0.03203261343636733</v>
       </c>
       <c r="M193" s="14" t="n">
-        <v>-0.07957513279287798</v>
+        <v>-0.07605527033672965</v>
       </c>
       <c r="N193" s="15" t="n">
         <v>0</v>
@@ -13676,12 +13668,12 @@
       </c>
       <c r="B194" s="17" t="inlineStr">
         <is>
-          <t>COLO @ NU</t>
+          <t>OHIO @ USA</t>
         </is>
       </c>
       <c r="C194" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D194" s="25" t="n">
@@ -13689,40 +13681,40 @@
       </c>
       <c r="E194" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F194" s="17" t="inlineStr">
         <is>
-          <t>COLO +3.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G194" s="26" t="n">
-        <v>-3.5</v>
+        <v>51.5</v>
       </c>
       <c r="H194" s="18" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I194" s="20" t="n">
-        <v>0.4702700415350176</v>
+        <v>0.4779129118190826</v>
       </c>
       <c r="J194" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K194" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L194" s="19" t="n">
-        <v>-0.03663153387249715</v>
+        <v>-0.03421804508283911</v>
       </c>
       <c r="M194" s="19" t="n">
-        <v>-0.0818537284316323</v>
+        <v>-0.07957513279287798</v>
       </c>
       <c r="N194" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O194" s="27" t="n">
-        <v>0.725</v>
+        <v>0.839</v>
       </c>
       <c r="P194" s="17" t="inlineStr">
         <is>
@@ -13739,12 +13731,12 @@
       </c>
       <c r="B195" s="12" t="inlineStr">
         <is>
-          <t>ASU @ KU</t>
+          <t>COLO @ NU</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D195" s="22" t="n">
@@ -13752,40 +13744,40 @@
       </c>
       <c r="E195" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F195" s="12" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>COLO +3.5</t>
         </is>
       </c>
       <c r="G195" s="23" t="n">
-        <v>51.5</v>
+        <v>-3.5</v>
       </c>
       <c r="H195" s="13" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="I195" s="15" t="n">
-        <v>0.4800777888540669</v>
+        <v>0.4702700415350176</v>
       </c>
       <c r="J195" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K195" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L195" s="14" t="n">
-        <v>-0.03766155893987126</v>
+        <v>-0.03663153387249715</v>
       </c>
       <c r="M195" s="14" t="n">
-        <v>-0.08348785764223576</v>
+        <v>-0.0818537284316323</v>
       </c>
       <c r="N195" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O195" s="24" t="n">
-        <v>0.839</v>
+        <v>0.725</v>
       </c>
       <c r="P195" s="12" t="inlineStr">
         <is>
@@ -13802,12 +13794,12 @@
       </c>
       <c r="B196" s="17" t="inlineStr">
         <is>
-          <t>TULN @ KSU</t>
+          <t>LT @ BAY</t>
         </is>
       </c>
       <c r="C196" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D196" s="25" t="n">
@@ -13820,29 +13812,29 @@
       </c>
       <c r="F196" s="17" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="G196" s="26" t="n">
-        <v>49.5</v>
+        <v>53.5</v>
       </c>
       <c r="H196" s="18" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I196" s="20" t="n">
-        <v>0.480077758966456</v>
+        <v>0.4759283852644601</v>
       </c>
       <c r="J196" s="20" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K196" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L196" s="19" t="n">
-        <v>-0.03766160932064762</v>
+        <v>-0.03764823725098458</v>
       </c>
       <c r="M196" s="19" t="n">
-        <v>-0.08348791470040218</v>
+        <v>-0.08339718393511375</v>
       </c>
       <c r="N196" s="20" t="n">
         <v>0</v>
@@ -13865,12 +13857,12 @@
       </c>
       <c r="B197" s="12" t="inlineStr">
         <is>
-          <t>BUFF @ PSU</t>
+          <t>BALL @ LIB</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D197" s="22" t="n">
@@ -13883,29 +13875,29 @@
       </c>
       <c r="F197" s="12" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>Under 49.5</t>
         </is>
       </c>
       <c r="G197" s="23" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="H197" s="13" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I197" s="15" t="n">
-        <v>0.4800777277523177</v>
+        <v>0.4759283281732838</v>
       </c>
       <c r="J197" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K197" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L197" s="14" t="n">
-        <v>-0.03766166193749009</v>
+        <v>-0.03764833434153798</v>
       </c>
       <c r="M197" s="14" t="n">
-        <v>-0.08348797429102972</v>
+        <v>-0.08339729388849038</v>
       </c>
       <c r="N197" s="15" t="n">
         <v>0</v>
@@ -13928,12 +13920,12 @@
       </c>
       <c r="B198" s="17" t="inlineStr">
         <is>
-          <t>UAB @ UL</t>
+          <t>TULN @ KSU</t>
         </is>
       </c>
       <c r="C198" s="17" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D198" s="25" t="n">
@@ -13941,32 +13933,34 @@
       </c>
       <c r="E198" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F198" s="17" t="inlineStr">
         <is>
-          <t>UL ML</t>
-        </is>
-      </c>
-      <c r="G198" s="26" t="n"/>
+          <t>Under 49.5</t>
+        </is>
+      </c>
+      <c r="G198" s="26" t="n">
+        <v>49.5</v>
+      </c>
       <c r="H198" s="18" t="n">
-        <v>-310</v>
+        <v>-110</v>
       </c>
       <c r="I198" s="20" t="n">
-        <v>0.6940263514324089</v>
+        <v>0.480077758966456</v>
       </c>
       <c r="J198" s="20" t="n">
-        <v>0.725752508361204</v>
+        <v>0.5</v>
       </c>
       <c r="K198" s="20" t="n">
-        <v>0.7560975609756098</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L198" s="19" t="n">
-        <v>-0.04087009668957784</v>
+        <v>-0.03766160932064762</v>
       </c>
       <c r="M198" s="19" t="n">
-        <v>-0.08209418036358829</v>
+        <v>-0.08348791470040218</v>
       </c>
       <c r="N198" s="20" t="n">
         <v>0</v>
@@ -13989,12 +13983,12 @@
       </c>
       <c r="B199" s="12" t="inlineStr">
         <is>
-          <t>NCSU @ VAN</t>
+          <t>BUFF @ PSU</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 16:45</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D199" s="22" t="n">
@@ -14007,29 +14001,29 @@
       </c>
       <c r="F199" s="12" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="G199" s="23" t="n">
-        <v>51.5</v>
+        <v>48.5</v>
       </c>
       <c r="H199" s="13" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I199" s="15" t="n">
-        <v>0.4874814491661821</v>
+        <v>0.4800777277523177</v>
       </c>
       <c r="J199" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5</v>
       </c>
       <c r="K199" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L199" s="14" t="n">
-        <v>-0.04248519273151656</v>
+        <v>-0.03766166193749009</v>
       </c>
       <c r="M199" s="14" t="n">
-        <v>-0.08862163851539884</v>
+        <v>-0.08348797429102972</v>
       </c>
       <c r="N199" s="15" t="n">
         <v>0</v>
@@ -14052,12 +14046,12 @@
       </c>
       <c r="B200" s="17" t="inlineStr">
         <is>
-          <t>LT @ BAY</t>
+          <t>UAB @ UL</t>
         </is>
       </c>
       <c r="C200" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D200" s="25" t="n">
@@ -14065,34 +14059,32 @@
       </c>
       <c r="E200" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F200" s="17" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
-        </is>
-      </c>
-      <c r="G200" s="26" t="n">
-        <v>53.5</v>
-      </c>
+          <t>UL ML</t>
+        </is>
+      </c>
+      <c r="G200" s="26" t="n"/>
       <c r="H200" s="18" t="n">
-        <v>-112</v>
+        <v>-310</v>
       </c>
       <c r="I200" s="20" t="n">
-        <v>0.480258139334429</v>
+        <v>0.6940263514324089</v>
       </c>
       <c r="J200" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.725752508361204</v>
       </c>
       <c r="K200" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.7560975609756098</v>
       </c>
       <c r="L200" s="19" t="n">
-        <v>-0.04408174129539089</v>
+        <v>-0.04087009668957784</v>
       </c>
       <c r="M200" s="19" t="n">
-        <v>-0.09093995054554527</v>
+        <v>-0.08209418036358829</v>
       </c>
       <c r="N200" s="20" t="n">
         <v>0</v>
@@ -14115,12 +14107,12 @@
       </c>
       <c r="B201" s="12" t="inlineStr">
         <is>
-          <t>BALL @ LIB</t>
+          <t>NCSU @ VAN</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-19 16:45</t>
         </is>
       </c>
       <c r="D201" s="22" t="n">
@@ -14133,29 +14125,29 @@
       </c>
       <c r="F201" s="12" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G201" s="23" t="n">
-        <v>49.5</v>
+        <v>51.5</v>
       </c>
       <c r="H201" s="13" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I201" s="15" t="n">
-        <v>0.4802580822432527</v>
+        <v>0.4874814491661821</v>
       </c>
       <c r="J201" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K201" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L201" s="14" t="n">
-        <v>-0.04408183012353974</v>
+        <v>-0.04248519273151656</v>
       </c>
       <c r="M201" s="14" t="n">
-        <v>-0.09094005861098597</v>
+        <v>-0.08862163851539884</v>
       </c>
       <c r="N201" s="15" t="n">
         <v>0</v>
@@ -14178,7 +14170,7 @@
       </c>
       <c r="B202" s="17" t="inlineStr">
         <is>
-          <t>OHIO @ USA</t>
+          <t>GASO @ JVST</t>
         </is>
       </c>
       <c r="C202" s="17" t="inlineStr">
@@ -14196,32 +14188,32 @@
       </c>
       <c r="F202" s="17" t="inlineStr">
         <is>
-          <t>OHIO +4.5</t>
+          <t>GASO +3</t>
         </is>
       </c>
       <c r="G202" s="26" t="n">
-        <v>-4.5</v>
+        <v>-3</v>
       </c>
       <c r="H202" s="18" t="n">
-        <v>-115</v>
+        <v>102</v>
       </c>
       <c r="I202" s="20" t="n">
-        <v>0.4844946709563394</v>
+        <v>0.4514699861434015</v>
       </c>
       <c r="J202" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.4739134147382802</v>
       </c>
       <c r="K202" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.495049504950495</v>
       </c>
       <c r="L202" s="19" t="n">
-        <v>-0.04703180838894528</v>
+        <v>-0.043789106549648</v>
       </c>
       <c r="M202" s="19" t="n">
-        <v>-0.09420561516858306</v>
+        <v>-0.08272238112251207</v>
       </c>
       <c r="N202" s="20" t="n">
-        <v>0</v>
+        <v>0.0603</v>
       </c>
       <c r="O202" s="27" t="n">
         <v>0.839</v>
@@ -14241,12 +14233,12 @@
       </c>
       <c r="B203" s="12" t="inlineStr">
         <is>
-          <t>FIU @ FAU</t>
+          <t>OHIO @ USA</t>
         </is>
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D203" s="22" t="n">
@@ -14259,27 +14251,27 @@
       </c>
       <c r="F203" s="12" t="inlineStr">
         <is>
-          <t>FAU ML</t>
+          <t>OHIO ML</t>
         </is>
       </c>
       <c r="G203" s="23" t="n"/>
       <c r="H203" s="13" t="n">
-        <v>-250</v>
+        <v>180</v>
       </c>
       <c r="I203" s="15" t="n">
-        <v>0.6491394483291937</v>
+        <v>0.3257650214448146</v>
       </c>
       <c r="J203" s="15" t="n">
-        <v>0.6853932584269663</v>
+        <v>0.3425247738043947</v>
       </c>
       <c r="K203" s="15" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L203" s="14" t="n">
-        <v>-0.04803111775364441</v>
+        <v>-0.0450179318888992</v>
       </c>
       <c r="M203" s="14" t="n">
-        <v>-0.09120477233912894</v>
+        <v>-0.08785793995451929</v>
       </c>
       <c r="N203" s="15" t="n">
         <v>0</v>
@@ -14302,12 +14294,12 @@
       </c>
       <c r="B204" s="17" t="inlineStr">
         <is>
-          <t>UTEP @ MICH</t>
+          <t>ASU @ KU</t>
         </is>
       </c>
       <c r="C204" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D204" s="25" t="n">
@@ -14320,17 +14312,17 @@
       </c>
       <c r="F204" s="17" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G204" s="26" t="n">
-        <v>48.5</v>
+        <v>51.5</v>
       </c>
       <c r="H204" s="18" t="n">
         <v>-115</v>
       </c>
       <c r="I204" s="20" t="n">
-        <v>0.4835102934077787</v>
+        <v>0.4854949069472414</v>
       </c>
       <c r="J204" s="20" t="n">
         <v>0.5108342361863488</v>
@@ -14339,10 +14331,10 @@
         <v>0.5348837209302325</v>
       </c>
       <c r="L204" s="19" t="n">
-        <v>-0.04847184985543468</v>
+        <v>-0.04553864828568632</v>
       </c>
       <c r="M204" s="19" t="n">
-        <v>-0.09604597319415287</v>
+        <v>-0.09233560875080959</v>
       </c>
       <c r="N204" s="20" t="n">
         <v>0</v>
@@ -14365,12 +14357,12 @@
       </c>
       <c r="B205" s="12" t="inlineStr">
         <is>
-          <t>GASO @ JVST</t>
+          <t>UTEP @ MICH</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D205" s="22" t="n">
@@ -14378,37 +14370,37 @@
       </c>
       <c r="E205" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F205" s="12" t="inlineStr">
         <is>
-          <t>GASO +3</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="G205" s="23" t="n">
-        <v>-3</v>
+        <v>48.5</v>
       </c>
       <c r="H205" s="13" t="n">
-        <v>-102</v>
+        <v>-115</v>
       </c>
       <c r="I205" s="15" t="n">
-        <v>0.4558312159161263</v>
+        <v>0.4835102934077787</v>
       </c>
       <c r="J205" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K205" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L205" s="14" t="n">
-        <v>-0.04997083654564062</v>
+        <v>-0.04847184985543468</v>
       </c>
       <c r="M205" s="14" t="n">
-        <v>-0.0914097264071613</v>
+        <v>-0.09604597319415287</v>
       </c>
       <c r="N205" s="15" t="n">
-        <v>0.0603</v>
+        <v>0</v>
       </c>
       <c r="O205" s="24" t="n">
         <v>0.839</v>
@@ -14428,12 +14420,12 @@
       </c>
       <c r="B206" s="17" t="inlineStr">
         <is>
-          <t>CLT @ APP</t>
+          <t>GASO @ JVST</t>
         </is>
       </c>
       <c r="C206" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D206" s="25" t="n">
@@ -14441,34 +14433,32 @@
       </c>
       <c r="E206" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F206" s="17" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
-        </is>
-      </c>
-      <c r="G206" s="26" t="n">
-        <v>51.5</v>
-      </c>
+          <t>GASO ML</t>
+        </is>
+      </c>
+      <c r="G206" s="26" t="n"/>
       <c r="H206" s="18" t="n">
-        <v>-115</v>
+        <v>150</v>
       </c>
       <c r="I206" s="20" t="n">
-        <v>0.4815279804051003</v>
+        <v>0.3627575403170191</v>
       </c>
       <c r="J206" s="20" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.3835616438356164</v>
       </c>
       <c r="K206" s="20" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.4</v>
       </c>
       <c r="L206" s="19" t="n">
-        <v>-0.05128201958250349</v>
+        <v>-0.04902465989302795</v>
       </c>
       <c r="M206" s="19" t="n">
-        <v>-0.09975203663394305</v>
+        <v>-0.09310614920745219</v>
       </c>
       <c r="N206" s="20" t="n">
         <v>0</v>
@@ -14491,12 +14481,12 @@
       </c>
       <c r="B207" s="12" t="inlineStr">
         <is>
-          <t>NDSU @ SAC</t>
+          <t>CLT @ APP</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 02:30</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D207" s="22" t="n">
@@ -14509,35 +14499,35 @@
       </c>
       <c r="F207" s="12" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="G207" s="23" t="n">
-        <v>52.5</v>
+        <v>51.5</v>
       </c>
       <c r="H207" s="13" t="n">
-        <v>-102</v>
+        <v>-115</v>
       </c>
       <c r="I207" s="15" t="n">
-        <v>0.4536297311797856</v>
+        <v>0.4815279804051003</v>
       </c>
       <c r="J207" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K207" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L207" s="14" t="n">
-        <v>-0.05318646381742838</v>
+        <v>-0.05128201958250349</v>
       </c>
       <c r="M207" s="14" t="n">
-        <v>-0.1016352382517972</v>
+        <v>-0.09975203663394305</v>
       </c>
       <c r="N207" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O207" s="24" t="n">
-        <v>0.926</v>
+        <v>0.839</v>
       </c>
       <c r="P207" s="12" t="inlineStr">
         <is>
@@ -14554,12 +14544,12 @@
       </c>
       <c r="B208" s="17" t="inlineStr">
         <is>
-          <t>TEM @ TOL</t>
+          <t>NDSU @ SAC</t>
         </is>
       </c>
       <c r="C208" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 19:00</t>
+          <t>2026-09-20 02:30</t>
         </is>
       </c>
       <c r="D208" s="25" t="n">
@@ -14567,38 +14557,40 @@
       </c>
       <c r="E208" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F208" s="17" t="inlineStr">
         <is>
-          <t>TEM ML</t>
-        </is>
-      </c>
-      <c r="G208" s="26" t="n"/>
+          <t>Over 52.5</t>
+        </is>
+      </c>
+      <c r="G208" s="26" t="n">
+        <v>52.5</v>
+      </c>
       <c r="H208" s="18" t="n">
-        <v>180</v>
+        <v>-102</v>
       </c>
       <c r="I208" s="20" t="n">
-        <v>0.3218143749297715</v>
+        <v>0.4536297311797856</v>
       </c>
       <c r="J208" s="20" t="n">
-        <v>0.3425247738043947</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K208" s="20" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L208" s="19" t="n">
-        <v>-0.05343618392095172</v>
+        <v>-0.05318646381742838</v>
       </c>
       <c r="M208" s="19" t="n">
-        <v>-0.0989197501966399</v>
+        <v>-0.1016352382517972</v>
       </c>
       <c r="N208" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O208" s="27" t="n">
-        <v>0.839</v>
+        <v>0.926</v>
       </c>
       <c r="P208" s="17" t="inlineStr">
         <is>
@@ -14615,12 +14607,12 @@
       </c>
       <c r="B209" s="12" t="inlineStr">
         <is>
-          <t>STAN @ DUKE</t>
+          <t>TEM @ TOL</t>
         </is>
       </c>
       <c r="C209" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-19 19:00</t>
         </is>
       </c>
       <c r="D209" s="22" t="n">
@@ -14633,27 +14625,27 @@
       </c>
       <c r="F209" s="12" t="inlineStr">
         <is>
-          <t>DUKE ML</t>
+          <t>TEM ML</t>
         </is>
       </c>
       <c r="G209" s="23" t="n"/>
       <c r="H209" s="13" t="n">
-        <v>-375</v>
+        <v>180</v>
       </c>
       <c r="I209" s="15" t="n">
-        <v>0.7082831892859056</v>
+        <v>0.3218143749297715</v>
       </c>
       <c r="J209" s="15" t="n">
-        <v>0.7571884984025559</v>
+        <v>0.3425247738043947</v>
       </c>
       <c r="K209" s="15" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="L209" s="14" t="n">
-        <v>-0.05618655651003966</v>
+        <v>-0.05343618392095172</v>
       </c>
       <c r="M209" s="14" t="n">
-        <v>-0.1028412935711863</v>
+        <v>-0.0989197501966399</v>
       </c>
       <c r="N209" s="15" t="n">
         <v>0</v>
@@ -14676,12 +14668,12 @@
       </c>
       <c r="B210" s="17" t="inlineStr">
         <is>
-          <t>SYR @ PITT</t>
+          <t>STAN @ DUKE</t>
         </is>
       </c>
       <c r="C210" s="17" t="inlineStr">
         <is>
-          <t>2026-09-17 23:30</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D210" s="25" t="n">
@@ -14694,27 +14686,27 @@
       </c>
       <c r="F210" s="17" t="inlineStr">
         <is>
-          <t>PITT ML</t>
+          <t>DUKE ML</t>
         </is>
       </c>
       <c r="G210" s="26" t="n"/>
       <c r="H210" s="18" t="n">
-        <v>-380</v>
+        <v>-375</v>
       </c>
       <c r="I210" s="20" t="n">
-        <v>0.7096889400846278</v>
+        <v>0.7082831892859056</v>
       </c>
       <c r="J210" s="20" t="n">
-        <v>0.7600000000000001</v>
+        <v>0.7571884984025559</v>
       </c>
       <c r="K210" s="20" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="L210" s="19" t="n">
-        <v>-0.0572233653165885</v>
+        <v>-0.05618655651003966</v>
       </c>
       <c r="M210" s="19" t="n">
-        <v>-0.1035508125246807</v>
+        <v>-0.1028412935711863</v>
       </c>
       <c r="N210" s="20" t="n">
         <v>0</v>
@@ -14737,12 +14729,12 @@
       </c>
       <c r="B211" s="12" t="inlineStr">
         <is>
-          <t>M-OH @ CIN</t>
+          <t>FIU @ FAU</t>
         </is>
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D211" s="22" t="n">
@@ -14750,34 +14742,32 @@
       </c>
       <c r="E211" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F211" s="12" t="inlineStr">
         <is>
-          <t>Under 50.5</t>
-        </is>
-      </c>
-      <c r="G211" s="23" t="n">
-        <v>50.5</v>
-      </c>
+          <t>FAU ML</t>
+        </is>
+      </c>
+      <c r="G211" s="23" t="n"/>
       <c r="H211" s="13" t="n">
-        <v>-102</v>
+        <v>-278</v>
       </c>
       <c r="I211" s="15" t="n">
-        <v>0.4497177517892554</v>
+        <v>0.6589594012460265</v>
       </c>
       <c r="J211" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.705033164260632</v>
       </c>
       <c r="K211" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.7354497354497355</v>
       </c>
       <c r="L211" s="14" t="n">
-        <v>-0.0584853695896224</v>
+        <v>-0.05667950385636537</v>
       </c>
       <c r="M211" s="14" t="n">
-        <v>-0.1093824915546118</v>
+        <v>-0.1040048429100792</v>
       </c>
       <c r="N211" s="15" t="n">
         <v>0</v>
@@ -14800,12 +14790,12 @@
       </c>
       <c r="B212" s="17" t="inlineStr">
         <is>
-          <t>COLO @ NU</t>
+          <t>SYR @ PITT</t>
         </is>
       </c>
       <c r="C212" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-17 23:30</t>
         </is>
       </c>
       <c r="D212" s="25" t="n">
@@ -14818,33 +14808,33 @@
       </c>
       <c r="F212" s="17" t="inlineStr">
         <is>
-          <t>COLO ML</t>
+          <t>PITT ML</t>
         </is>
       </c>
       <c r="G212" s="26" t="n"/>
       <c r="H212" s="18" t="n">
-        <v>150</v>
+        <v>-380</v>
       </c>
       <c r="I212" s="20" t="n">
-        <v>0.3571954489739273</v>
+        <v>0.7096889400846278</v>
       </c>
       <c r="J212" s="20" t="n">
-        <v>0.3835616438356164</v>
+        <v>0.7600000000000001</v>
       </c>
       <c r="K212" s="20" t="n">
-        <v>0.4</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="L212" s="19" t="n">
-        <v>-0.05881679195126074</v>
+        <v>-0.0572233653165885</v>
       </c>
       <c r="M212" s="19" t="n">
-        <v>-0.1070113775651818</v>
+        <v>-0.1035508125246807</v>
       </c>
       <c r="N212" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O212" s="27" t="n">
-        <v>0.725</v>
+        <v>0.839</v>
       </c>
       <c r="P212" s="17" t="inlineStr">
         <is>
@@ -14861,12 +14851,12 @@
       </c>
       <c r="B213" s="12" t="inlineStr">
         <is>
-          <t>GASO @ JVST</t>
+          <t>M-OH @ CIN</t>
         </is>
       </c>
       <c r="C213" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D213" s="22" t="n">
@@ -14874,32 +14864,34 @@
       </c>
       <c r="E213" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F213" s="12" t="inlineStr">
         <is>
-          <t>GASO ML</t>
-        </is>
-      </c>
-      <c r="G213" s="23" t="n"/>
+          <t>Under 50.5</t>
+        </is>
+      </c>
+      <c r="G213" s="23" t="n">
+        <v>50.5</v>
+      </c>
       <c r="H213" s="13" t="n">
-        <v>140</v>
+        <v>-102</v>
       </c>
       <c r="I213" s="15" t="n">
-        <v>0.3711573324871098</v>
+        <v>0.4497177517892554</v>
       </c>
       <c r="J213" s="15" t="n">
-        <v>0.4003612281757977</v>
+        <v>0.4826358742837298</v>
       </c>
       <c r="K213" s="15" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="L213" s="14" t="n">
-        <v>-0.06133826608661176</v>
+        <v>-0.0584853695896224</v>
       </c>
       <c r="M213" s="14" t="n">
-        <v>-0.1092224020309365</v>
+        <v>-0.1093824915546118</v>
       </c>
       <c r="N213" s="15" t="n">
         <v>0</v>
@@ -14922,12 +14914,12 @@
       </c>
       <c r="B214" s="17" t="inlineStr">
         <is>
-          <t>ECU @ ODU</t>
+          <t>COLO @ NU</t>
         </is>
       </c>
       <c r="C214" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D214" s="25" t="n">
@@ -14935,40 +14927,38 @@
       </c>
       <c r="E214" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F214" s="17" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
-        </is>
-      </c>
-      <c r="G214" s="26" t="n">
-        <v>49.5</v>
-      </c>
+          <t>COLO ML</t>
+        </is>
+      </c>
+      <c r="G214" s="26" t="n"/>
       <c r="H214" s="18" t="n">
-        <v>-110</v>
+        <v>150</v>
       </c>
       <c r="I214" s="20" t="n">
-        <v>0.4623117303209874</v>
+        <v>0.3571954489739273</v>
       </c>
       <c r="J214" s="20" t="n">
-        <v>0.5</v>
+        <v>0.3835616438356164</v>
       </c>
       <c r="K214" s="20" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.4</v>
       </c>
       <c r="L214" s="19" t="n">
-        <v>-0.0627334237387708</v>
+        <v>-0.05881679195126074</v>
       </c>
       <c r="M214" s="19" t="n">
-        <v>-0.117404878478115</v>
+        <v>-0.1070113775651818</v>
       </c>
       <c r="N214" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O214" s="27" t="n">
-        <v>0.839</v>
+        <v>0.725</v>
       </c>
       <c r="P214" s="17" t="inlineStr">
         <is>
@@ -14985,12 +14975,12 @@
       </c>
       <c r="B215" s="12" t="inlineStr">
         <is>
-          <t>FLA @ AUB</t>
+          <t>ECU @ ODU</t>
         </is>
       </c>
       <c r="C215" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D215" s="22" t="n">
@@ -15003,29 +14993,29 @@
       </c>
       <c r="F215" s="12" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>Under 49.5</t>
         </is>
       </c>
       <c r="G215" s="23" t="n">
-        <v>53.5</v>
+        <v>49.5</v>
       </c>
       <c r="H215" s="13" t="n">
         <v>-110</v>
       </c>
       <c r="I215" s="15" t="n">
-        <v>0.4614513123747238</v>
+        <v>0.4623117303209874</v>
       </c>
       <c r="J215" s="15" t="n">
-        <v>0.5021949078138718</v>
+        <v>0.5</v>
       </c>
       <c r="K215" s="15" t="n">
         <v>0.5238095238095238</v>
       </c>
       <c r="L215" s="14" t="n">
-        <v>-0.0658501126740325</v>
+        <v>-0.0627334237387708</v>
       </c>
       <c r="M215" s="14" t="n">
-        <v>-0.1190474945573454</v>
+        <v>-0.117404878478115</v>
       </c>
       <c r="N215" s="15" t="n">
         <v>0</v>
@@ -15048,12 +15038,12 @@
       </c>
       <c r="B216" s="17" t="inlineStr">
         <is>
-          <t>HOU @ TTU</t>
+          <t>UK @ TA&amp;M</t>
         </is>
       </c>
       <c r="C216" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 00:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D216" s="25" t="n">
@@ -15061,22 +15051,22 @@
       </c>
       <c r="E216" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F216" s="17" t="inlineStr">
         <is>
-          <t>TTU -7.5</t>
+          <t>Under 50.5</t>
         </is>
       </c>
       <c r="G216" s="26" t="n">
-        <v>-7.5</v>
+        <v>50.5</v>
       </c>
       <c r="H216" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I216" s="20" t="n">
-        <v>0.4633466590589891</v>
+        <v>0.4644766198726817</v>
       </c>
       <c r="J216" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -15085,10 +15075,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L216" s="19" t="n">
-        <v>-0.06591834269153674</v>
+        <v>-0.06473745029899024</v>
       </c>
       <c r="M216" s="19" t="n">
-        <v>-0.1229509667811992</v>
+        <v>-0.1208121123838525</v>
       </c>
       <c r="N216" s="20" t="n">
         <v>0</v>
@@ -15111,7 +15101,7 @@
       </c>
       <c r="B217" s="12" t="inlineStr">
         <is>
-          <t>OHIO @ USA</t>
+          <t>FLA @ AUB</t>
         </is>
       </c>
       <c r="C217" s="12" t="inlineStr">
@@ -15124,32 +15114,34 @@
       </c>
       <c r="E217" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F217" s="12" t="inlineStr">
         <is>
-          <t>OHIO ML</t>
-        </is>
-      </c>
-      <c r="G217" s="23" t="n"/>
+          <t>Over 53.5</t>
+        </is>
+      </c>
+      <c r="G217" s="23" t="n">
+        <v>53.5</v>
+      </c>
       <c r="H217" s="13" t="n">
-        <v>160</v>
+        <v>-110</v>
       </c>
       <c r="I217" s="15" t="n">
-        <v>0.3390324626518184</v>
+        <v>0.4614513123747238</v>
       </c>
       <c r="J217" s="15" t="n">
-        <v>0.3690596562184025</v>
+        <v>0.5021949078138718</v>
       </c>
       <c r="K217" s="15" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L217" s="14" t="n">
-        <v>-0.0659695668744965</v>
+        <v>-0.0658501126740325</v>
       </c>
       <c r="M217" s="14" t="n">
-        <v>-0.1185155971052722</v>
+        <v>-0.1190474945573454</v>
       </c>
       <c r="N217" s="15" t="n">
         <v>0</v>
@@ -15172,12 +15164,12 @@
       </c>
       <c r="B218" s="17" t="inlineStr">
         <is>
-          <t>CONN @ USM</t>
+          <t>HOU @ TTU</t>
         </is>
       </c>
       <c r="C218" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 00:00</t>
         </is>
       </c>
       <c r="D218" s="25" t="n">
@@ -15185,22 +15177,22 @@
       </c>
       <c r="E218" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F218" s="17" t="inlineStr">
         <is>
-          <t>Over 54.5</t>
+          <t>TTU -7.5</t>
         </is>
       </c>
       <c r="G218" s="26" t="n">
-        <v>54.5</v>
+        <v>-7.5</v>
       </c>
       <c r="H218" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I218" s="20" t="n">
-        <v>0.4625187268183728</v>
+        <v>0.4633466590589891</v>
       </c>
       <c r="J218" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -15209,10 +15201,10 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L218" s="19" t="n">
-        <v>-0.06675942504984723</v>
+        <v>-0.06591834269153674</v>
       </c>
       <c r="M218" s="19" t="n">
-        <v>-0.1245181242366515</v>
+        <v>-0.1229509667811992</v>
       </c>
       <c r="N218" s="20" t="n">
         <v>0</v>
@@ -15235,12 +15227,12 @@
       </c>
       <c r="B219" s="12" t="inlineStr">
         <is>
-          <t>PUR @ UCLA</t>
+          <t>CONN @ USM</t>
         </is>
       </c>
       <c r="C219" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 03:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D219" s="22" t="n">
@@ -15248,32 +15240,34 @@
       </c>
       <c r="E219" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F219" s="12" t="inlineStr">
         <is>
-          <t>UCLA ML</t>
-        </is>
-      </c>
-      <c r="G219" s="23" t="n"/>
+          <t>Over 54.5</t>
+        </is>
+      </c>
+      <c r="G219" s="23" t="n">
+        <v>54.5</v>
+      </c>
       <c r="H219" s="13" t="n">
-        <v>-700</v>
+        <v>-112</v>
       </c>
       <c r="I219" s="15" t="n">
-        <v>0.7691944299789779</v>
+        <v>0.4625187268183728</v>
       </c>
       <c r="J219" s="15" t="n">
-        <v>0.84</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K219" s="15" t="n">
-        <v>0.875</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L219" s="14" t="n">
-        <v>-0.06745489826432</v>
+        <v>-0.06675942504984723</v>
       </c>
       <c r="M219" s="14" t="n">
-        <v>-0.1209206514525967</v>
+        <v>-0.1245181242366515</v>
       </c>
       <c r="N219" s="15" t="n">
         <v>0</v>
@@ -15286,11 +15280,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q219" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q219" s="12" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="17" t="inlineStr">
@@ -15300,12 +15290,12 @@
       </c>
       <c r="B220" s="17" t="inlineStr">
         <is>
-          <t>JMU @ SDSU</t>
+          <t>PUR @ UCLA</t>
         </is>
       </c>
       <c r="C220" s="17" t="inlineStr">
         <is>
-          <t>2026-09-20 02:00</t>
+          <t>2026-09-20 03:00</t>
         </is>
       </c>
       <c r="D220" s="25" t="n">
@@ -15313,34 +15303,32 @@
       </c>
       <c r="E220" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F220" s="17" t="inlineStr">
         <is>
-          <t>JMU +2.5</t>
-        </is>
-      </c>
-      <c r="G220" s="26" t="n">
-        <v>-2.5</v>
-      </c>
+          <t>UCLA ML</t>
+        </is>
+      </c>
+      <c r="G220" s="26" t="n"/>
       <c r="H220" s="18" t="n">
-        <v>-108</v>
+        <v>-700</v>
       </c>
       <c r="I220" s="20" t="n">
-        <v>0.4537735800127758</v>
+        <v>0.7691944299789779</v>
       </c>
       <c r="J220" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.84</v>
       </c>
       <c r="K220" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.875</v>
       </c>
       <c r="L220" s="19" t="n">
-        <v>-0.06757019217948999</v>
+        <v>-0.06745489826432</v>
       </c>
       <c r="M220" s="19" t="n">
-        <v>-0.1260656977531724</v>
+        <v>-0.1209206514525967</v>
       </c>
       <c r="N220" s="20" t="n">
         <v>0</v>
@@ -15353,7 +15341,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q220" s="17" t="n"/>
+      <c r="Q220" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="12" t="inlineStr">
@@ -15363,12 +15355,12 @@
       </c>
       <c r="B221" s="12" t="inlineStr">
         <is>
-          <t>UK @ TA&amp;M</t>
+          <t>JMU @ SDSU</t>
         </is>
       </c>
       <c r="C221" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-20 02:00</t>
         </is>
       </c>
       <c r="D221" s="22" t="n">
@@ -15376,32 +15368,34 @@
       </c>
       <c r="E221" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F221" s="12" t="inlineStr">
         <is>
-          <t>TA&amp;M ML</t>
-        </is>
-      </c>
-      <c r="G221" s="23" t="n"/>
+          <t>JMU +2.5</t>
+        </is>
+      </c>
+      <c r="G221" s="23" t="n">
+        <v>-2.5</v>
+      </c>
       <c r="H221" s="13" t="n">
-        <v>-850</v>
+        <v>-108</v>
       </c>
       <c r="I221" s="15" t="n">
-        <v>0.7840769193671434</v>
+        <v>0.4537735800127758</v>
       </c>
       <c r="J221" s="15" t="n">
-        <v>0.8579439252336449</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K221" s="15" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L221" s="14" t="n">
-        <v>-0.06833802271869539</v>
+        <v>-0.06757019217948999</v>
       </c>
       <c r="M221" s="14" t="n">
-        <v>-0.1236787371778986</v>
+        <v>-0.1260656977531724</v>
       </c>
       <c r="N221" s="15" t="n">
         <v>0</v>
@@ -15414,11 +15408,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q221" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q221" s="12" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="17" t="inlineStr">
@@ -15428,7 +15418,7 @@
       </c>
       <c r="B222" s="17" t="inlineStr">
         <is>
-          <t>FSU @ ALA</t>
+          <t>UK @ TA&amp;M</t>
         </is>
       </c>
       <c r="C222" s="17" t="inlineStr">
@@ -15441,34 +15431,32 @@
       </c>
       <c r="E222" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F222" s="17" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
-        </is>
-      </c>
-      <c r="G222" s="26" t="n">
-        <v>49.5</v>
-      </c>
+          <t>TA&amp;M ML</t>
+        </is>
+      </c>
+      <c r="G222" s="26" t="n"/>
       <c r="H222" s="18" t="n">
-        <v>-112</v>
+        <v>-850</v>
       </c>
       <c r="I222" s="20" t="n">
-        <v>0.4605646802600389</v>
+        <v>0.7840769193671434</v>
       </c>
       <c r="J222" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.8579439252336449</v>
       </c>
       <c r="K222" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="L222" s="19" t="n">
-        <v>-0.06866493014955929</v>
+        <v>-0.06833802271869539</v>
       </c>
       <c r="M222" s="19" t="n">
-        <v>-0.1282168552220692</v>
+        <v>-0.1236787371778986</v>
       </c>
       <c r="N222" s="20" t="n">
         <v>0</v>
@@ -15481,7 +15469,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q222" s="17" t="n"/>
+      <c r="Q222" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="12" t="inlineStr">
@@ -15491,12 +15483,12 @@
       </c>
       <c r="B223" s="12" t="inlineStr">
         <is>
-          <t>AKR @ MINN</t>
+          <t>FSU @ ALA</t>
         </is>
       </c>
       <c r="C223" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D223" s="22" t="n">
@@ -15516,22 +15508,22 @@
         <v>49.5</v>
       </c>
       <c r="H223" s="13" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="I223" s="15" t="n">
-        <v>0.4657709273155551</v>
+        <v>0.4605646802600389</v>
       </c>
       <c r="J223" s="15" t="n">
-        <v>0.5108342361863488</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K223" s="15" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L223" s="14" t="n">
-        <v>-0.06934347438782833</v>
+        <v>-0.06866493014955929</v>
       </c>
       <c r="M223" s="14" t="n">
-        <v>-0.1292108750187448</v>
+        <v>-0.1282168552220692</v>
       </c>
       <c r="N223" s="15" t="n">
         <v>0</v>
@@ -15554,12 +15546,12 @@
       </c>
       <c r="B224" s="17" t="inlineStr">
         <is>
-          <t>COLO @ NU</t>
+          <t>AKR @ MINN</t>
         </is>
       </c>
       <c r="C224" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D224" s="25" t="n">
@@ -15572,35 +15564,35 @@
       </c>
       <c r="F224" s="17" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>Under 49.5</t>
         </is>
       </c>
       <c r="G224" s="26" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="H224" s="18" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="I224" s="20" t="n">
-        <v>0.445209524275868</v>
+        <v>0.4657709273155551</v>
       </c>
       <c r="J224" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.5108342361863488</v>
       </c>
       <c r="K224" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="L224" s="19" t="n">
-        <v>-0.07010210931374714</v>
+        <v>-0.06934347438782833</v>
       </c>
       <c r="M224" s="19" t="n">
-        <v>-0.1307814049852101</v>
+        <v>-0.1292108750187448</v>
       </c>
       <c r="N224" s="20" t="n">
         <v>0</v>
       </c>
       <c r="O224" s="27" t="n">
-        <v>0.725</v>
+        <v>0.839</v>
       </c>
       <c r="P224" s="17" t="inlineStr">
         <is>
@@ -15617,12 +15609,12 @@
       </c>
       <c r="B225" s="12" t="inlineStr">
         <is>
-          <t>ECU @ ODU</t>
+          <t>COLO @ NU</t>
         </is>
       </c>
       <c r="C225" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D225" s="22" t="n">
@@ -15630,40 +15622,40 @@
       </c>
       <c r="E225" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F225" s="12" t="inlineStr">
         <is>
-          <t>ECU +3</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="G225" s="23" t="n">
-        <v>-3</v>
+        <v>48.5</v>
       </c>
       <c r="H225" s="13" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="I225" s="15" t="n">
-        <v>0.4587228120660992</v>
+        <v>0.445209524275868</v>
       </c>
       <c r="J225" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K225" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L225" s="14" t="n">
-        <v>-0.07036112565367562</v>
+        <v>-0.07010210931374714</v>
       </c>
       <c r="M225" s="14" t="n">
-        <v>-0.1238273943235371</v>
+        <v>-0.1307814049852101</v>
       </c>
       <c r="N225" s="15" t="n">
-        <v>0.0598</v>
+        <v>0</v>
       </c>
       <c r="O225" s="24" t="n">
-        <v>0.839</v>
+        <v>0.725</v>
       </c>
       <c r="P225" s="12" t="inlineStr">
         <is>
@@ -15680,12 +15672,12 @@
       </c>
       <c r="B226" s="17" t="inlineStr">
         <is>
-          <t>SMU @ LOU</t>
+          <t>ECU @ ODU</t>
         </is>
       </c>
       <c r="C226" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D226" s="25" t="n">
@@ -15698,17 +15690,17 @@
       </c>
       <c r="F226" s="17" t="inlineStr">
         <is>
-          <t>SMU +1.5</t>
+          <t>ECU +3</t>
         </is>
       </c>
       <c r="G226" s="26" t="n">
-        <v>-1.5</v>
+        <v>-3</v>
       </c>
       <c r="H226" s="18" t="n">
         <v>-112</v>
       </c>
       <c r="I226" s="20" t="n">
-        <v>0.458506286674047</v>
+        <v>0.4587228120660992</v>
       </c>
       <c r="J226" s="20" t="n">
         <v>0.5043297540699688</v>
@@ -15717,13 +15709,13 @@
         <v>0.5283018867924528</v>
       </c>
       <c r="L226" s="19" t="n">
-        <v>-0.07055429896792037</v>
+        <v>-0.07036112565367562</v>
       </c>
       <c r="M226" s="19" t="n">
-        <v>-0.1321131002241253</v>
+        <v>-0.1238273943235371</v>
       </c>
       <c r="N226" s="20" t="n">
-        <v>0</v>
+        <v>0.0598</v>
       </c>
       <c r="O226" s="27" t="n">
         <v>0.839</v>
@@ -15743,12 +15735,12 @@
       </c>
       <c r="B227" s="12" t="inlineStr">
         <is>
-          <t>WYO @ CMU</t>
+          <t>SMU @ LOU</t>
         </is>
       </c>
       <c r="C227" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 17:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D227" s="22" t="n">
@@ -15761,29 +15753,29 @@
       </c>
       <c r="F227" s="12" t="inlineStr">
         <is>
-          <t>WYO +1.5</t>
+          <t>SMU +1.5</t>
         </is>
       </c>
       <c r="G227" s="23" t="n">
         <v>-1.5</v>
       </c>
       <c r="H227" s="13" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="I227" s="15" t="n">
-        <v>0.4505236120046303</v>
+        <v>0.458506286674047</v>
       </c>
       <c r="J227" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K227" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L227" s="14" t="n">
-        <v>-0.07065361651501766</v>
+        <v>-0.07055429896792037</v>
       </c>
       <c r="M227" s="14" t="n">
-        <v>-0.1323248953984897</v>
+        <v>-0.1321131002241253</v>
       </c>
       <c r="N227" s="15" t="n">
         <v>0</v>
@@ -15806,12 +15798,12 @@
       </c>
       <c r="B228" s="17" t="inlineStr">
         <is>
-          <t>CLT @ APP</t>
+          <t>WYO @ CMU</t>
         </is>
       </c>
       <c r="C228" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 17:00</t>
         </is>
       </c>
       <c r="D228" s="25" t="n">
@@ -15819,32 +15811,34 @@
       </c>
       <c r="E228" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F228" s="17" t="inlineStr">
         <is>
-          <t>APP ML</t>
-        </is>
-      </c>
-      <c r="G228" s="26" t="n"/>
+          <t>WYO +1.5</t>
+        </is>
+      </c>
+      <c r="G228" s="26" t="n">
+        <v>-1.5</v>
+      </c>
       <c r="H228" s="18" t="n">
-        <v>-1050</v>
+        <v>-108</v>
       </c>
       <c r="I228" s="20" t="n">
-        <v>0.7946862521841903</v>
+        <v>0.4505236120046303</v>
       </c>
       <c r="J228" s="20" t="n">
-        <v>0.8761776581426649</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K228" s="20" t="n">
-        <v>0.9130434782608695</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L228" s="19" t="n">
-        <v>-0.07150134368871548</v>
+        <v>-0.07065361651501766</v>
       </c>
       <c r="M228" s="19" t="n">
-        <v>-0.1296293428458867</v>
+        <v>-0.1323248953984897</v>
       </c>
       <c r="N228" s="20" t="n">
         <v>0</v>
@@ -15857,11 +15851,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q228" s="17" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q228" s="17" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="12" t="inlineStr">
@@ -15871,12 +15861,12 @@
       </c>
       <c r="B229" s="12" t="inlineStr">
         <is>
-          <t>UAB @ UL</t>
+          <t>CLT @ APP</t>
         </is>
       </c>
       <c r="C229" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D229" s="22" t="n">
@@ -15884,34 +15874,32 @@
       </c>
       <c r="E229" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F229" s="12" t="inlineStr">
         <is>
-          <t>UL -7.5</t>
-        </is>
-      </c>
-      <c r="G229" s="23" t="n">
-        <v>-7.5</v>
-      </c>
+          <t>APP ML</t>
+        </is>
+      </c>
+      <c r="G229" s="23" t="n"/>
       <c r="H229" s="13" t="n">
-        <v>-110</v>
+        <v>-1050</v>
       </c>
       <c r="I229" s="15" t="n">
-        <v>0.4527904060105175</v>
+        <v>0.7946862521841903</v>
       </c>
       <c r="J229" s="15" t="n">
-        <v>0.5</v>
+        <v>0.8761776581426649</v>
       </c>
       <c r="K229" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.9130434782608695</v>
       </c>
       <c r="L229" s="14" t="n">
-        <v>-0.07210638064482937</v>
+        <v>-0.07150134368871548</v>
       </c>
       <c r="M229" s="14" t="n">
-        <v>-0.1355819521617394</v>
+        <v>-0.1296293428458867</v>
       </c>
       <c r="N229" s="15" t="n">
         <v>0</v>
@@ -15924,7 +15912,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q229" s="12" t="n"/>
+      <c r="Q229" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="17" t="inlineStr">
@@ -15934,12 +15926,12 @@
       </c>
       <c r="B230" s="17" t="inlineStr">
         <is>
-          <t>WVU @ UVA</t>
+          <t>UAB @ UL</t>
         </is>
       </c>
       <c r="C230" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D230" s="25" t="n">
@@ -15947,34 +15939,34 @@
       </c>
       <c r="E230" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F230" s="17" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>UL -7.5</t>
         </is>
       </c>
       <c r="G230" s="26" t="n">
-        <v>52.5</v>
+        <v>-7.5</v>
       </c>
       <c r="H230" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I230" s="20" t="n">
-        <v>0.4566692266748813</v>
+        <v>0.4527904060105175</v>
       </c>
       <c r="J230" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K230" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L230" s="19" t="n">
-        <v>-0.07214176083278304</v>
+        <v>-0.07210638064482937</v>
       </c>
       <c r="M230" s="19" t="n">
-        <v>-0.1355903923654033</v>
+        <v>-0.1355819521617394</v>
       </c>
       <c r="N230" s="20" t="n">
         <v>0</v>
@@ -15997,12 +15989,12 @@
       </c>
       <c r="B231" s="12" t="inlineStr">
         <is>
-          <t>ASU @ KU</t>
+          <t>MIA @ WAKE</t>
         </is>
       </c>
       <c r="C231" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-18 23:30</t>
         </is>
       </c>
       <c r="D231" s="22" t="n">
@@ -16010,32 +16002,34 @@
       </c>
       <c r="E231" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F231" s="12" t="inlineStr">
         <is>
-          <t>ASU ML</t>
-        </is>
-      </c>
-      <c r="G231" s="23" t="n"/>
+          <t>Over 55.5</t>
+        </is>
+      </c>
+      <c r="G231" s="23" t="n">
+        <v>55.5</v>
+      </c>
       <c r="H231" s="13" t="n">
-        <v>-225</v>
+        <v>-105</v>
       </c>
       <c r="I231" s="15" t="n">
-        <v>0.5963562053711293</v>
+        <v>0.4413512990820579</v>
       </c>
       <c r="J231" s="15" t="n">
-        <v>0.6636481241914618</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K231" s="15" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L231" s="14" t="n">
-        <v>-0.07490329167741676</v>
+        <v>-0.07347993042761794</v>
       </c>
       <c r="M231" s="14" t="n">
-        <v>-0.1385965922417021</v>
+        <v>-0.1383141303636012</v>
       </c>
       <c r="N231" s="15" t="n">
         <v>0</v>
@@ -16058,12 +16052,12 @@
       </c>
       <c r="B232" s="17" t="inlineStr">
         <is>
-          <t>MIA @ WAKE</t>
+          <t>ASU @ KU</t>
         </is>
       </c>
       <c r="C232" s="17" t="inlineStr">
         <is>
-          <t>2026-09-18 23:30</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D232" s="25" t="n">
@@ -16071,34 +16065,32 @@
       </c>
       <c r="E232" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F232" s="17" t="inlineStr">
         <is>
-          <t>Over 55.5</t>
-        </is>
-      </c>
-      <c r="G232" s="26" t="n">
-        <v>55.5</v>
-      </c>
+          <t>ASU ML</t>
+        </is>
+      </c>
+      <c r="G232" s="26" t="n"/>
       <c r="H232" s="18" t="n">
-        <v>-108</v>
+        <v>-225</v>
       </c>
       <c r="I232" s="20" t="n">
-        <v>0.4446035401402479</v>
+        <v>0.5963562053711293</v>
       </c>
       <c r="J232" s="20" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.6636481241914618</v>
       </c>
       <c r="K232" s="20" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="L232" s="19" t="n">
-        <v>-0.07551116788271293</v>
+        <v>-0.07490329167741676</v>
       </c>
       <c r="M232" s="19" t="n">
-        <v>-0.1437265152854483</v>
+        <v>-0.1385965922417021</v>
       </c>
       <c r="N232" s="20" t="n">
         <v>0</v>
@@ -16247,12 +16239,12 @@
       </c>
       <c r="B235" s="12" t="inlineStr">
         <is>
-          <t>FIU @ FAU</t>
+          <t>WYO @ CMU</t>
         </is>
       </c>
       <c r="C235" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 17:00</t>
         </is>
       </c>
       <c r="D235" s="22" t="n">
@@ -16260,37 +16252,35 @@
       </c>
       <c r="E235" s="12" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F235" s="12" t="inlineStr">
         <is>
-          <t>FAU -7</t>
-        </is>
-      </c>
-      <c r="G235" s="23" t="n">
-        <v>-7</v>
-      </c>
+          <t>WYO ML</t>
+        </is>
+      </c>
+      <c r="G235" s="23" t="n"/>
       <c r="H235" s="13" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="I235" s="15" t="n">
-        <v>0.4281409397439165</v>
+        <v>0.4240150238839833</v>
       </c>
       <c r="J235" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="K235" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5</v>
       </c>
       <c r="L235" s="14" t="n">
-        <v>-0.07886185356718828</v>
+        <v>-0.07902033828117308</v>
       </c>
       <c r="M235" s="14" t="n">
-        <v>-0.1445986566788771</v>
+        <v>-0.1519699522320335</v>
       </c>
       <c r="N235" s="15" t="n">
-        <v>0.0494</v>
+        <v>0</v>
       </c>
       <c r="O235" s="24" t="n">
         <v>0.839</v>
@@ -16310,12 +16300,12 @@
       </c>
       <c r="B236" s="17" t="inlineStr">
         <is>
-          <t>WYO @ CMU</t>
+          <t>SMU @ LOU</t>
         </is>
       </c>
       <c r="C236" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 17:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="D236" s="25" t="n">
@@ -16328,27 +16318,27 @@
       </c>
       <c r="F236" s="17" t="inlineStr">
         <is>
-          <t>WYO ML</t>
+          <t>SMU ML</t>
         </is>
       </c>
       <c r="G236" s="26" t="n"/>
       <c r="H236" s="18" t="n">
-        <v>100</v>
+        <v>-105</v>
       </c>
       <c r="I236" s="20" t="n">
-        <v>0.4240150238839833</v>
+        <v>0.4330326427741102</v>
       </c>
       <c r="J236" s="20" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K236" s="20" t="n">
-        <v>0.5</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L236" s="19" t="n">
-        <v>-0.07902033828117308</v>
+        <v>-0.07942528273414519</v>
       </c>
       <c r="M236" s="19" t="n">
-        <v>-0.1519699522320335</v>
+        <v>-0.154555316488642</v>
       </c>
       <c r="N236" s="20" t="n">
         <v>0</v>
@@ -16371,12 +16361,12 @@
       </c>
       <c r="B237" s="12" t="inlineStr">
         <is>
-          <t>UK @ TA&amp;M</t>
+          <t>BALL @ LIB</t>
         </is>
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D237" s="22" t="n">
@@ -16384,34 +16374,32 @@
       </c>
       <c r="E237" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F237" s="12" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
-        </is>
-      </c>
-      <c r="G237" s="23" t="n">
-        <v>49.5</v>
-      </c>
+          <t>LIB ML</t>
+        </is>
+      </c>
+      <c r="G237" s="23" t="n"/>
       <c r="H237" s="13" t="n">
-        <v>-110</v>
+        <v>-650</v>
       </c>
       <c r="I237" s="15" t="n">
-        <v>0.4429309109103309</v>
+        <v>0.7361130634217865</v>
       </c>
       <c r="J237" s="15" t="n">
-        <v>0.5</v>
+        <v>0.8316498316498315</v>
       </c>
       <c r="K237" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L237" s="14" t="n">
-        <v>-0.07923928370038286</v>
+        <v>-0.0794623979688158</v>
       </c>
       <c r="M237" s="14" t="n">
-        <v>-0.1544046246257319</v>
+        <v>-0.1506387729748618</v>
       </c>
       <c r="N237" s="15" t="n">
         <v>0</v>
@@ -16424,7 +16412,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q237" s="12" t="n"/>
+      <c r="Q237" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="17" t="inlineStr">
@@ -16434,12 +16426,12 @@
       </c>
       <c r="B238" s="17" t="inlineStr">
         <is>
-          <t>SMU @ LOU</t>
+          <t>ECU @ ODU</t>
         </is>
       </c>
       <c r="C238" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D238" s="25" t="n">
@@ -16452,27 +16444,27 @@
       </c>
       <c r="F238" s="17" t="inlineStr">
         <is>
-          <t>SMU ML</t>
+          <t>ECU ML</t>
         </is>
       </c>
       <c r="G238" s="26" t="n"/>
       <c r="H238" s="18" t="n">
-        <v>-105</v>
+        <v>124</v>
       </c>
       <c r="I238" s="20" t="n">
-        <v>0.4330326427741102</v>
+        <v>0.3779393751763391</v>
       </c>
       <c r="J238" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.4279403644395361</v>
       </c>
       <c r="K238" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.4464285714285715</v>
       </c>
       <c r="L238" s="19" t="n">
-        <v>-0.07942528273414519</v>
+        <v>-0.08004243138577664</v>
       </c>
       <c r="M238" s="19" t="n">
-        <v>-0.154555316488642</v>
+        <v>-0.1534157996050003</v>
       </c>
       <c r="N238" s="20" t="n">
         <v>0</v>
@@ -16495,12 +16487,12 @@
       </c>
       <c r="B239" s="12" t="inlineStr">
         <is>
-          <t>BALL @ LIB</t>
+          <t>FIU @ FAU</t>
         </is>
       </c>
       <c r="C239" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-19 22:00</t>
         </is>
       </c>
       <c r="D239" s="22" t="n">
@@ -16508,35 +16500,37 @@
       </c>
       <c r="E239" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F239" s="12" t="inlineStr">
         <is>
-          <t>LIB ML</t>
-        </is>
-      </c>
-      <c r="G239" s="23" t="n"/>
+          <t>FAU -7</t>
+        </is>
+      </c>
+      <c r="G239" s="23" t="n">
+        <v>-7</v>
+      </c>
       <c r="H239" s="13" t="n">
-        <v>-650</v>
+        <v>-105</v>
       </c>
       <c r="I239" s="15" t="n">
-        <v>0.7361130634217865</v>
+        <v>0.4314058845088772</v>
       </c>
       <c r="J239" s="15" t="n">
-        <v>0.8316498316498315</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K239" s="15" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L239" s="14" t="n">
-        <v>-0.0794623979688158</v>
+        <v>-0.08039746792467641</v>
       </c>
       <c r="M239" s="14" t="n">
-        <v>-0.1506387729748618</v>
+        <v>-0.1499394387438246</v>
       </c>
       <c r="N239" s="15" t="n">
-        <v>0</v>
+        <v>0.0494</v>
       </c>
       <c r="O239" s="24" t="n">
         <v>0.839</v>
@@ -16546,11 +16540,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q239" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q239" s="12" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="17" t="inlineStr">
@@ -16560,12 +16550,12 @@
       </c>
       <c r="B240" s="17" t="inlineStr">
         <is>
-          <t>ECU @ ODU</t>
+          <t>BGSU @ ISU</t>
         </is>
       </c>
       <c r="C240" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D240" s="25" t="n">
@@ -16578,27 +16568,27 @@
       </c>
       <c r="F240" s="17" t="inlineStr">
         <is>
-          <t>ECU ML</t>
+          <t>ISU ML</t>
         </is>
       </c>
       <c r="G240" s="26" t="n"/>
       <c r="H240" s="18" t="n">
-        <v>124</v>
+        <v>-3600</v>
       </c>
       <c r="I240" s="20" t="n">
-        <v>0.3779393751763391</v>
+        <v>0.8254237633576067</v>
       </c>
       <c r="J240" s="20" t="n">
-        <v>0.4279403644395361</v>
+        <v>0.9396411092985318</v>
       </c>
       <c r="K240" s="20" t="n">
-        <v>0.4464285714285715</v>
+        <v>0.972972972972973</v>
       </c>
       <c r="L240" s="19" t="n">
-        <v>-0.08004243138577664</v>
+        <v>-0.08135386568885872</v>
       </c>
       <c r="M240" s="19" t="n">
-        <v>-0.1534157996050003</v>
+        <v>-0.1516477987713487</v>
       </c>
       <c r="N240" s="20" t="n">
         <v>0</v>
@@ -16611,7 +16601,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q240" s="17" t="n"/>
+      <c r="Q240" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="12" t="inlineStr">
@@ -16644,22 +16638,22 @@
       </c>
       <c r="G241" s="23" t="n"/>
       <c r="H241" s="13" t="n">
-        <v>-1450</v>
+        <v>-1600</v>
       </c>
       <c r="I241" s="15" t="n">
-        <v>0.7897668561477887</v>
+        <v>0.7923152197573406</v>
       </c>
       <c r="J241" s="15" t="n">
-        <v>0.8988580750407831</v>
+        <v>0.9039548022598869</v>
       </c>
       <c r="K241" s="15" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="L241" s="14" t="n">
-        <v>-0.08130371180141044</v>
+        <v>-0.08186403174177347</v>
       </c>
       <c r="M241" s="14" t="n">
-        <v>-0.1557664641178811</v>
+        <v>-0.1581650790078255</v>
       </c>
       <c r="N241" s="15" t="n">
         <v>0</v>
@@ -16686,12 +16680,12 @@
       </c>
       <c r="B242" s="17" t="inlineStr">
         <is>
-          <t>BGSU @ ISU</t>
+          <t>TROY @ MIZ</t>
         </is>
       </c>
       <c r="C242" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D242" s="25" t="n">
@@ -16704,27 +16698,27 @@
       </c>
       <c r="F242" s="17" t="inlineStr">
         <is>
-          <t>ISU ML</t>
+          <t>MIZ ML</t>
         </is>
       </c>
       <c r="G242" s="26" t="n"/>
       <c r="H242" s="18" t="n">
-        <v>-3600</v>
+        <v>-6500</v>
       </c>
       <c r="I242" s="20" t="n">
-        <v>0.8254237633576067</v>
+        <v>0.8317947492251805</v>
       </c>
       <c r="J242" s="20" t="n">
-        <v>0.9396411092985318</v>
+        <v>0.9538784067085954</v>
       </c>
       <c r="K242" s="20" t="n">
-        <v>0.972972972972973</v>
+        <v>0.9848484848484849</v>
       </c>
       <c r="L242" s="19" t="n">
-        <v>-0.08135386568885872</v>
+        <v>-0.08297274179583243</v>
       </c>
       <c r="M242" s="19" t="n">
-        <v>-0.1516477987713487</v>
+        <v>-0.1554084084790476</v>
       </c>
       <c r="N242" s="20" t="n">
         <v>0</v>
@@ -16751,12 +16745,12 @@
       </c>
       <c r="B243" s="12" t="inlineStr">
         <is>
-          <t>TROY @ MIZ</t>
+          <t>UAB @ UL</t>
         </is>
       </c>
       <c r="C243" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D243" s="22" t="n">
@@ -16764,32 +16758,34 @@
       </c>
       <c r="E243" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F243" s="12" t="inlineStr">
         <is>
-          <t>MIZ ML</t>
-        </is>
-      </c>
-      <c r="G243" s="23" t="n"/>
+          <t>Over 56.5</t>
+        </is>
+      </c>
+      <c r="G243" s="23" t="n">
+        <v>56.5</v>
+      </c>
       <c r="H243" s="13" t="n">
-        <v>-6500</v>
+        <v>-112</v>
       </c>
       <c r="I243" s="15" t="n">
-        <v>0.8317947492251805</v>
+        <v>0.4393816764752666</v>
       </c>
       <c r="J243" s="15" t="n">
-        <v>0.9538784067085954</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K243" s="15" t="n">
-        <v>0.9848484848484849</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L243" s="14" t="n">
-        <v>-0.08297274179583243</v>
+        <v>-0.0831597783271758</v>
       </c>
       <c r="M243" s="14" t="n">
-        <v>-0.1554084084790476</v>
+        <v>-0.1683132552432454</v>
       </c>
       <c r="N243" s="15" t="n">
         <v>0</v>
@@ -16802,11 +16798,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q243" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q243" s="12" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="17" t="inlineStr">
@@ -16816,7 +16808,7 @@
       </c>
       <c r="B244" s="17" t="inlineStr">
         <is>
-          <t>UAB @ UL</t>
+          <t>ARST @ TCU</t>
         </is>
       </c>
       <c r="C244" s="17" t="inlineStr">
@@ -16834,29 +16826,29 @@
       </c>
       <c r="F244" s="17" t="inlineStr">
         <is>
-          <t>Over 56.5</t>
+          <t>Over 55.5</t>
         </is>
       </c>
       <c r="G244" s="26" t="n">
-        <v>56.5</v>
+        <v>55.5</v>
       </c>
       <c r="H244" s="18" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I244" s="20" t="n">
-        <v>0.4393816764752666</v>
+        <v>0.4353240072943866</v>
       </c>
       <c r="J244" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K244" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L244" s="19" t="n">
-        <v>-0.0831597783271758</v>
+        <v>-0.08329254278965623</v>
       </c>
       <c r="M244" s="19" t="n">
-        <v>-0.1683132552432454</v>
+        <v>-0.1689268951652619</v>
       </c>
       <c r="N244" s="20" t="n">
         <v>0</v>
@@ -16879,12 +16871,12 @@
       </c>
       <c r="B245" s="12" t="inlineStr">
         <is>
-          <t>ARST @ TCU</t>
+          <t>TULN @ KSU</t>
         </is>
       </c>
       <c r="C245" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D245" s="22" t="n">
@@ -16892,34 +16884,32 @@
       </c>
       <c r="E245" s="12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F245" s="12" t="inlineStr">
         <is>
-          <t>Over 55.5</t>
-        </is>
-      </c>
-      <c r="G245" s="23" t="n">
-        <v>55.5</v>
-      </c>
+          <t>KSU ML</t>
+        </is>
+      </c>
+      <c r="G245" s="23" t="n"/>
       <c r="H245" s="13" t="n">
-        <v>-110</v>
+        <v>-1800</v>
       </c>
       <c r="I245" s="15" t="n">
-        <v>0.4353240072943866</v>
+        <v>0.7942152473020465</v>
       </c>
       <c r="J245" s="15" t="n">
-        <v>0.5</v>
+        <v>0.912442396313364</v>
       </c>
       <c r="K245" s="15" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="L245" s="14" t="n">
-        <v>-0.08329254278965623</v>
+        <v>-0.08334336689120363</v>
       </c>
       <c r="M245" s="14" t="n">
-        <v>-0.1689268951652619</v>
+        <v>-0.1616616834033954</v>
       </c>
       <c r="N245" s="15" t="n">
         <v>0</v>
@@ -16932,7 +16922,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q245" s="12" t="n"/>
+      <c r="Q245" s="12" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="17" t="inlineStr">
@@ -16942,12 +16936,12 @@
       </c>
       <c r="B246" s="17" t="inlineStr">
         <is>
-          <t>TULN @ KSU</t>
+          <t>WVU @ UVA</t>
         </is>
       </c>
       <c r="C246" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D246" s="25" t="n">
@@ -16955,32 +16949,34 @@
       </c>
       <c r="E246" s="17" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F246" s="17" t="inlineStr">
         <is>
-          <t>KSU ML</t>
-        </is>
-      </c>
-      <c r="G246" s="26" t="n"/>
+          <t>Over 53.5</t>
+        </is>
+      </c>
+      <c r="G246" s="26" t="n">
+        <v>53.5</v>
+      </c>
       <c r="H246" s="18" t="n">
-        <v>-1800</v>
+        <v>-112</v>
       </c>
       <c r="I246" s="20" t="n">
-        <v>0.7942152473020465</v>
+        <v>0.4374889082941585</v>
       </c>
       <c r="J246" s="20" t="n">
-        <v>0.912442396313364</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K246" s="20" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L246" s="19" t="n">
-        <v>-0.08334336689120363</v>
+        <v>-0.08400724365321681</v>
       </c>
       <c r="M246" s="19" t="n">
-        <v>-0.1616616834033954</v>
+        <v>-0.1718959950146285</v>
       </c>
       <c r="N246" s="20" t="n">
         <v>0</v>
@@ -16993,11 +16989,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q246" s="17" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q246" s="17" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="12" t="inlineStr">
@@ -17007,12 +16999,12 @@
       </c>
       <c r="B247" s="12" t="inlineStr">
         <is>
-          <t>EMU @ WIS</t>
+          <t>UNM @ OU</t>
         </is>
       </c>
       <c r="C247" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 16:30</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D247" s="22" t="n">
@@ -17025,29 +17017,29 @@
       </c>
       <c r="F247" s="12" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="G247" s="23" t="n">
-        <v>45.5</v>
+        <v>46.5</v>
       </c>
       <c r="H247" s="13" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I247" s="15" t="n">
-        <v>0.431272438741787</v>
+        <v>0.4242665320851896</v>
       </c>
       <c r="J247" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.4891657638136511</v>
       </c>
       <c r="K247" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L247" s="14" t="n">
-        <v>-0.08342338155527183</v>
+        <v>-0.08403757223048447</v>
       </c>
       <c r="M247" s="14" t="n">
-        <v>-0.1694012290898916</v>
+        <v>-0.1716701040241536</v>
       </c>
       <c r="N247" s="15" t="n">
         <v>0</v>
@@ -17070,12 +17062,12 @@
       </c>
       <c r="B248" s="17" t="inlineStr">
         <is>
-          <t>UNM @ OU</t>
+          <t>KENN @ TENN</t>
         </is>
       </c>
       <c r="C248" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 23:45</t>
         </is>
       </c>
       <c r="D248" s="25" t="n">
@@ -17083,34 +17075,32 @@
       </c>
       <c r="E248" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F248" s="17" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
-        </is>
-      </c>
-      <c r="G248" s="26" t="n">
-        <v>46.5</v>
-      </c>
+          <t>TENN ML</t>
+        </is>
+      </c>
+      <c r="G248" s="26" t="n"/>
       <c r="H248" s="18" t="n">
-        <v>-105</v>
+        <v>-100000</v>
       </c>
       <c r="I248" s="20" t="n">
-        <v>0.4242665320851896</v>
+        <v>0.8499367258373444</v>
       </c>
       <c r="J248" s="20" t="n">
-        <v>0.4891657638136511</v>
+        <v>0.9807503701851887</v>
       </c>
       <c r="K248" s="20" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.999000999000999</v>
       </c>
       <c r="L248" s="19" t="n">
-        <v>-0.08403757223048447</v>
+        <v>-0.08419050806545607</v>
       </c>
       <c r="M248" s="19" t="n">
-        <v>-0.1716701040241536</v>
+        <v>-0.1492133374368184</v>
       </c>
       <c r="N248" s="20" t="n">
         <v>0</v>
@@ -17123,7 +17113,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q248" s="17" t="n"/>
+      <c r="Q248" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="12" t="inlineStr">
@@ -17133,12 +17127,12 @@
       </c>
       <c r="B249" s="12" t="inlineStr">
         <is>
-          <t>KENN @ TENN</t>
+          <t>EMU @ WIS</t>
         </is>
       </c>
       <c r="C249" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:45</t>
+          <t>2026-09-19 16:30</t>
         </is>
       </c>
       <c r="D249" s="22" t="n">
@@ -17146,32 +17140,34 @@
       </c>
       <c r="E249" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F249" s="12" t="inlineStr">
         <is>
-          <t>TENN ML</t>
-        </is>
-      </c>
-      <c r="G249" s="23" t="n"/>
+          <t>Under 45.5</t>
+        </is>
+      </c>
+      <c r="G249" s="23" t="n">
+        <v>45.5</v>
+      </c>
       <c r="H249" s="13" t="n">
-        <v>-100000</v>
+        <v>-112</v>
       </c>
       <c r="I249" s="15" t="n">
-        <v>0.8499367258373444</v>
+        <v>0.4356021928117558</v>
       </c>
       <c r="J249" s="15" t="n">
-        <v>0.9807503701851887</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K249" s="15" t="n">
-        <v>0.999000999000999</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L249" s="14" t="n">
-        <v>-0.08419050806545607</v>
+        <v>-0.08479508550645673</v>
       </c>
       <c r="M249" s="14" t="n">
-        <v>-0.1492133374368184</v>
+        <v>-0.1754672778920336</v>
       </c>
       <c r="N249" s="15" t="n">
         <v>0</v>
@@ -17184,11 +17180,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q249" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q249" s="12" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="17" t="inlineStr">
@@ -17261,12 +17253,12 @@
       </c>
       <c r="B251" s="12" t="inlineStr">
         <is>
-          <t>LT @ BAY</t>
+          <t>MSU @ ND</t>
         </is>
       </c>
       <c r="C251" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D251" s="22" t="n">
@@ -17279,27 +17271,27 @@
       </c>
       <c r="F251" s="12" t="inlineStr">
         <is>
-          <t>BAY ML</t>
+          <t>ND ML</t>
         </is>
       </c>
       <c r="G251" s="23" t="n"/>
       <c r="H251" s="13" t="n">
-        <v>-1200</v>
+        <v>-6500</v>
       </c>
       <c r="I251" s="15" t="n">
-        <v>0.7647141463477202</v>
+        <v>0.8214101582527794</v>
       </c>
       <c r="J251" s="15" t="n">
-        <v>0.8869565217391304</v>
+        <v>0.9538784067085954</v>
       </c>
       <c r="K251" s="15" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.9848484848484849</v>
       </c>
       <c r="L251" s="14" t="n">
-        <v>-0.08510510669348836</v>
+        <v>-0.08531060133862964</v>
       </c>
       <c r="M251" s="14" t="n">
-        <v>-0.1715596747899699</v>
+        <v>-0.1659527623894855</v>
       </c>
       <c r="N251" s="15" t="n">
         <v>0</v>
@@ -17326,12 +17318,12 @@
       </c>
       <c r="B252" s="17" t="inlineStr">
         <is>
-          <t>MSU @ ND</t>
+          <t>LT @ BAY</t>
         </is>
       </c>
       <c r="C252" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D252" s="25" t="n">
@@ -17344,27 +17336,27 @@
       </c>
       <c r="F252" s="17" t="inlineStr">
         <is>
-          <t>ND ML</t>
+          <t>BAY ML</t>
         </is>
       </c>
       <c r="G252" s="26" t="n"/>
       <c r="H252" s="18" t="n">
-        <v>-6500</v>
+        <v>-1350</v>
       </c>
       <c r="I252" s="20" t="n">
-        <v>0.8214101582527794</v>
+        <v>0.7679270619487433</v>
       </c>
       <c r="J252" s="20" t="n">
-        <v>0.9538784067085954</v>
+        <v>0.8933823529411765</v>
       </c>
       <c r="K252" s="20" t="n">
-        <v>0.9848484848484849</v>
+        <v>0.9310344827586207</v>
       </c>
       <c r="L252" s="19" t="n">
-        <v>-0.08531060133862964</v>
+        <v>-0.08560705354002204</v>
       </c>
       <c r="M252" s="19" t="n">
-        <v>-0.1659527623894855</v>
+        <v>-0.1751894519809796</v>
       </c>
       <c r="N252" s="20" t="n">
         <v>0</v>
@@ -17521,12 +17513,12 @@
       </c>
       <c r="B255" s="12" t="inlineStr">
         <is>
-          <t>ARST @ TCU</t>
+          <t>UNC @ CLEM</t>
         </is>
       </c>
       <c r="C255" s="12" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00</t>
+          <t>2026-09-19 16:00</t>
         </is>
       </c>
       <c r="D255" s="22" t="n">
@@ -17534,32 +17526,34 @@
       </c>
       <c r="E255" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F255" s="12" t="inlineStr">
         <is>
-          <t>TCU ML</t>
-        </is>
-      </c>
-      <c r="G255" s="23" t="n"/>
+          <t>Under 44.5</t>
+        </is>
+      </c>
+      <c r="G255" s="23" t="n">
+        <v>44.5</v>
+      </c>
       <c r="H255" s="13" t="n">
-        <v>-1350</v>
+        <v>-112</v>
       </c>
       <c r="I255" s="15" t="n">
-        <v>0.7616698450434658</v>
+        <v>0.4299815804168907</v>
       </c>
       <c r="J255" s="15" t="n">
-        <v>0.8933823529411765</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K255" s="15" t="n">
-        <v>0.9310344827586207</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L255" s="14" t="n">
-        <v>-0.0868394806998839</v>
+        <v>-0.08683758636894096</v>
       </c>
       <c r="M255" s="14" t="n">
-        <v>-0.1819101664347961</v>
+        <v>-0.1861062942108854</v>
       </c>
       <c r="N255" s="15" t="n">
         <v>0</v>
@@ -17572,11 +17566,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q255" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q255" s="12" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="17" t="inlineStr">
@@ -17586,12 +17576,12 @@
       </c>
       <c r="B256" s="17" t="inlineStr">
         <is>
-          <t>WVU @ UVA</t>
+          <t>ARST @ TCU</t>
         </is>
       </c>
       <c r="C256" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-20 00:00</t>
         </is>
       </c>
       <c r="D256" s="25" t="n">
@@ -17604,27 +17594,27 @@
       </c>
       <c r="F256" s="17" t="inlineStr">
         <is>
-          <t>UVA ML</t>
+          <t>TCU ML</t>
         </is>
       </c>
       <c r="G256" s="26" t="n"/>
       <c r="H256" s="18" t="n">
-        <v>-395</v>
+        <v>-1350</v>
       </c>
       <c r="I256" s="20" t="n">
-        <v>0.6519324025282154</v>
+        <v>0.7616698450434658</v>
       </c>
       <c r="J256" s="20" t="n">
-        <v>0.7659021045164341</v>
+        <v>0.8933823529411765</v>
       </c>
       <c r="K256" s="20" t="n">
-        <v>0.797979797979798</v>
+        <v>0.9310344827586207</v>
       </c>
       <c r="L256" s="19" t="n">
-        <v>-0.08706231180975971</v>
+        <v>-0.0868394806998839</v>
       </c>
       <c r="M256" s="19" t="n">
-        <v>-0.1830214196165402</v>
+        <v>-0.1819101664347961</v>
       </c>
       <c r="N256" s="20" t="n">
         <v>0</v>
@@ -17637,7 +17627,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q256" s="17" t="n"/>
+      <c r="Q256" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="12" t="inlineStr">
@@ -17647,12 +17641,12 @@
       </c>
       <c r="B257" s="12" t="inlineStr">
         <is>
-          <t>GAST @ UCF</t>
+          <t>WVU @ UVA</t>
         </is>
       </c>
       <c r="C257" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D257" s="22" t="n">
@@ -17665,27 +17659,27 @@
       </c>
       <c r="F257" s="12" t="inlineStr">
         <is>
-          <t>UCF ML</t>
+          <t>UVA ML</t>
         </is>
       </c>
       <c r="G257" s="23" t="n"/>
       <c r="H257" s="13" t="n">
-        <v>-1200</v>
+        <v>-395</v>
       </c>
       <c r="I257" s="15" t="n">
-        <v>0.7540652140144954</v>
+        <v>0.6519324025282154</v>
       </c>
       <c r="J257" s="15" t="n">
-        <v>0.8869565217391304</v>
+        <v>0.7659021045164341</v>
       </c>
       <c r="K257" s="15" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.797979797979798</v>
       </c>
       <c r="L257" s="14" t="n">
-        <v>-0.08722465784831755</v>
+        <v>-0.08706231180975971</v>
       </c>
       <c r="M257" s="14" t="n">
-        <v>-0.1830960181509633</v>
+        <v>-0.1830214196165402</v>
       </c>
       <c r="N257" s="15" t="n">
         <v>0</v>
@@ -17698,11 +17692,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q257" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q257" s="12" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="17" t="inlineStr">
@@ -17712,12 +17702,12 @@
       </c>
       <c r="B258" s="17" t="inlineStr">
         <is>
-          <t>STAN @ DUKE</t>
+          <t>GAST @ UCF</t>
         </is>
       </c>
       <c r="C258" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00</t>
+          <t>2026-09-19 23:00</t>
         </is>
       </c>
       <c r="D258" s="25" t="n">
@@ -17725,34 +17715,32 @@
       </c>
       <c r="E258" s="17" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F258" s="17" t="inlineStr">
         <is>
-          <t>DUKE -9.5</t>
-        </is>
-      </c>
-      <c r="G258" s="26" t="n">
-        <v>-9.5</v>
-      </c>
+          <t>UCF ML</t>
+        </is>
+      </c>
+      <c r="G258" s="26" t="n"/>
       <c r="H258" s="18" t="n">
-        <v>-112</v>
+        <v>-1200</v>
       </c>
       <c r="I258" s="20" t="n">
-        <v>0.4284774069304556</v>
+        <v>0.7540652140144954</v>
       </c>
       <c r="J258" s="20" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.8869565217391304</v>
       </c>
       <c r="K258" s="20" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="L258" s="19" t="n">
-        <v>-0.08731425001538265</v>
+        <v>-0.08722465784831755</v>
       </c>
       <c r="M258" s="19" t="n">
-        <v>-0.1889534797387806</v>
+        <v>-0.1830960181509633</v>
       </c>
       <c r="N258" s="20" t="n">
         <v>0</v>
@@ -17765,7 +17753,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q258" s="17" t="n"/>
+      <c r="Q258" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="12" t="inlineStr">
@@ -17775,12 +17767,12 @@
       </c>
       <c r="B259" s="12" t="inlineStr">
         <is>
-          <t>UNM @ OU</t>
+          <t>STAN @ DUKE</t>
         </is>
       </c>
       <c r="C259" s="12" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30</t>
+          <t>2026-09-19 20:00</t>
         </is>
       </c>
       <c r="D259" s="22" t="n">
@@ -17788,32 +17780,34 @@
       </c>
       <c r="E259" s="12" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="F259" s="12" t="inlineStr">
         <is>
-          <t>OU ML</t>
-        </is>
-      </c>
-      <c r="G259" s="23" t="n"/>
+          <t>DUKE -9.5</t>
+        </is>
+      </c>
+      <c r="G259" s="23" t="n">
+        <v>-9.5</v>
+      </c>
       <c r="H259" s="13" t="n">
-        <v>-2100</v>
+        <v>-112</v>
       </c>
       <c r="I259" s="15" t="n">
-        <v>0.7800066377068618</v>
+        <v>0.4284774069304556</v>
       </c>
       <c r="J259" s="15" t="n">
-        <v>0.9197080291970804</v>
+        <v>0.5043297540699688</v>
       </c>
       <c r="K259" s="15" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="L259" s="14" t="n">
-        <v>-0.08754307503525306</v>
+        <v>-0.08731425001538265</v>
       </c>
       <c r="M259" s="14" t="n">
-        <v>-0.1828501890690019</v>
+        <v>-0.1889534797387806</v>
       </c>
       <c r="N259" s="15" t="n">
         <v>0</v>
@@ -17826,11 +17820,7 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q259" s="12" t="inlineStr">
-        <is>
-          <t>price outside allowed range</t>
-        </is>
-      </c>
+      <c r="Q259" s="12" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="17" t="inlineStr">
@@ -17840,12 +17830,12 @@
       </c>
       <c r="B260" s="17" t="inlineStr">
         <is>
-          <t>UNC @ CLEM</t>
+          <t>UNM @ OU</t>
         </is>
       </c>
       <c r="C260" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00</t>
+          <t>2026-09-19 23:30</t>
         </is>
       </c>
       <c r="D260" s="25" t="n">
@@ -17853,34 +17843,32 @@
       </c>
       <c r="E260" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F260" s="17" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
-        </is>
-      </c>
-      <c r="G260" s="26" t="n">
-        <v>44.5</v>
-      </c>
+          <t>OU ML</t>
+        </is>
+      </c>
+      <c r="G260" s="26" t="n"/>
       <c r="H260" s="18" t="n">
-        <v>-118</v>
+        <v>-2100</v>
       </c>
       <c r="I260" s="20" t="n">
-        <v>0.4364987662400414</v>
+        <v>0.7800066377068618</v>
       </c>
       <c r="J260" s="20" t="n">
-        <v>0.5173641257162701</v>
+        <v>0.9197080291970804</v>
       </c>
       <c r="K260" s="20" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="L260" s="19" t="n">
-        <v>-0.08817981134676509</v>
+        <v>-0.08754307503525306</v>
       </c>
       <c r="M260" s="19" t="n">
-        <v>-0.1935870250819575</v>
+        <v>-0.1828501890690019</v>
       </c>
       <c r="N260" s="20" t="n">
         <v>0</v>
@@ -17893,7 +17881,11 @@
           <t>Draft Kings</t>
         </is>
       </c>
-      <c r="Q260" s="17" t="n"/>
+      <c r="Q260" s="17" t="inlineStr">
+        <is>
+          <t>price outside allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="12" t="inlineStr">
@@ -19818,22 +19810,22 @@
       </c>
       <c r="G291" s="23" t="n"/>
       <c r="H291" s="13" t="n">
-        <v>-4500</v>
+        <v>-3600</v>
       </c>
       <c r="I291" s="15" t="n">
-        <v>0.6801039801348587</v>
+        <v>0.6767936936626293</v>
       </c>
       <c r="J291" s="15" t="n">
-        <v>0.9462616822429908</v>
+        <v>0.9396411092985318</v>
       </c>
       <c r="K291" s="15" t="n">
-        <v>0.9782608695652174</v>
+        <v>0.972972972972973</v>
       </c>
       <c r="L291" s="14" t="n">
-        <v>-0.09449195573926773</v>
+        <v>-0.09447524839467397</v>
       </c>
       <c r="M291" s="14" t="n">
-        <v>-0.3047825980843667</v>
+        <v>-0.3044064815134089</v>
       </c>
       <c r="N291" s="15" t="n">
         <v>0</v>
@@ -20856,22 +20848,22 @@
         <v>-19.5</v>
       </c>
       <c r="H307" s="13" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="I307" s="15" t="n">
-        <v>0.3206557336886854</v>
+        <v>0.318490856653701</v>
       </c>
       <c r="J307" s="15" t="n">
-        <v>0.5043297540699688</v>
+        <v>0.5</v>
       </c>
       <c r="K307" s="15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="L307" s="14" t="n">
-        <v>-0.09491113990263532</v>
+        <v>-0.09490891350155506</v>
       </c>
       <c r="M307" s="14" t="n">
-        <v>-0.393044504089274</v>
+        <v>-0.3919720009338434</v>
       </c>
       <c r="N307" s="15" t="n">
         <v>0</v>
@@ -20990,22 +20982,22 @@
         <v>-19.5</v>
       </c>
       <c r="H309" s="13" t="n">
-        <v>-102</v>
+        <v>-108</v>
       </c>
       <c r="I309" s="15" t="n">
-        <v>0.298607597438345</v>
+        <v>0.3051247832614956</v>
       </c>
       <c r="J309" s="15" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.4956702459300312</v>
       </c>
       <c r="K309" s="15" t="n">
-        <v>0.504950495049505</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="L309" s="14" t="n">
-        <v>-0.09493800097383333</v>
+        <v>-0.09494194301249712</v>
       </c>
       <c r="M309" s="14" t="n">
-        <v>-0.4086398560534736</v>
+        <v>-0.4123522692741566</v>
       </c>
       <c r="N309" s="15" t="n">
         <v>0</v>
@@ -21124,22 +21116,22 @@
         <v>-20.5</v>
       </c>
       <c r="H311" s="13" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I311" s="15" t="n">
-        <v>0.2957106649598328</v>
+        <v>0.2978755419948172</v>
       </c>
       <c r="J311" s="15" t="n">
-        <v>0.4956702459300312</v>
+        <v>0.5</v>
       </c>
       <c r="K311" s="15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="L311" s="14" t="n">
-        <v>-0.094961073339285</v>
+        <v>-0.09496175264016267</v>
       </c>
       <c r="M311" s="14" t="n">
-        <v>-0.4304831637810628</v>
+        <v>-0.4184334656291664</v>
       </c>
       <c r="N311" s="15" t="n">
         <v>0</v>
@@ -21462,19 +21454,19 @@
         <v>-102</v>
       </c>
       <c r="I316" s="20" t="n">
-        <v>0.2630944811315276</v>
+        <v>0.2671935925689478</v>
       </c>
       <c r="J316" s="20" t="n">
-        <v>0.4826358742837298</v>
+        <v>0.4908340971585702</v>
       </c>
       <c r="K316" s="20" t="n">
         <v>0.504950495049505</v>
       </c>
       <c r="L316" s="19" t="n">
-        <v>-0.09498682541574716</v>
+        <v>-0.09498703277688722</v>
       </c>
       <c r="M316" s="19" t="n">
-        <v>-0.4789697530532493</v>
+        <v>-0.470851904912476</v>
       </c>
       <c r="N316" s="20" t="n">
         <v>0</v>
@@ -43226,7 +43218,7 @@
         <v>-10.5</v>
       </c>
       <c r="J190" s="30" t="n">
-        <v>50.5</v>
+        <v>51.5</v>
       </c>
       <c r="K190" s="18" t="n">
         <v>300</v>
@@ -43456,10 +43448,10 @@
         <v>54.5</v>
       </c>
       <c r="K195" s="13" t="n">
-        <v>-4500</v>
+        <v>-3600</v>
       </c>
       <c r="L195" s="13" t="n">
-        <v>1700</v>
+        <v>1500</v>
       </c>
       <c r="M195" s="12" t="inlineStr">
         <is>
@@ -43693,10 +43685,10 @@
         <v>44.5</v>
       </c>
       <c r="K200" s="18" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L200" s="18" t="n">
-        <v>-166</v>
+        <v>-175</v>
       </c>
       <c r="M200" s="17" t="inlineStr">
         <is>
@@ -44148,7 +44140,7 @@
         <v>-5.5</v>
       </c>
       <c r="J210" s="30" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="K210" s="18" t="n">
         <v>180</v>
@@ -44200,10 +44192,10 @@
         <v>49.5</v>
       </c>
       <c r="K211" s="13" t="n">
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="L211" s="13" t="n">
-        <v>-1450</v>
+        <v>-1600</v>
       </c>
       <c r="M211" s="12" t="inlineStr">
         <is>
@@ -44246,7 +44238,7 @@
         <v>-16.5</v>
       </c>
       <c r="J212" s="30" t="n">
-        <v>49.5</v>
+        <v>50.5</v>
       </c>
       <c r="K212" s="18" t="n">
         <v>575</v>
@@ -44830,10 +44822,10 @@
         <v>53.5</v>
       </c>
       <c r="K225" s="13" t="n">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="L225" s="13" t="n">
-        <v>-1200</v>
+        <v>-1350</v>
       </c>
       <c r="M225" s="12" t="inlineStr">
         <is>
@@ -45014,10 +45006,10 @@
         <v>62.5</v>
       </c>
       <c r="K229" s="13" t="n">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="L229" s="13" t="n">
-        <v>-250</v>
+        <v>-278</v>
       </c>
       <c r="M229" s="12" t="inlineStr">
         <is>
@@ -45560,16 +45552,16 @@
       </c>
       <c r="H241" s="12" t="inlineStr"/>
       <c r="I241" s="23" t="n">
-        <v>-4.5</v>
+        <v>-5.5</v>
       </c>
       <c r="J241" s="29" t="n">
         <v>51.5</v>
       </c>
       <c r="K241" s="13" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="L241" s="13" t="n">
-        <v>-192</v>
+        <v>-218</v>
       </c>
       <c r="M241" s="12" t="inlineStr">
         <is>
@@ -45615,10 +45607,10 @@
         <v>52.5</v>
       </c>
       <c r="K242" s="18" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="L242" s="18" t="n">
-        <v>-166</v>
+        <v>-180</v>
       </c>
       <c r="M242" s="17" t="inlineStr">
         <is>
@@ -45972,7 +45964,7 @@
         <v>-10</v>
       </c>
       <c r="J250" s="30" t="n">
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
       <c r="K250" s="18" t="n">
         <v>310</v>
@@ -72856,7 +72848,7 @@
         </is>
       </c>
       <c r="B4" s="39" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="5">
@@ -72876,7 +72868,7 @@
         </is>
       </c>
       <c r="B6" s="39" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7">
